--- a/outputs/linkedin_hr_growth_leads_100.xlsx
+++ b/outputs/linkedin_hr_growth_leads_100.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$R$101</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,19 +17,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -53,17 +43,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Headline 4" xfId="1" builtinId="19" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,114 +415,94 @@
   </sheetPr>
   <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="54" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>linkedin_url</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>company_industry</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>company_size</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>seniority</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>likely_pain_point</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>english_need_signal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>outreach_angle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>lead_score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>personalized_linkedin_dm</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>personalized_cold_email</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>personalization_basis</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -575,54 +542,58 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>Human Resources / People Management</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to verify</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee language proficiency and global meeting readiness</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>High, due to the HR role requiring effective communication in English</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>50</v>
+          <t>Enhancing employee confidence in speaking English for better global collaboration</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Merhaba Elif Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Elif, HR alanındaki deneyiminizle çalışanların İngilizce yeterliliğini artırmanın önemini biliyorsunuz. Konuşarak Öğren ile, ekiplerinizi global işbirliklerine hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Elif Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizi Global İşbirliğine Hazırlayın
+Merhaba Elif,
+HR profesyoneli olarak, ekip üyelerinizin İngilizce yeterliliklerinin ve global toplantılara katılım becerilerinin arttırılması gerektiğini biliyorum. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği sunarak, kendilerine olan güvenlerini artırmalarına ve uluslararası işbirliklerine daha etkili katılmalarına yardımcı olabilir.
+Detayları görüşmek isterseniz, sevinirim.
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Elif'in HR alanındaki uzmanlığı ve ekiplerin dil yeterliliği ile global işbirliklerine hazırlık ihtiyacı</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -639,12 +610,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Antwell Suites Istanbul</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -655,7 +626,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Maltepe, Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -665,59 +636,61 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>Medium (estimate)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving English speaking skills for effective communication in global meetings.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR Manager, likely focused on employee development and communication skills.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of enhanced speaking confidence and global meeting readiness for HR teams.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Merhaba Eylül Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Eylül, Antwell Suites İstanbul'da İnsan Kaynakları Müdürü olarak çalışan bir profesyonel olarak, ekiplerinizin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma pratiğine ihtiyaç duyduğunuzu biliyorum. Bu konuda konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Eylül Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Eylül Hanım,
+Antwell Suites İstanbul'daki İnsan Kaynakları Müdürü olarak, global toplantılarda etkili iletişim için İngilizce konuşma becerilerini geliştirmenin önemini biliyorsunuzdur. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, çalışanlarınızın kendine güvenini artırmayı ve iletişim becerilerini geliştirmeyi amaçlıyoruz. Bu sayede, ekiplerinizin global arenada daha etkili olmasını sağlayabiliriz. Görüşmek ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Eylül Özüşanlı'nın pozisyonu ve global toplantılarda etkili iletişim ihtiyacı</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -729,12 +702,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Emelda Deri Konfeksiyon San.Tic.A.Ş.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -745,7 +718,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -755,59 +728,63 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>Deri ve Konfeksiyon</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>Estimate: 100-500 employees</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global pazarlar ve iletişim ihtiyaçları doğrultusunda çalışanların İngilizce konuşma becerilerini geliştirmek.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İnsan Kaynakları Müdürü olarak, ekip içi iletişim ve global toplantılara hazırlık için İngilizce konuşma pratiğine ihtiyaç duyabilir.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>58</v>
+          <t>Emelda Deri'nin uluslararası pazarlarda rekabet edebilmesi için çalışanlarının İngilizce iletişim becerilerini artırmak.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Merhaba Savaş Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Savaş Bey, Emelda Deri'nin global pazarlarda güçlü bir konumda kalması için çalışanlarınızın İngilizce becerilerini geliştirmesi çok önemli. Konuşarak Öğren, online pratik ve takip ile bu süreci destekleyebilir. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Savaş Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Emelda Deri için İngilizce İletişim Becerileri Geliştirme
+Merhaba Savaş Bey,
+Emelda Deri'nin uluslararası pazarlarda rekabet edebilmesi için çalışanlarınızın İngilizce iletişim becerilerini artırmak, kritik bir adım. Konuşarak Öğren, online İngilizce konuşma pratiği sunarak ekip içi iletişimi güçlendirmeye ve global toplantılara hazırlığı artırmaya yardımcı olabilir. Bu süreçte nasıl bir destek sağlayabileceğimizi konuşmak ister misiniz?
+Saygılarımla,
+[Adınız]  
+[Pozisyonunuz]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Savaş T'nin İnsan Kaynakları Müdürü olarak, Emelda Deri'nin global pazarlarda rekabet edebilmesi ve ekip içi iletişimde İngilizce konuşma pratiğine ihtiyacı olduğu dikkate alınarak hazırlandı.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -819,12 +796,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Kastamonu Entegre Ağaç San. A.Ş.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -835,7 +812,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -845,59 +822,62 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>Wood Industry</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>Large (estimate based on company profile)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid to Senior level</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving communication skills for global collaboration</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR manager, likely focused on employee development and training</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>58</v>
+          <t>Enhancing employee speaking confidence for international meetings</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Merhaba Veysel Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Veysel Bey, Kastamonu Entegre'deki uluslararası projelerde çalışan ekiplerin iletişim becerilerini geliştirme konusunda bir çözüm sunmak isterim. Online İngilizce konuşma pratiği ile çalışanlarınızın özgüvenini artırmak için bir görüşme ayarlayabilir miyiz?</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Veysel Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Takımınızın İletişim Becerilerini Geliştirin
+Merhaba Veysel Bey,
+Kastamonu Entegre Ağaç San. A.Ş. olarak uluslararası işbirliklerinizde çalışanlarınızın iletişim becerilerinin kritik öneme sahip olduğunu biliyorum. Konuşarak Öğren, ekiplerinize online İngilizce konuşma pratiği sunarak, uluslararası toplantılarda daha fazla özgüven kazanmalarına yardımcı olabilir. Uzaktan takip ve raporlama ile gelişimlerini de gözlemleyebilirsiniz.
+Detayları konuşmak isterseniz, size uygun bir zaman ayarlamak isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Veysel Bey'in İnsan Kaynakları Müdürü olarak uluslararası işbirlikleri ve çalışan gelişimi konusundaki odak noktası.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -935,54 +915,58 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen çalışanların İngilizce konuşma becerileri ve global toplantılara hazırlık eksiklikleri</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Kurumsal ekipler için online İngilizce konuşma pratiği ihtiyacı</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>50</v>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness üzerine değer sunma</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Merhaba Berkan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Berkan, iletişim becerilerinin geliştirilmesi konusundaki çalışmalarınızı görüyorum. Kurumsal ekipler için İngilizce konuşma pratiği sağlıyor ve bu sayede global toplantılara hazırlığı artırıyoruz. Bir sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Berkan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Kurumsal Ekipler İçin İngilizce Konuşma Pratiği
+Merhaba Berkan,
+Gelişen çalışanlarınızın İngilizce konuşma becerilerini artırmak ve global toplantılara hazırlıklarını güçlendirmek adına size yardımcı olabileceğimizi düşünüyorum. Konuşarak Öğren, kurumsal ekiplerin online İngilizce konuşma pratiği yapmasını sağlarken, gelişim takibi ve raporlama sunarak performanslarını artırmayı hedefliyor. İlgilenirseniz, sizinle bir görüşme ayarlamak isterim.
+Saygılarımla,
+[Adınız]
+[Pozisyonunuz]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Berkan'ın HR profesyoneli olarak çalışanların İngilizce konuşma becerilerini geliştirme ihtiyacına yönelik bir yaklaşım sergilemek.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -999,12 +983,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Naci Çorap San. ve Tic. A.Ş.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları ve İdari İşler Müdürü</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1015,7 +999,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1025,59 +1009,62 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employee communication skills for global business interactions</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR manager, likely responsible for employee training and development in language skills</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>58</v>
+          <t>Highlighting the importance of English speaking confidence for employee performance in global meetings</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Merhaba Nihal Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Nihal, kurumunuzun global iş ilişkilerindeki iletişim becerilerini geliştirmeye yönelik çabalarınızı takdir ediyorum. Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yapmalarına yardımcı olabiliriz. Daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Nihal Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Nihal,
+Naci Çorap San. ve Tic. A.Ş.'deki iletişim becerilerini güçlendirme çabalarınızı biliyorum. Global iş ortamında etkili iletişim, başarı için kritik öneme sahip. Biz, Konuşarak Öğren olarak, çalışanlarınıza online İngilizce konuşma pratiği sunarak, güvenli bir iletişim ortamı yaratmayı hedefliyoruz. Bu süreçte gelişimlerini takip edip raporlayarak, ihtiyaçlarınıza özel çözümler sunabiliriz. 
+Detayları konuşmak ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Nihal Gül'ün pozisyonu ve şirketinin global iş ilişkilerindeki iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1076,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Sektör Kimya</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1105,7 +1092,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Üsküdar, Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1115,59 +1102,62 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>Kimya</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Müdür</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Çalışanların İngilizce konuşma becerilerinde eksiklikler ve global toplantılara hazırlık</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İnsan Kaynakları departmanında çalışanların iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>58</v>
+          <t>Kurumsal eğitim programları aracılığıyla çalışanların İngilizce konuşma pratiği yapmalarını sağlama</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Merhaba Nursen Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Nursen, çalışanlarınızın İngilizce konuşma becerilerini geliştirmelerine yardımcı olabileceğimizi düşündüm. Kurumsal eğitim programlarımızla, global toplantılara hazırlıkları için pratik imkanı sunuyoruz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Nursen Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce Konuşma Becerilerini Geliştirme Fırsatı
+Merhaba Nursen,
+Sektör Kimya'daki çalışanlarınızın İngilizce konuşma becerilerindeki eksiklikleri gidermeye yardımcı olabileceğimizi düşünüyorum. Kurumsal eğitim programlarımızla, global toplantılara daha iyi hazırlanmalarına ve iletişim becerilerini geliştirmelerine destek sunuyoruz. 
+Daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Nursen Asar'ın İnsan Kaynakları Müdürü olarak çalışanlarının İngilizce konuşma becerilerinde eksiklikler yaşadığını ve global toplantılara hazırlık ihtiyacını belirtmesi.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1169,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>VisionF Yachts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1195,7 +1185,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1205,59 +1195,62 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>Yacht Manufacturing</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>Estimate 50-200 employees</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level Management</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing communication skills among employees for global interactions</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR Manager, likely responsible for employee development and training programs</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>58</v>
+          <t>Emphasize the importance of speaking confidence and readiness for global meetings, which aligns with the company's operational needs</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Merhaba Sevda Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sevda, global etkileşimlerde iletişim becerilerinin önemi gün geçtikçe artıyor. Konuşarak Öğren ile ekibinizin İngilizce konuşma pratiğini geliştirerek bu süreci destekleyebiliriz. Detayları paylaşmak isterim. Selamlar!</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sevda Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Sevda Hanım,
+VisionF Yachts’ta çalışanların iletişim becerilerini geliştirmek, global etkileşimlerde büyük bir fark yaratabilir. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ve gelişim takibi sunarak, ekibinizin kendine güvenen bir şekilde toplantılara katılmasını sağlıyoruz. Bu konuda detayları görüşmek isterim.
+İyi çalışmalar,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sevda Kartal, VisionF Yachts'ta İnsan Kaynakları Müdürü olarak çalışanların gelişimine odaklanıyor; global etkileşimlerde iletişim becerilerinin önemini vurgulamak.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1295,54 +1288,57 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında ekiplerin İngilizce konuşma becerilerinin artırılması</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyonellerinin global toplantılarda etkili iletişim kurma ihtiyacı</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>50</v>
+          <t>Kurumsal ekiplerin İngilizce konuşma pratiği yaparak özgüven kazanmalarını sağlama</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Merhaba Burak Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Burak, global iş ortamında ekiplerin İngilizce konuşma becerilerini artırmak için neler yapıyorsunuz? Konuşarak Öğren ile kurumsal ekiplerinize online pratik imkanı sunarak özgüven kazandırmayı hedefliyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Burak Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Burak,
+Gelişen global iş ortamında, ekiplerinizin İngilizce konuşma becerilerini artırmak kritik bir öneme sahip. Konuşarak Öğren, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, özgüven kazanmalarına yardımcı oluyor. 
+Hedefimiz, HR profesyonellerinin global toplantılarda etkili iletişim kurma ihtiyaçlarına yanıt vermek. Eğer bu konuda daha fazla bilgi almak isterseniz, sizinle görüşmekten mutluluk duyarım.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Burak'ın HR profesyoneli olarak global iş ortamında ekiplerin İngilizce konuşma becerilerini artırma ihtiyacı ve HR teknoloji sektöründe yer alması.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1359,12 +1355,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Op. Dr. Fatih Kırar / Kırar Holding</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1375,7 +1371,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Şişli, Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1385,59 +1381,62 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-Level</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global pazarlarda iletişim yetkinliği ve dil becerileri</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İngilizce konuşma pratiği ihtiyacı, global toplantılara hazırlık</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerin konuşma güvenini arttırma ve gelişim takibi sağlama</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Merhaba Şefaat Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Şefaat Bey, Kırar Holding'deki insan kaynakları süreçlerinizi takip ediyorum. Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Global pazarlarda iletişim yetkinliğini artırmanın yollarını keşfetmek ister misiniz?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Şefaat Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Yetkinliğini Artırın
+Merhaba Şefaat Bey,
+Kırar Holding'deki ekiplerinizin global pazarlarda etkili iletişim kurabilmesi için İngilizce konuşma pratiği sunuyoruz. Online platformumuz, çalışanlarınızın konuşma güvenini artırırken, gelişim takibi ve raporlama imkanı da sağlıyor. Global toplantılara daha iyi hazırlanmaları için nasıl destek olabileceğimizi konuşmak ister misiniz?
+İyi çalışmalar,
+[Adınız]
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Şefaat Özbakir'in pozisyonu ve şirketinin sağlık sektöründeki global pazarlardaki iletişim yetkinliği ihtiyacı</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1448,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Bilek Istanbul</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Human Resources Manager</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1465,7 +1464,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1475,59 +1474,63 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>Mid-size (estimate)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee communication skills for global interactions</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As a Human Resources Manager, likely focused on employee development and training</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>58</v>
+          <t>Offering a solution to enhance speaking confidence and prepare teams for global meetings</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Merhaba Esra Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Esra, Bilek İstanbul'da çalışanların global iletişim becerilerini geliştirmek için bir çözüm arayışında olduğunuzu anlıyorum. Konuşarak Öğren, ekiplerinizi online İngilizce konuşma pratiği ile güçlendirmeye yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Esra Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Esra Hanım,
+Bilek İstanbul'daki çalışanların global iletişim becerilerini artırmak için etkili bir çözüm aradığınızı biliyorum. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, bireylerin kendine güvenini artırmayı ve global toplantılara hazırlıklı olmalarını sağlamayı hedefliyoruz. 
+Daha fazla bilgi almak isterseniz, sizinle bir görüşme ayarlamaktan memnuniyet duyarım.
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Esra Başbuğa'nın pozisyonu ve Bilek İstanbul'daki rolü, global iletişim becerilerini geliştirme ihtiyacı üzerine odaklanıyor.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1547,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1555,7 +1558,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1565,54 +1568,56 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>estimate 50-200 employees</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee confidence in English communication for global meetings</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR Manager, likely focuses on employee development and training solutions</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>58</v>
+          <t>Enhancing speaking confidence and readiness for international collaboration within teams</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Merhaba Pervin Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Pervin, İngilizce iletişimde güven artırma konusunda çalışan bir HR profesyoneli olarak, ekibinizin uluslararası toplantılarda daha hazır olmasına yardımcı olabileceğimi düşünüyorum. Konuşarak Öğren ile detayları paylaşmak isterim. Görüşmek üzere!</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Pervin Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Uluslararası Toplantılarda Güvenli İletişim İçin Çözüm
+Merhaba Pervin Hanım,
+İnsan Kaynakları Müdürü olarak, ekiplerinizin uluslararası toplantılarda daha güvenli bir şekilde iletişim kurmasına yardımcı olabileceğimizi düşünüyorum. Konuşarak Öğren, çalışanlarınızın İngilizce konuşma pratiği yapmalarını, gelişimlerini takip etmelerini ve raporlama süreçlerini kolaylaştırmalarını sağlıyor. Ekibinizin uluslararası işbirliklerine daha hazır olmasını sağlamak için bir görüşme ayarlamak ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Pervin Doğan Korkmaz'ın HR Müdürü olarak ekiplerin İngilizce iletişimde daha güvenli olmasına yönelik ilgi ve ihtiyaçları.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1629,12 +1634,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Yapay Zekâ Girişim Fabrikası @ İş Bank Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1645,7 +1650,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1655,59 +1660,62 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-Senior Level</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing employees' speaking confidence and global meeting readiness.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR Manager in a global company, there is likely a need for English communication skills among employees.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>50</v>
+          <t>Offering tailored online English speaking practice to enhance employee communication skills and support their professional development.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Merhaba Merve Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Merve, İngilizce konuşma pratiği ve gelişim takibi konusunda destek sunuyoruz. Çalışanlarınızın kendine güvenini artırmalarına ve global toplantılara hazır olmalarına yardımcı olabileceğimizi düşünüyorum. Tanışmak ister misiniz?</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Merve Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Merve Hanım,
+Yapay Zekâ Girişim Fabrikası’nda çalışanlarınızın İngilizce iletişim becerilerini geliştirmelerine yardımcı olmak için online konuşma pratiği sunuyoruz. Global toplantılara daha hazır olmaları ve kendilerine güven duymaları adına kişiselleştirilmiş programlarımızla destek olabiliriz. 
+Detayları konuşmak isterseniz, size uygun bir zaman ayarlayabiliriz.
+Sevgiler,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Merve'nin HR Müdürü olarak çalıştığı finans sektöründe, çalışanların İngilizce iletişim becerilerinin geliştirilmesi ihtiyacı.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1727,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>İş Merkezleri Yönetim ve İşletim A.Ş. (İşmer)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1735,7 +1743,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1745,59 +1753,62 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>Facility Management</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>Estimate 50-200 employees</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid to Senior Level</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Need for enhancing employee communication skills for global collaboration and meetings.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As HR Manager, likely involved in talent development and employee training initiatives.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>58</v>
+          <t>Offer solutions for improving speaking confidence and global meeting readiness among employees.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Merhaba Aşır Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Aşır Bey, İşmer'deki çalışanların global işbirlikleri ve toplantılardaki iletişim becerilerini geliştirmeye yönelik bir çözüm sunmak isterim. Konuşarak Öğren ile online İngilizce pratiği yaparak, çalışanlarınızın kendine güvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Aşır Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirelim
+Merhaba Aşır Bey,
+İş Merkezleri Yönetim ve İşletim A.Ş. olarak global işbirliklerinde etkili iletişim becerileri, başarı için kritik. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği sunarak, kendilerine olan güvenlerini artırmalarını sağlıyor. Programımız, gelişim takibi ve raporlama ile destekleniyor. İlgilenirseniz detayları paylaşmak isterim.
+Saygılarımla,
+[İsminiz]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Aşır Özgür Erdoğan'ın İnsan Kaynakları Müdürü olarak global işbirlikleri ve çalışan iletişimi konusundaki ihtiyaçları</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1809,12 +1820,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Eti Alüminyum A.Ş.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1825,7 +1836,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1835,59 +1846,63 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>Alüminyum Üretimi</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>Büyük (1000+ çalışan)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Yönetici</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Ekip üyelerinin İngilizce konuşma becerilerinin geliştirilmesi ve uluslararası toplantılara hazırlık</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İngilizce konuşma pratiği ihtiyacı, özellikle global projelerde yer alan ekipler için önemli olabilir</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerde speaking confidence artırma ve gelişim takibi sağlama</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Merhaba Ahmet Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ahmet Bey, kurumsal ekiplerde İngilizce konuşma pratiğinin önemini biliyorum. Konuşarak Öğren ile ekip üyelerinizin speaking confidence'ını artırabilir ve uluslararası toplantılara daha iyi hazırlanmalarını sağlayabilirsiniz. Detayları paylaşmak isterim. Sevgiler!</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ahmet Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Ahmet Bey,
+Eti Alüminyum A.Ş.'deki ekiplerinizin İngilizce konuşma becerilerini geliştirmek ve uluslararası projelere daha iyi hazırlanmalarını sağlamak için Konuşarak Öğren olarak size destek olabiliriz. Online İngilizce konuşma pratiği sunuyor, gelişim takibi ve raporlama ile ekip üyelerinizin speaking confidence'ını artırıyoruz. Bu sayede, global projelerdeki etkinliklerini de yükseltebiliriz. Görüşmek ister misiniz?
+Saygılarımla,
+[Adınız]  
+[Unvanınız]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ahmet Hergüner'in pozisyonu ve şirketindeki ekiplerin İngilizce konuşma becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1925,54 +1940,57 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication and global collaboration challenges</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in improving employee communication skills, particularly in English.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>58</v>
+          <t>Enhancing speaking confidence and meeting readiness for employees, which aligns with HR development goals.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Merhaba Ceren Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ceren, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, iletişim ve küresel işbirliği konularında yaşadıkları zorlukları aşmalarına yardımcı olabileceğimize inanıyorum. Konuşarak Öğren ile bu konuda nasıl destek olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ceren Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Ceren Hanım,
+HR profesyoneli olarak, çalışanlarınızın iletişim becerilerini geliştirmek ve global işbirliğini artırmak sizin için ne kadar önemli olduğunu biliyorum. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği sunarak, çalışanların kendine güvenini artırmalarına ve toplantılara daha hazırlıklı girmelerine yardımcı oluyor. Şirketinizin HR gelişim hedefleriyle uyumlu bir çözüm sunmak için sizinle konuşmak isterim.
+İlginizi çekerse, bir görüşme ayarlayalım.
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli olarak çalışanların iletişim becerilerini geliştirme ihtiyacı ve global işbirliği zorlukları</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2015,54 +2033,57 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level or higher - estimate</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Need for effective communication in global meetings</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee training and development, which may include language skills enhancement</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>50</v>
+          <t>Offering solutions to improve speaking confidence and meeting readiness for their team</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Merhaba Tuğçe Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Tuğçe, global toplantılardaki iletişim zorluklarını aşmak için ekibinize online İngilizce konuşma pratiği sunuyoruz. İletişim becerilerini geliştirmek ve toplantılara daha hazır girmek için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Tuğçe Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İletişim Becerilerini Geliştirin
+Merhaba Tuğçe,
+Kurumsal ekiplere yönelik sunduğumuz online İngilizce konuşma pratiği, gelişim takibi ve raporlama hizmeti ile global toplantılardaki iletişim zorluklarını aşmanıza yardımcı olabiliriz. Ekibinizin kendine güvenini artırarak, etkili iletişim kurmalarını sağlamak istiyoruz. Bu konuda nasıl bir yol alabileceğimiz hakkında bir görüşme ayarlamak ister misiniz?
+İlginiz için teşekkürler,
+[Adınız]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Tuğçe'nin HR profesyoneli olarak global toplantılardaki iletişim konusundaki sorunları hedef alarak, ekibinin konuşma pratiği ve kendine güven geliştirmesi ihtiyacını vurgulamak.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2105,54 +2126,57 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employees' English speaking confidence and global communication skills</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely to be focused on employee development and training in language skills</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of enhancing speaking confidence for global meetings and effective communication in diverse teams</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Merhaba Latife Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Latife, HR profesyonellerinin dil becerilerini geliştirmeye yönelik çalışmalarda oldukça etkili olabileceğini düşünüyorum. Konuşarak Öğren ile ekip üyelerinizin İngilizce konuşma güvenini artırarak global iletişimde daha etkili olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Latife Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Latife,
+Kurumsal ekibinizin global toplantılarda daha güçlü bir iletişim kurmasını sağlamak için İngilizce konuşma pratiği sunuyoruz. Konuşarak Öğren ile çalışanlarınızın konuşma güvenini artırarak, çeşitli takımlarda etkili bir iletişim sağlamalarına yardımcı olabiliriz. Bu konuda bir görüşme yapmak ister misiniz?
+Sevgiler,
+[Adınız]
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Latife Dülgercan'ın HR profesyoneli olarak çalışan gelişimine odaklandığı ve ekiplerin global iletişim becerilerini artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2195,54 +2219,56 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely focused on employee development and training</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>58</v>
+          <t>Highlight the importance of communication skills for global collaboration and employee growth</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Merhaba H Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Gökben, iletişim becerilerinin küresel işbirliği için ne kadar önemli olduğunu biliyorum. Kurumsal ekiplerde İngilizce konuşma pratiği ve gelişim takibi konusundaki çözümlerimizi keşfetmek istersen, sohbet edelim.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba H Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba,
+Kurumsal ekibinizin İngilizce konuşma pratiği ve global toplantılara hazırlıklı olmasını sağlamak, çalışanlarınızın kariyer gelişimi için kritik. Konuşarak Öğren olarak, online platformumuzla bu süreci kolaylaştırıyor ve gelişim takibi yaparak raporlama sunuyoruz. Çalışanlarınızın kendine güvenini artırmak ve global iş ortamında daha etkili olmalarını sağlamak için bir görüşme ayarlamak ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Gökben'in HR profesyoneli olması ve iletişim becerilerinin geliştirilmesine odaklanması.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2285,54 +2311,58 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Estimate based on title; likely mid to senior level given HR/People Professional title</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for English language development within corporate teams</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>58</v>
+          <t>Emphasize the importance of communication skills in global business environments and how Konuşarak Öğren can enhance team performance</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Merhaba Ümmühan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ümmühan, iletişim becerilerinin global iş dünyasında ne kadar önemli olduğunu biliyoruz. Konuşarak Öğren ile ekibinizin İngilizce konuşma becerilerini geliştirmesine yardımcı olabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ümmühan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İletişim Becerilerini Geliştirin
+Merhaba Ümmühan,
+Global iş dünyasında etkili iletişim, başarıyı belirleyen kritik bir faktördür. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, çalışanlarınızın özgüvenini artırmayı ve global toplantılara hazırlıklarını geliştirmeyi hedefliyoruz. İş birliğimiz sayesinde, ekibinizin performansını önemli ölçüde artırabiliriz. Detayları görüşmek için uygun bir zamanınız var mı?
+İyi çalışmalar dilerim,
+[Adınız]  
+[Pozisyonunuz]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ümmühan'ın HR profesyoneli olarak iletişim becerileri geliştirme konusundaki ilgi alanı ve global iş dünyasındaki önem.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2375,54 +2405,58 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Kurumsal ekiplerde speaking confidence eksikliği ve global meeting readiness ihtiyacı</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyonellerinin İngilizce iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>50</v>
+          <t>İngilizce konuşma pratiği ile ekiplerin global toplantılara daha hazırlıklı hale gelmesine yardımcı olma</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Merhaba Nazan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Nazan, kurumsal ekiplerdeki İngilizce konuşma pratiği ile ilgili zorlukları bildiğinizi düşünüyorum. Konuşarak Öğren olarak, ekiplerinizi global toplantılara daha iyi hazırlamak için online çözümler sunuyoruz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Nazan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekipleriniz İçin İngilizce Konuşma Pratiği
+Merhaba Nazan,
+Şirketinizin global toplantılarda daha fazla başarı elde etmesi için ekiplerinizin İngilizce konuşma becerilerini geliştirmek önem taşıyor. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Bu sayede, speaking confidence eksikliğini giderip, global toplantılara daha hazırlıklı hale gelmelerine yardımcı olabiliriz. 
+Size uygun bir zamanda detayları paylaşmak isterim.
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Nazan'ın HR profesyoneli olması ve kurumsal ekiplerdeki speaking confidence eksikliği ile global meeting readiness ihtiyacını göz önünde bulundurarak, Konuşarak Öğren'in çözümlerini sundum.</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2465,54 +2499,57 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee English speaking confidence and readiness for global meetings</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, there may be a need for improving employees' English speaking skills</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>58</v>
+          <t>Highlighting the importance of English communication skills for team effectiveness and global collaboration</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Merhaba Ilker Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba İlker, HR profesyonelleri olarak iletişim becerilerinin önemini biliyoruz. Ekibinizin İngilizce konuşma güvenini artırmak, global toplantılara hazırlıklarını güçlendirmek için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz?</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ilker Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Geliştirin
+Merhaba,
+Şirketinizdeki ekiplerin global toplantılara daha hazır ve güvenle katılabilmesi için İngilizce iletişim becerilerini geliştirmek büyük bir fırsat. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği, gelişim takibi ve raporlama sunuyoruz. Bu süreçte, çalışanlarınızın kendine güveni artacak ve etkili bir iletişim ile işbirlikleri güçlenecek. 
+Detayları görüşmek isterseniz, size yardımcı olmaktan memnuniyet duyarım.
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>İlker'in HR profesyoneli olması ve çalışanlarının İngilizce konuşma güvenini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2555,54 +2592,60 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında çalışanların İngilizce konuşma pratiği yapma ihtiyacı</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness önemi</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>58</v>
+          <t>Merve'nin çalışanlarının İngilizce konuşma pratiği yapmalarına yardımcı olmak için sunabileceğimiz çözümler</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Merhaba Merve Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Merve, gelişen global iş ortamında ekiplerinizin İngilizce konuşma pratiği yapma ihtiyacını göz önünde bulundurarak, Konuşarak Öğren olarak onlara nasıl destek olabileceğimizi paylaşmak isterim. Görüşmeye ne dersiniz?</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Merve Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Merve,
+Umarım iyisinizdir. Gelişen global iş ortamında, çalışanlarınızın İngilizce konuşma pratiği yapma ihtiyacının ne denli önemli olduğunu biliyorum. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunuyoruz. Böylece hem speaking confidence kazanabilirler hem de global toplantılara daha hazır hale gelebilirler.
+Detayları konuşmak için uygun bir zaman ayarlayabilir miyiz?
+Sevgiler,
+[Adınız] [Soyadınız]  
+[Pozisyonunuz]  
+[Şirket Adınız]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Merve'nin çalışanlarının İngilizce konuşma pratiği yapma ihtiyacı ve global iş ortamındaki rolü.</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2645,54 +2688,57 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely values communication skills development for teams</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>58</v>
+          <t>Highlighting how Konuşarak Öğren can enhance employee communication skills and readiness for global interactions</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Merhaba Mesut Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Mesut, insan kaynakları profesyonellerinin ekip iletişimini geliştirmelerine yardımcı olma konusunda uzmanız. Konuşarak Öğren olarak, çalışanlarınızın global toplantılara hazır olmalarını sağlamak için online İngilizce konuşma pratiği sunuyoruz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Mesut Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Mesut,
+Şirketinizde ekiplerinizi global toplantalara daha iyi hazırlamak ve İngilizce konuşma becerilerini geliştirmek için bir çözüm arıyorsanız, Konuşarak Öğren tam size göre. Online platformumuz sayesinde çalışanlarınız, güvenle iletişim kurma pratiği yapabilir. Gelin, ekiplerinizi daha etkili hale getirelim.
+Detayları görüşmek ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Mesut Gülçiçek'in HR profesyoneli olarak, çalışan iletişimi ve global toplantılara hazırlık konularına değer verdiği düşünülerek hazırlandı.</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2735,54 +2781,56 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in training and development, which may include English language skills</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>50</v>
+          <t>Offering solutions to enhance communication skills and boost employee confidence in international settings</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Merhaba Ali Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ali, iletişim becerilerini geliştirmek ve çalışanların uluslararası toplantılara daha hazırlıklı olmalarını sağlamak için çözümler sunuyoruz. Konuşarak Öğren ile online İngilizce pratiği yaparak bu hedeflere ulaşmanızda yardımcı olabiliriz. Detayları görüşmek ister misin?</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ali Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Ali,
+Kurumsal ekibinizin uluslararası ortamlarda daha etkili iletişim kurabilmesi için destek sunmak istiyoruz. Konuşarak Öğren, online İngilizce konuşma pratiği ile çalışanlarınızın kendine güvenini artırmayı ve global toplantılara hazır olmalarını sağlamayı hedefliyor. İlgilenirseniz, nasıl bir işbirliği yapabileceğimizi konuşmak isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ali'nin HR profesyoneli olarak çalışanların iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2825,54 +2873,59 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level - estimate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving team communication and confidence in English during meetings</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in global communications and employee development</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of enhancing speaking confidence and readiness for global meetings, which aligns with HR's focus on employee training and development</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Merhaba Ecem Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ecem, HR profesyonellerinin ekip iletişimini güçlendirmek için arayış içinde olduğunu biliyorum. Konuşarak Öğren ile İngilizce konuşma pratiği yaparak, global toplantılara daha hazır hale gelmeleri konusunda nasıl yardımcı olabileceğimizi keşfetmek ister misin?</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ecem Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Ecem,
+Ekiplerinizin İngilizce konuşma pratiği ile iletişim becerilerini geliştirmeleri, global toplantılarda daha özgüvenli olmalarını sağlayabilir. Konuşarak Öğren, kurumsal ekipler için özel olarak tasarlanmış online İngilizce programları sunuyor. Bu sayede, çalışanlarınızın gelişimini takip edebilir ve raporlarla destekleyebilirsiniz.
+Detayları konuşmak için bir görüşme ayarlayabilir miyiz?
+İyi çalışmalar,
+[Adınız]  
+[Pozisyonunuz]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ecem'in HR profesyoneli olarak ekip iletişimini ve İngilizce becerilerini geliştirme ihtiyacı.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2915,54 +2968,57 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence among employees and ensuring readiness for global meetings.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training, indicating a potential need for English communication skills enhancement.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>58</v>
+          <t>Highlight how Konuşarak Öğren can support employee development through online English speaking practice, increasing team confidence and global engagement.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Merhaba Şeyda Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Şeyda, HR profesyonellerinin ekiplerinin konuşma özgüvenini artırmalarına yardımcı olduğumuzu duydum. Global toplantılara hazırlık konusunda nasıl destek olabileceğimizi konuşmak ister misin?</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Şeyda Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Gücünü Artırın
+Merhaba Şeyda,
+Şirketinizdeki çalışanların İngilizce konuşma becerilerini geliştirmeleri, global toplantılarda daha etkili olmaları için kritik öneme sahip. Konuşarak Öğren, online İngilizce konuşma pratiğiyle ekip üyelerinizin güvenini artırarak, global arenada daha etkin olmalarına yardımcı olabilir.
+Gelişim takibi ve raporlama ile desteklenen programlarımız hakkında daha fazla bilgi almak istersen, sizinle görüşmeyi çok isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Şeyda'nın HR profesyoneli olarak çalışanlarının konuşma özgüvenini geliştirme ihtiyacı ve global toplantılara hazırlık konusundaki ilgisi.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3005,54 +3061,59 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in international communications requiring English proficiency</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>58</v>
+          <t>Enhancing employee speaking confidence and meeting readiness through tailored English conversation practice</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Merhaba Mehmet Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Mehmet, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve uluslararası toplantılara hazırlıklarını güçlendirmek için nasıl bir yol izlediğinizi merak ediyorum. Bu konuda size yardımcı olabilecek bir çözüm sunabilirim. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Mehmet Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Mehmet,
+Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek, uluslararası iletişimde daha etkili olmalarını sağlamak için önemli bir adım. Konuşarak Öğren olarak, çalışanlarınız için kişiselleştirilmiş online İngilizce konuşma pratiği sunuyoruz. Bu sayede, hem konuşma özgüvenleri artacak hem de global toplantılara hazırlıkları güçlenecek. 
+Detayları konuşmak için zaman ayırabilir miyiz? 
+Saygılarımla,
+[Adınız]
+[Pozisyonunuz]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Mehmet'in HR profesyoneli olması ve çalışanlarının İngilizce konuşma özgüvenine ve global toplantılara hazırlıklarına odaklanması</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3095,54 +3156,60 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Speaking confidence in global meetings and effective communication within diverse teams</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in international communication and team development, suggesting a need for English speaking practice</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>50</v>
+          <t>Highlight how Konuşarak Öğren can enhance speaking confidence and global meeting readiness for HR teams, thereby improving team dynamics and performance</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Merhaba Serpil Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Serpil, global toplantılarda konuşma güveni ve farklı takımlarla etkili iletişim, HR profesyonelleri için kritik. Konuşarak Öğren'le, bu alandaki yetkinliğinizi artırabilirsiniz. Detaylar için bağlantıda kalalım!</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Serpil Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: HR Ekibiniz İçin İngilizce Konuşma Desteği
+Merhaba Serpil Hanım,
+Şirketinizin uluslararası iletişimdeki başarıları için İngilizce konuşma pratiğinin önemini biliyoruz. Konuşarak Öğren, kurumsal ekiplere online İngilizce konuşma pratiği sunarak, global toplantılarda daha fazla özgüven ve etkili iletişim sağlamanıza yardımcı olabilir. Takım dinamiklerinizi güçlendirirken, gelişim takibi ve raporlama ile sürecinizi de destekliyoruz.
+Detayları paylaşmak için bir görüşme ayarlamayı çok isterim.
+Sevgiler,
+[Adınız]  
+[Pozisyonunuz]  
+[Şirketiniz]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Serpil'in HR profesyoneli olarak global toplantılarda konuşma güveni ve etkili iletişim konusundaki ihtiyacı</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3185,54 +3252,59 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>likely mid to senior level</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>improving speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, likely focused on employee development and training</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>58</v>
+          <t>enhancing employee communication skills and readiness for international collaboration</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Merhaba Ayten Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ayten, Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yaparak global toplantılara daha hazır hale gelmelerine yardımcı olabiliriz. İlgilendiğiniz bir konu mu? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ayten Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Yetkinliğini Artırın
+Merhaba Ayten Hanım,
+Şirketinizdeki çalışanların İngilizce konuşma güvenini artırmak ve uluslararası işbirliklerine daha hazır hale gelmelerini sağlamak için size yardımcı olabileceğimizi düşünüyorum. Konuşarak Öğren, online platformumuzla kurumsal ekiplerinize özel konuşma pratiği ve gelişim takibi sunuyor. 
+Detayları paylaşmak isterim.
+İyi çalışmalar dilerim,
+[Adınız] 
+[Pozisyonunuz] 
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ayten Hanım'ın HR pozisyonu ve çalışanların konuşma güvenliğini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3275,54 +3347,57 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Speaking confidence and global meeting readiness for employees</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for English speaking practice in corporate teams</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>58</v>
+          <t>Enhancing employee communication skills and confidence in English through online practice</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Merhaba Sinem Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sinem, İngilizce iletişim becerilerini geliştirmek ve çalışanların global toplantılara hazırlıklarını artırmak için online pratik sunuyoruz. Bu konuda daha fazla bilgi almak istersen, sevinirim! İyi çalışmalar dilerim.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sinem Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirme
+Merhaba Sinem,
+Kurumsal ekibinizin İngilizce konuşma pratiği ve global toplantılara hazırlık konusunda zorluklar yaşadığını biliyorum. Konuşarak Öğren olarak, online platformumuzda çalışanlarınıza kişiselleştirilmiş İngilizce pratik imkanı sunuyoruz. Gelişim takibi ve raporlama ile bu süreci daha etkili kılabiliriz. 
+Detayları paylaşmak ve size nasıl yardımcı olabileceğimizi konuşmak için bir görüşme ayarlamak ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sinem'in HR profesyoneli olarak çalışanların İngilizce konuşma becerilerine ve global toplantılara hazırlık konusundaki ihtiyaçlarına odaklanıldı.</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3365,54 +3440,57 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>Human Resources / People Management</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employee communication and confidence in English during meetings</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, improving English speaking skills is likely essential for global collaboration</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>58</v>
+          <t>Offering tailored online English speaking practice to boost team confidence and meeting readiness</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Merhaba Inci Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba İnci, HR profesyonellerine yönelik sunduğumuz online İngilizce konuşma pratiği ile ekiplerinizi toplantılarda daha özgüvenli hale getirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Inci Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Geliştirin
+Merhaba İnci,
+Şirketinizdeki HR süreçlerini güçlendirmek için, ekip üyelerinizin İngilizce iletişim becerilerini artırmaya yönelik özel online konuşma pratiği sunuyoruz. Bu program, çalışanlarınızın toplantılarda daha özgüvenli olmalarına ve etkin bir şekilde iletişim kurmalarına yardımcı olabilir. 
+Detayları konuşmak isterseniz, size yardımcı olmaktan memnuniyet duyarım.
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>İnci'nin HR profesyoneli olarak ekip iletişimini güçlendirme ihtiyacı ve toplantılarda İngilizceye olan ilgisi.</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3455,54 +3533,56 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in talent development and communication skills training</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>50</v>
+          <t>Offering solutions to enhance employee communication skills and confidence in English for better global collaboration</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Merhaba Sevgi Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sevgi, kurumsal ekiplerin İngilizce konuşma pratiğiyle gelişimlerini destekleyen Konuşarak Öğren'i paylaşmak istedim. Çalışanlarınızın global toplantılarda daha özgüvenli olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sevgi Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Sevgi Hanım,
+Şirketinizdeki çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlıklarını güçlendirmek adına Konuşarak Öğren olarak destek sunmak istiyoruz. Online İngilizce pratik imkanı ile gelişim takibi yaparak, ekibinizin iletişim becerilerini güçlendirebiliriz. Bu konuda bir sohbet etmek ister misiniz?
+İyi çalışmalar,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sevgi Kamilçelebi'nin HR profesyoneli olarak, çalışanların konuşma güvenini geliştirme ihtiyacı üzerine odaklanılması.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3545,54 +3625,58 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Ekiplerin İngilizce konuşma becerilerinde eksiklik ve global toplantılara hazırlık</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyonellerinin global iş ortamında etkili iletişim kurma ihtiyacı</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>58</v>
+          <t>Online İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmak ve global toplantılara hazırlık sağlamak</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Merhaba Özgen Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Özgen, ekiplerin global toplantılara hazırlık sürecinde İngilizce konuşma becerilerini geliştirmek için nasıl bir yol izlediğinizi merak ettim. Konuşarak Öğren ile çalışanlarınızın kendine güvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Özgen Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin Global Başarıları İçin İngilizce Pratiği
+Merhaba Özgen,
+Şirketinizdeki ekiplerin global toplantılara daha iyi hazırlanmaları için etkili bir yol arayışında olduğunuzu duydum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın kendine güvenini artırabiliriz. 
+Bu süreç, ekip üyelerinizin iletişim becerilerini geliştirmelerine ve uluslararası iş ortamında daha etkili olmalarına yardımcı olacaktır. Detayları konuşmak için bir zaman ayıralım mı?
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ekiplerin İngilizce konuşma becerilerinde eksiklik ve global toplantılara hazırlık ihtiyacı</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3635,54 +3719,56 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Estimate: Mid to Senior level</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in talent development and training initiatives</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>58</v>
+          <t>Enhancing communication skills within teams to support global collaboration</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Merhaba Müzeyyen Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Müzeyyen, HR alanındaki deneyiminizle global iş ortamında etkili iletişimin önemini bildiğinizi düşünüyorum. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için bir çözüm sunuyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Müzeyyen Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Müzeyyen,
+Kurumsal ekiplerde çalışanların İngilizce konuşma becerilerini geliştirmek, global işbirliğini artırabilir. Konuşarak Öğren olarak, çevrimiçi platformda personelinizin konuşma pratiği yapmasını sağlıyoruz. Bu süreç, gelişim takibi ve raporlama ile destekleniyor. Ekibinizin güvenle global toplantılara katılmasına yardımcı olmak için bir görüşme ayarlamak ister misiniz?
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Müzeyyen'in HR alanındaki tecrübesi ve çalışanların konuşma güvenini artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3725,54 +3811,56 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional (to verify)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında çalışanların İngilizce iletişim becerilerinin artırılması.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR departmanlarında çalışanların konuşma pratiğine ihtiyaç duyduğuna dair bir sinyal.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerde konuşma güvenini artırmak ve global toplantılara hazırlıkları desteklemek.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Merhaba Şule Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Şule, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirme üzerine çalıştığınızı biliyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha iyi hazırlanmasını sağlamak için bir çözüm sunuyoruz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Şule Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce İletişim Becerilerini Geliştirin
+Merhaba Şule,
+Gelişen global iş ortamında, çalışanlarınızın İngilizce iletişim becerilerini artırmak adına etkili bir çözüm arayışında olduğunuzu biliyorum. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği, gelişim takibi ve raporlama hizmeti sunuyor. Ekibinizin global toplantılara daha iyi hazırlanmalarına destek olmak ve konuşma güvenlerini artırmak için birlikte çalışabiliriz. Detayları görüşmek ister misiniz?
+Sevgiler,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Şule'nin HR alanındaki uzmanlığı ve çalışanların İngilizce iletişim becerilerini geliştirme ihtiyacına vurgu yapıldı.</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3815,54 +3903,56 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employees may need enhanced speaking confidence and global meeting readiness.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, Zeynep is likely focused on employee development, making English speaking skills relevant.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>50</v>
+          <t>Highlight the importance of effective communication in global teams and how online speaking practice can address this need.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Merhaba Zeynep Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Zeynep, çalışanların global toplantılarda daha etkili iletişim kurabilmesi için online İngilizce konuşma pratiği sunuyoruz. Ekibinizin kendine güvenini artırmak ve iletişim becerilerini geliştirmek için birlikte çalışabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Zeynep Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global İletişim Becerilerini Geliştirin
+Merhaba Zeynep,
+Kurumsal ekibinizin global toplantılarda daha etkili olabilmesi için iletişim becerilerini geliştirmek önemlidir. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Çalışanlarınızın kendine güvenini artırarak, global iş dünyasında daha hazır hale gelmelerine yardımcı olabiliriz. İlgilenirseniz, detayları paylaşmak isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Zeynep'in HR profesyoneli olarak çalışan gelişimine odaklanması ve global toplantılarda etkili iletişimin önemine olan ilgisi.</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3905,54 +3995,58 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving communication skills and confidence in English among team members</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in global meetings and training, indicating a need for English speaking practice</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of online English conversation practice for enhancing team communication and readiness for global interactions</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Merhaba Bahar Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Bahar, ekibinizin İngilizce iletişim becerilerini geliştirmek için online konuşma pratiği sunuyoruz. Küresel etkileşimlerde daha özgüvenli bir iletişim için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Bahar Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce İletişim Becerilerinizi Geliştirin
+Merhaba Bahar,
+Şirketinizdeki ekip üyelerinin İngilizce iletişim becerilerini geliştirmek ve global etkileşimlerde daha etkili olmalarına yardımcı olmak için online İngilizce konuşma pratiği sunuyoruz. Gelişim takibi ve raporlama ile süreçlerinizi kolaylaştırıyoruz. Ekiplerinizin daha özgüvenli olmasını sağlayacak çözümlerimiz hakkında daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
+İyi çalışmalar,
+[Adınız]
+[Pozisyonunuz]
+[Şirketiniz]</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Bahar'ın HR profesyoneli olarak ekip üyelerinin İngilizce iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3995,54 +4089,59 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Working in an HR role likely involves communication with diverse teams, indicating a need for English speaking practice</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>58</v>
+          <t>Emphasize how online English conversation practice can enhance team collaboration and global engagement</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Merhaba Cagri Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Çağrı, HR alanındaki deneyiminizle ekibinizin İngilizce konuşma pratiğini geliştirmeye yönelik ilginizi keşfettim. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha hazır hale gelmesine yardımcı olabileceğimizi düşünüyorum. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Cagri Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba,
+Şirketinizin global iletişim becerilerini artırmak üzere çalışanlarınızın İngilizce konuşma pratiğine ihtiyaç duyduğunu düşünüyorum. Konuşarak Öğren olarak, online platformumuzda sunmuş olduğumuz pratik ve gelişim takibi ile ekip üyelerinizin özgüven kazanmasına ve etkili bir şekilde global toplantılara hazırlanmalarına katkı sağlayabiliriz.
+Detayları görüşmek için uygun bir zaman ayarlayabilir miyiz?
+Saygılarımla,
+[Adınız]  
+[Unvanınız]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli olarak çalışanlarının İngilizce konuşma becerilerini geliştirmek istemesi ve global toplantılara daha iyi hazırlanmaları konusunda yaşadıkları zorluklar.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4085,54 +4184,59 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Speaking confidence and global meeting readiness within corporate teams</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for English speaking practice in HR context</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>58</v>
+          <t>Enhancing employee communication skills and readiness for global interactions</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Merhaba Ilker Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba İlker, HR alanında çalışan biri olarak, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmeleri konusunda önemli bir rol oynadığınızı biliyorum. Konuşarak Öğren ile bu becerileri güçlendirmek ve global toplantılara hazırlık sağlamak üzerine bir görüşme yapmayı ister misiniz?</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ilker Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Kurumsal Ekipler İçin İngilizce Pratiği
+Merhaba İlker,
+Umarım iyisinizdir. Şirketinizdeki ekiplerin global toplantılara daha iyi hazırlanmaları ve İngilizce konuşma konusundaki güvenlerini artırmaları için online pratik fırsatları sunuyoruz. Konuşarak Öğren ile, ekip üyelerinizin iletişim becerilerini geliştirmek ve gelişimlerini raporlamak mümkün. Sizinle bu konuda bir görüşme yapmayı çok isterim.
+İyi günler dilerim,
+[Adınız]  
+[Pozisyonunuz]  
+[Şirket Adı]  
+[İletişim Bilgileri]</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli ve İngilizce konuşma pratiği ihtiyacı</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4175,54 +4279,56 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in communication training and development for employees</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>50</v>
+          <t>Offering solutions to improve employee communication skills and readiness for international collaboration</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Merhaba Gökçe Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Gökçe, HR alanında çalışan bir profesyonel olarak, çalışanların İngilizce konuşma becerilerini geliştirmelerine nasıl katkıda bulunduğunuzu merak ediyorum. Konuşarak Öğren ile bu konuda destek olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Gökçe Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Gökçe,
+Kurumsal ekibinizin İngilizce konuşma pratiği yaparak global toplantılara daha hazır hale gelmesine nasıl katkıda bulunabileceğimizi konuşmak isterim. Konuşarak Öğren, çalışanlarınızın iletişim becerilerini geliştirmelerine ve güvenle konuşmalarına yardımcı oluyor. Eğitim süreçlerinize entegre edebileceğimiz çözümler sunuyoruz. İlgilenirseniz, detayları görüşmek için bir zaman ayarlayalım.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Gökçe'nin HR profesyoneli olarak çalışanların İngilizce konuşma güvenini artırma ve uluslararası toplantılara hazırlık konusundaki ihtiyacını hedef alarak iletimi özelleştirdim.</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4265,54 +4371,56 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>likely mid to senior level</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, likely interested in improving employees' English speaking skills</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>58</v>
+          <t>highlighting how Konuşarak Öğren can enhance communication skills and support employee development</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Merhaba Ilker Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba İlker Bey, iletişim becerileri geliştirmek, çalışanlarınızın global toplantılara hazırlığını artırmak için Konuşarak Öğren olarak destek olabileceğimizi düşünüyorum. Daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ilker Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba İlker Bey,
+Şirketinizdeki çalışanların İngilizce konuşma becerilerini geliştirmek ve global toplantılara hazırlıklarını artırmak adına Konuşarak Öğren olarak size yardımcı olabiliriz. Online platformumuzla, çalışanlarınızın iletişim yeteneklerini güçlendirirken gelişim takibi ve raporlama sunuyoruz. Daha fazla bilgi almak isterseniz, sizinle görüşmekten memnuniyet duyarım.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>İlker Bey'in HR profesyoneli olarak çalışanlarının İngilizce konuşma becerilerini geliştirmeye yönelik ilgisi ve ihtiyaçları</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4355,54 +4463,57 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level to senior-level</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employee communication skills and global collaboration readiness</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in global teams or communications</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>58</v>
+          <t>Offering online English speaking practice to improve team confidence and readiness for international meetings</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Merhaba Lale Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Lale, İngilizce iletişim becerilerini güçlendirmek ve ekiplerinizi uluslararası toplantalara hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim. Görüşmek üzere!</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Lale Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Güçlendirin
+Merhaba Lale Hanım,
+Kurumsal ekiplerin global iş birliğini güçlendirmek için İngilizce konuşma pratiği sunuyoruz. Ekibinizin güvenle iletişim kurmasını ve uluslararası toplantılara daha iyi hazırlanmasını sağlamak amacıyla online seanslar sunuyoruz. Gelişim takibi ve raporlama ile süreçlerinizi destekleyebiliriz. 
+Detayları görüşmek isterseniz, memnuniyetle yardımcı olurum.
+İyi çalışmalar dilerim,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Lale'nin HR profesyoneli olması ve çalışanların iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4445,54 +4556,57 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level (estimate)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication and confidence in English during global meetings</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training programs</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>58</v>
+          <t>Highlight the importance of effective communication skills in a global workplace and how Konuşarak Öğren can enhance team confidence and readiness</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Merhaba Gizem Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Gizem, global toplantılarda etkili iletişimin ne kadar önemli olduğunu biliyoruz. Ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazanmasına yardımcı olabiliriz. Daha fazla bilgi almak isterseniz, memnuniyetle konuşalım!</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Gizem Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İletişim Becerilerinizi Geliştirin
+Merhaba Gizem,
+Global toplantılarda etkili iletişim, ekiplerin başarısını doğrudan etkiler. Konuşarak Öğren olarak, şirketinizin İngilizce konuşma pratiği yaparak çalışanlarınızın kendine güven kazanmasına yardımcı olabiliriz. Ekip üyelerinin gelişimini takip edebilir ve raporlayabiliriz. Bu konuyu daha detaylı konuşmak için bir görüşme ayarlamayı ister misiniz?
+Saygılarımla,
+[Adınız]
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Gizem'in HR profesyoneli olması ve global toplantılarda İngilizce iletişim konusundaki sıkıntıları.</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4535,54 +4649,59 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee confidence in English speaking and global meeting readiness.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely responsible for employee development and training.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>50</v>
+          <t>Highlight how our platform can enhance speaking confidence and improve global communication within teams.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Merhaba Arzu Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Arzu Hanım, İngilizce konuşma pratiği üzerine sunduğumuz platformun, ekiplerinizin global toplantılara daha hazırlıklı olmasına yardımcı olabileceğini düşünüyorum. Bu konuda daha fazla bilgi almak isterseniz, memnuniyetle paylaşırım. Sevgiler!</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Arzu Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizi Global İletişime Hazırlayın
+Merhaba Arzu Hanım,
+Kurumsal ekiplerin global iletişimde daha etkili olmaları için İngilizce konuşma pratiği sunan Konuşarak Öğren ile tanışmanızı isterim. Platformumuz, çalışanların konuşma güvenini artırarak global toplantılara daha iyi hazırlanmalarını sağlıyor. Bu süreçte sizinle iş birliği yaparak, ekiplerinizin gelişimini desteklemek harika olur. 
+İlginizi çekerse, detayları paylaşmak isterim.
+Sevgiler,
+[Adınız]  
+[Pozisyonunuz]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Arzu Hanım'ın HR profesyoneli olması ve çalışanların İngilizce konuşma güveni ile global toplantılara hazırlığına yönelik ihtiyaçları.</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4625,54 +4744,56 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication in English and global meeting readiness</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR professionals often require effective communication skills in English for international collaboration</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>58</v>
+          <t>Highlight the importance of speaking confidence in global HR roles and how online practice can enhance team readiness</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Merhaba Şahika Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Şahika, global HR rollerinde iletişim becerilerinin önemini biliyorum. Konuşarak Öğren ile online İngilizce pratiği yaparak ekibinizin global toplantılara daha hazır olmasını sağlayabilirsiniz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Şahika Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global HR İletişim Becerilerinizi Geliştirin
+Merhaba Şahika,
+Şirketinizdeki HR profesyonellerinin İngilizce iletişim becerilerini geliştirmek, uluslararası işbirliklerinde başarıyı artırabilir. Konuşarak Öğren, kurumsal ekiplerinize online konuşma pratiği sunarak, global toplantılara daha hazır olmalarını sağlıyor. Ekibinizin bu fırsattan nasıl faydalanabileceğini konuşmak ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyonellerinin global toplantılara hazırlık ihtiyacı ve iletişim becerilerinin önemine vurgu</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4715,54 +4836,60 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level or Senior (estimate based on title)</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Lack of effective communication in global meetings and need for improving team members' speaking confidence</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, Ezgi may be focused on developing employees' language skills for better performance</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>58</v>
+          <t>Highlight how Konuşarak Öğren can enhance speaking confidence and meeting readiness for HR professionals and their teams</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Merhaba Ezgi Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ezgi, Konuşarak Öğren ile ekiplerinizi küresel toplantılara daha hazır hale getirebilirsiniz. İngilizce konuşma pratiği ile iletişim becerilerini geliştirmek ve güven artırmak için bir görüşme ayarlamak ister misiniz?</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ezgi Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Ezgi,
+Kurumsal ekibinizin global toplantılardaki iletişimini geliştirmek için etkili bir çözüm arıyorsanız, Konuşarak Öğren tam size göre. Online İngilizce konuşma pratiği ile ekip üyelerinizin konuşma güvenini artırabilir ve toplantılara daha iyi hazırlanmış olmalarını sağlayabilirsiniz. 
+Eğitim programlarımız hakkında daha fazla bilgi almak isterseniz, size yardımcı olmaktan memnuniyet duyarım.
+Saygılarımla,
+[Adınız]  
+[Pozisyonunuz]  
+[Şirketiniz]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ezgi'nin HR profesyoneli olarak küresel toplantılarda etkili iletişim kurma ve ekip üyelerinin konuşma güvenini artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4805,54 +4932,56 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Speaking confidence and global meeting readiness for employees</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, Onur may be focused on enhancing communication skills within the organization.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>58</v>
+          <t>Highlight the importance of English speaking confidence in global business environments and how Konuşarak Öğren can help teams improve their skills.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Merhaba Onur Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Onur, İngilizce konuşma becerileri global iş dünyasında büyük önem taşıyor. Konuşarak Öğren, ekiplerinize çevrimiçi pratik yapma imkanı sunarak güvenlerini artırmalarına yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Onur Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Onur,
+Kurumsal ekipler için İngilizce konuşma pratiği sağlamak, global iş ortamlarında iletişim becerilerini güçlendirmenin anahtarı. Konuşarak Öğren olarak, çalışanlarınızın konuşma güvenini artırmalarına ve uluslararası toplantılara hazırlanmalarına yardımcı oluyoruz. Ekiplerinize özel programlarımızla gelişim takibi ve raporlama sunuyoruz. Detayları paylaşmak için bir görüşme ayarlayabilir miyiz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Onur'un HR profesyoneli olması ve konuşma güvenliği ile global toplantılara hazırlık konusundaki ihtiyacı</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4895,54 +5024,57 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication and global meeting readiness</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for English speaking practice for team members</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>50</v>
+          <t>Enhancing speaking confidence and improving global meeting performance for HR teams</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Merhaba Serdal Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Serdal, HR ekiplerinin iletişim becerilerini geliştirmesine yardımcı olan etkili bir çözüm sunuyoruz. Küresel toplantılarda daha fazla özgüven ve etkili iletişim için konuşma pratiği yapmayı düşünür müsünüz? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Serdal Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Küresel Toplantılarda Başarı İçin Konuşma Pratiği
+Merhaba Serdal,
+Kurumsal ekibinizin global toplantılarda daha etkili iletişim kurabilmesi için bir çözüm sunmak istiyorum. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği ve gelişim takibi sunarak, kendilerine olan güvenlerini artırmalarını sağlıyor. Bu sayede, ekibinizin uluslararası platformlarda daha başarılı olmasını hedefliyoruz.
+Detayları görüşmek isterseniz, sevinirim.
+İyi çalışmalar,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Serdal Akkaya'nın HR profesyoneli olarak ekip içi iletişim ve küresel toplantılardaki performansı artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4985,54 +5117,57 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Speaking confidence in global meetings</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee training and development, which may include language skills.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>58</v>
+          <t>Enhancing employee communication skills for better global collaboration.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Merhaba Türkan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Türkan, HR profesyonelleri için global toplantılarda etkili iletişim önemli. Konuşarak Öğren ile ekiplerinizin İngilizce konuşma pratiğini destekleyerek bu alanda güven kazanmalarına yardımcı olabiliriz. Detayları paylaşmayı çok isterim.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Türkan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Türkan, 
+Ekiplerinizin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma becerilerini geliştirmek önemli. Konuşarak Öğren, çalışanlarınızın konuşma pratiği yapmasını ve gelişimlerini takip etmesini sağlıyor. Eğlenceli ve etkileşimli bir ortamda, ekibinizin kendine güvenini artırmak için nasıl bir yol izleyebileceğimizi konuşmak isterim.
+İlgilenirseniz, bir görüşme ayarlayalım. 
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Türkan Aslancan'ın HR profesyoneli olması ve global toplantılarda konuşma güvenliği ihtiyacı.</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5075,54 +5210,56 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee speaking confidence and readiness for global meetings</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely focused on employee development and communication skills</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of online English speaking practice for enhancing team collaboration and confidence</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Merhaba Ezgi Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ezgi, İngilizce konuşma pratiği ile ekiplerinizi global toplantılara daha hazır hale getirmek için birlikte çalışabileceğimizi düşünüyorum. Konuşarak Öğren ile çalışanlarımızın özgüvenini artırabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ezgi Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Ezgi Hanım,
+Ekip üyelerinizin global toplantılara daha özgüvenli katılmalarını sağlamak için online İngilizce konuşma pratiği sunuyoruz. Konuşarak Öğren ile, ekip içi iletişimi güçlendirirken gelişim takibi ve raporlama hizmetimizle ilerlemelerini de takip edebilirsiniz. Bu süreci birlikte nasıl daha verimli hale getirebileceğimizi konuşmak ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ezgi Eker'in HR profesyoneli olarak çalışanların konuşma özgüvenini artırma ihtiyacına yönelik bir çözüm sunulması.</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5165,54 +5302,58 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Kurumsal ekiplerde speaking confidence eksikliği ve global meeting readiness ihtiyacı</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Duygu Aras'ın HR pozisyonu gereği, çalışanların İngilizce iletişim becerilerini geliştirmeye yönelik bir ihtiyaç olabilir.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerin İngilizce konuşma becerilerini geliştirmek ve global toplantılara hazırlık sağlamak</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Merhaba Duygu Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Duygu, LinkedIn profilinizdeki HR deneyiminizi inceledim. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için sizinle bağlantı kurmak istedim. Global toplantılara hazırlık sağlamak, çalışanlarınızın güvenini artırabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Duygu Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Kurumsal Ekiplerin İngilizce Becerilerini Geliştirmek
+Merhaba Duygu Hanım,
+HR alanındaki deneyiminizle, ekiplerinizin İngilizce konuşma becerilerini geliştirme ihtiyacını anlayışla karşılıyorum. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği sunarak global toplantılara daha iyi hazırlanmalarını sağlıyor. Bu konuda sizinle detaylı bir görüşme yapmayı çok isterim.
+İlginiz için teşekkürler,
+[İsminiz]
+[Pozisyonunuz]
+[Şirketiniz]</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Duygu Aras'ın HR pozisyonu ve kurumsal ekiplerdeki speaking confidence eksikliği</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5255,54 +5396,56 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee communication skills and global meeting readiness</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in global teams or collaboration requiring English proficiency</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>50</v>
+          <t>Highlight the importance of speaking confidence and communication skills in HR and team dynamics</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Merhaba Izel Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Izel, HR alanındaki deneyiminizle, ekipler arası iletişimi güçlendirmenin önemini biliyorsunuz. Konuşarak Öğren ile online İngilizce pratiği yaparak, ekiplerinizin küresel toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Izel Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Takım İletişimini Güçlendirin
+Merhaba Izel,
+HR alanındaki deneyiminizle, çalışanların iletişim becerilerinin artmasının ekip dinamiklerine katkısını biliyorsunuzdur. Konuşarak Öğren, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, global toplantılara hazırlık ve gelişim takibi yapmanızı sağlıyor. Ekibinizin kendine güvenle iletişim kurabilmesi için nasıl bir destek sunabileceğimizi konuşmak ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR alanındaki deneyimi ve ekip iletişimini güçlendirme isteği</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5345,54 +5488,57 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında çalışanların İngilizce konuşma becerilerinin artırılması</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Online İngilizce konuşma pratiği ihtiyacı</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerin speaking confidence ve global meeting readiness alanlarında gelişim sağlamalarına yardımcı olma</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Merhaba Yasemin Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Yasemin, gelişen global iş ortamında çalışanların İngilizce konuşma becerilerini artırmanın öneminin farkındayım. Konuşarak Öğren olarak, kurumsal ekiplerin speaking confidence ve global meeting readiness alanlarında gelişim sağlamalarına yardımcı olabiliyoruz. Görüşmek ister misin?</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Yasemin Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce Konuşma Pratiği ile Ekibinizi Güçlendirin
+Merhaba Yasemin,
+Kurumsal ekipler için İngilizce konuşma pratiği sağlamak, gelişen global iş ortamında önemli bir ihtiyaç haline geldi. Konuşarak Öğren olarak, ekiplerinizin speaking confidence ve global meeting readiness alanlarında gelişim göstermelerine yardımcı oluyoruz.
+Eğer şirketinizin bu alanda destek alabileceği bir çözüm arayışı varsa, sizinle bu konuyu daha detaylı konuşmak isterim. Uygun olduğunuz bir zaman diliminde görüşebilir miyiz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Yasemin'in HR profesyoneli olması ve global iş ortamında çalışanların İngilizce konuşma becerilerini artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5435,54 +5581,56 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication skills and global meeting readiness</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely focused on improving employee skills in a corporate setting</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>58</v>
+          <t>Offering a solution to enhance speaking confidence and development tracking for employees</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Merhaba Recep Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Recep Bey, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmek için sunmuş olduğunuz yöntemlerle ilgili konuşmak isterim. Çalışanlarınızın iletişim becerilerini artırmak, global toplantılara hazırlıklarını güçlendirmek için çözümlerimiz var. İlgilenirseniz detayları paylaşabilirim.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Recep Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İletişim Becerilerini Geliştirin
+Merhaba Recep Bey,
+Şirketinizdeki çalışanların iletişim becerilerini geliştirmek ve global toplantılara daha iyi hazırlanmalarını sağlamak için etkili bir çözüm sunuyoruz. Konuşarak Öğren, kurumsal ekiplere online İngilizce konuşma pratiği, gelişim takibi ve raporlama imkanı sunarak çalışanlarınızın kendine güvenini artırmayı hedefliyor. İlgilenirseniz size detayları iletebilirim.
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Recep Bey'in HR profesyoneli olarak çalışanların iletişim becerilerinin geliştirilmesine olan ilgisi ve global toplantılara hazırlık konusundaki ihtiyaçları.</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -5525,54 +5673,57 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Kurumsal ekiplerde İngilizce iletişimde güven eksikliği</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İngilizce konuşma pratiği ihtiyacı</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>58</v>
+          <t>Ekiplerin global toplantılara hazırlık düzeyini artırmak için online konuşma pratiği sunma</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Merhaba Orhan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Orhan, İngilizce iletişimde güven eksikliği, global toplantılara hazırlık açısından büyük bir engel olabilir. Kurumsal ekipler için online konuşma pratiği sunuyoruz. Bu konuda bir konuşma ayarlamak ister misiniz?</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Orhan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global Toplantılara Hazırlık İçin İngilizce Pratiği
+Merhaba Orhan Çelebi,
+Umarım bu mesajım sizi iyi bulur. Şirketinizdeki ekiplerin İngilizce iletişiminde yaşadığı güven eksikliği, global toplantılarda zorlanmalara neden olabilir. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunarak bu sorunu aşmalarına yardımcı olabiliriz. Gelişim takibi ve raporlama ile desteklenen programlarımız, ekiplerinizin kendine güvenini artırmalarını sağlayacaktır. 
+Daha fazla bilgi almak veya bir toplantı ayarlamak isterseniz, lütfen benimle iletişime geçin.
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Orhan Çelebi'nin HR profesyoneli olması ve kurumsal ekiplerde İngilizce iletişimde güven eksikliği yaşanmasının, global toplantılara hazırlık düzeyini etkileyebileceği.</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -5615,54 +5766,57 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to verify, likely mid to senior level</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>employees may lack speaking confidence in English during global meetings</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>potential need for improving English speaking skills for better meeting readiness</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>50</v>
+          <t>offer solutions for enhancing English speaking confidence and development tracking for HR teams</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Merhaba H Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba H Özdemir, global toplantılarda çalışanlarınızın İngilizce konuşma güvenini artırmak için neler yaptığınızı merak ediyorum. Konuşarak Öğren, online pratik ve gelişim takibi ile bu konuda destek olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba H Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce Konuşma Güvenini Artırma Çözümleri
+Merhaba,
+Şirketinizdeki çalışanların global toplantılarda daha fazla özgüvenle İngilizce konuşmalarını sağlamak için bir çözüm arayışında olabileceğinizi düşünüyorum. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği sunarak, gelişim takibi ve raporlama imkanı sağlar. Bu sayede, hem bireysel gelişim hem de ekip performansı artırılabilir.
+Detayları paylaşmak için bir görüşme ayarlamak ister misiniz? 
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Çalışanların global toplantılarda İngilizce konuşma güvenini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5705,54 +5859,57 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>likely mid to senior level</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>improving employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, likely involved in talent development and employee training</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>58</v>
+          <t>offering solutions that enhance communication skills and readiness for international collaboration</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Merhaba Funda Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Funda Hanım, Kurumsal ekiplerdeki İngilizce iletişim becerilerini geliştirme konusundaki çalışmalarınızı duyduğuma sevindim. Konuşarak Öğren olarak, ekiplerinizin global toplantılara daha hazır hale gelmesi için pratik çözümler sunuyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Funda Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Funda Hanım,
+Kurumsal ekibinizin uluslararası toplantılara katılımında daha fazla özgüven ve hazırlık sağlamak, çalışanlarınız için kritik bir adım. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ile gelişim takibi ve raporlama sunarak bu ihtiyacı karşılamayı hedefliyoruz. Sizlere özel çözümlerimiz hakkında bilgi almak isterseniz, görüşmeyi çok isterim.
+Saygılarımla,
+[Adınız]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Funda Kaval'ın HR alanındaki uzmanlığı ve çalışanların iletişim becerilerini geliştirme konusundaki ihtiyacı.</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5795,54 +5952,59 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for English language training to enhance communication skills in a corporate setting</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>58</v>
+          <t>Offering solutions for improving employees' speaking confidence and preparing them for global meetings through online practice</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Merhaba Derya Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Derya, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmak ve global toplantılara hazırlık konusunda destek olabileceğimizi düşünmüştüm. Konuşarak Öğren'i keşfetmek isterseniz, memnuniyetle paylaşırım. İyi çalışmalar dilerim!</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Derya Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Derya,
+Şirketinizdeki çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlık süreçlerini desteklemek için online pratik imkanı sunuyoruz. Konuşarak Öğren, gelişim takibi ve raporlama ile süreci daha etkili hale getiriyor. 
+İlgilenirseniz, detayları paylaşmaktan memnuniyet duyarım.
+İyi çalışmalar,
+[Adınız]  
+[Pozisyonunuz]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Derya'nın çalışanların konuşma güvenini geliştirme ihtiyacı ve global toplantılar için hazırlık konusundaki ilgisi.</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5885,54 +6047,56 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>to be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to verify</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliği</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>İnsan Kaynakları alanında çalışan bir profesyonel olarak, global toplantılarda etkin iletişim için İngilizce konuşma becerileri geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness konularında destek sunarak, çalışanların gelişim takibi yapma yeteneğini artırma</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Merhaba Özge Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Özge, kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliğini gidermeye yönelik çözümler sunuyoruz. Çalışanlarınızın global toplantılara daha hazır hale gelmesi için birlikte çalışmayı çok isterim. Detayları konuşalım mı?</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Özge Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Özge,
+Umarım iyisinizdir! Kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliği, global toplantılarda etkili iletişim için önemli bir engel oluşturabiliyor. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunarak, bu konuda gelişimlerini takip etmenize yardımcı olabiliriz. Çalışanlarınızın speaking confidence’ını artırarak, global toplantılara daha hazır olmalarını sağlamak için bir araya gelmeyi çok isterim.
+Görüşmek dileğiyle,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliği ile ilgili ihtiyaçları</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5975,54 +6139,56 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence among employees for global communication</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR professionals often seek ways to enhance language skills for effective team collaboration</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>50</v>
+          <t>Highlighting how Konuşarak Öğren can improve speaking confidence and meeting readiness for HR teams</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Merhaba Melike Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Melike, HR alanında çalışan bir profesyonel olarak, kurumsal ekiplerin İngilizce konuşma pratiğini geliştirmesi konusunda nasıl destek sağlayabileceğimizi konuşmak isterim. Konuşarak Öğren ile çalışanlarınızın güvenle konuşmasını sağlamak mümkün. Görüşmek dileğiyle!</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Melike Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce Konuşma Pratiği ile Güçlü Ekipler Yaratın
+Merhaba Melike,
+Kurumsal ekibinizin global iletişimde daha etkili olabilmesi için İngilizce konuşma pratiği sunan Konuşarak Öğren’i tanıtmak istiyorum. Çalışanlarınızın konuşma güvenini artırarak toplantılara daha hazır hale gelmelerini sağlayabiliriz. Detayları görüşmek ister misiniz?
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli olarak, çalışanların global iletişimde özgüven kazanmalarına yönelik ihtiyaçlarına atıfta bulundum.</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6065,54 +6231,57 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level to senior-level</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Increasing employee confidence in English speaking for global meetings</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Role in HR suggests a need for effective communication skills development</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>58</v>
+          <t>Enhance employee engagement and performance through online English speaking practice</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Merhaba Deniz Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Deniz, İngilizce konuşma pratiği ile çalışanların global toplantılardaki özgüvenini artırmanıza yardımcı olabiliriz. Kurumsal ekibinizin performansını artırmak için birlikte çalışmayı çok isteriz. Detayları konuşalım! Sevgiler, Konuşarak Öğren.</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Deniz Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Yetkinliğini Artırın
+Merhaba Deniz,
+HR alanındaki tecrübenizle, global toplantılarda çalışanların özgüvenini artırmanın önemini biliyorsunuzdur. Konuşarak Öğren olarak, kurumsal ekiplere yönelik online İngilizce konuşma pratiği sunuyoruz. Çalışanlarınızın iletişim becerilerini geliştirerek, hem katılımlarını hem de performanslarını artırabiliriz. Sizinle bu konuda detaylı bir görüşme yapmak isterim.
+Sevgiler,
+[Adınız]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Deniz Baygür'ün HR profesyoneli olması ve global toplantılarda çalışanların İngilizce konuşma özgüvenini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6155,54 +6324,59 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee communication and confidence in global meetings</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely interested in enhancing team members' English speaking skills</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>58</v>
+          <t>Offering tailored English speaking practice to boost speaking confidence and readiness for global meetings</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Merhaba Murat Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Murat, HR alanındaki deneyiminizle ekibinizin global toplantılardaki iletişimini güçlendirmek için bir çözüm sunmak istiyorum. Online İngilizce konuşma pratiği ile ekip üyelerinizin özgüvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Murat Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global Toplantılarda İletişim Gücünüzü Artırın
+Merhaba Murat,
+HR profesyoneli olarak, ekibinizin global toplantılarda etkili iletişim kurma yetkinliğini artırmak istediğinizi biliyorum. Konuşarak Öğren olarak, kurumsal ekipler için kişiselleştirilmiş online İngilizce konuşma pratiği sunuyoruz. Bu sayede çalışanlarınızın kendilerine olan güvenlerini artırarak, uluslararası ortamlarda daha etkili olmalarını sağlıyoruz.
+İlgilenirseniz, detayları konuşmak için bir görüşme ayarlayabiliriz.
+Saygılarımla,
+[Adınız] 
+[Pozisyonunuz] 
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Murat'ın HR alanındaki deneyimi ve global toplantılardaki iletişim sorununa odaklanarak, ekibinin İngilizce konuşma pratiği ihtiyacını vurgulamak.</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6245,54 +6419,57 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>employees lacking speaking confidence in English for global meetings</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Zeynep's role in HR suggests a focus on employee development and communication skills</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>58</v>
+          <t>presenting how Konuşarak Öğren can enhance speaking confidence and readiness for global interactions</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Merhaba Zeynep Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Zeynep, İngilizce konuşma pratiği ve gelişim takibi konusunda Konuşarak Öğren ile çalışan ekiplerin, global toplantılarda kendilerini daha güvende hissettiğini görüyoruz. İlgini çekerse, detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Zeynep Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Yetkinliğini Artırın
+Merhaba Zeynep,
+Şirketinizdeki çalışanların global toplantılarda daha fazla özgüvenle konuşmalarını sağlamak için Konuşarak Öğren olarak online İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Ekibinizin iletişim becerilerini geliştirmesi, uluslararası etkileşimlerde daha etkili olmalarına katkı sağlayacaktır. 
+Detayları paylaşmak için bir görüşme ayarlamak ister misin?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Zeynep'in HR profesyoneli olarak çalışan gelişimine odaklanması ve İngilizce konuşma becerilerinin arttırılması ihtiyacı.</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6335,54 +6512,57 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication challenges in English during global meetings</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in training and development; may require enhanced English speaking skills for effective communication.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>50</v>
+          <t>Emphasize how our platform can enhance speaking confidence and readiness for global meetings, aligning with HR development goals.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Merhaba Emre Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Emre, global toplantılarda İngilizce iletişim zorluklarının farkındayım. Konuşarak Öğren, ekip üyelerinizin konuşma özgüvenini artırarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim!</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Emre Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce İletişimde Güçlenin
+Merhaba Emre,
+Ekiplerinizin global toplantılarda etkili iletişim kurabilmesi için İngilizce konuşma pratiğine ihtiyaç duyduğunu düşünüyorum. Konuşarak Öğren, çalışanlarınızın konuşma özgüvenini artırarak bu zorlukları aşmalarına yardımcı olabilir. Online platformumuz sayesinde gelişim takibi ve raporlama da sağlıyoruz. 
+Detayları görüşmek ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Emre'nin HR profesyoneli olması ve global toplantılardaki İngilizce iletişim zorlukları</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -6425,54 +6605,59 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>employees may lack confidence in English speaking skills, impacting global communication</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, likely focused on employee development and training</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>58</v>
+          <t>offering solutions for enhancing speaking confidence and global meeting readiness</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Merhaba Enes Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Enes, İngilizce konuşma pratiği üzerine sunduğumuz çözümlerle çalışanların kendine güvenini artırarak global iletişimini güçlendirmeyi hedefliyoruz. Bu konuda daha fazla bilgi almak isterseniz, görüşmek isterim.</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Enes Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Yetkinliğini Artırın
+Merhaba,
+Şirketinizdeki çalışanların İngilizce konuşma becerilerini geliştirmek, global iletişimdeki güvenlerini artırmak için etkili bir yol aradığınızı biliyorum. Konuşarak Öğren olarak, online platformumuzda sunmuş olduğumuz İngilizce konuşma pratiği ile çalışanlarınızın kendine güvenini güçlendirebiliriz.
+Gelişim takibi ve raporlama ile birlikte, eğitim süreçlerinizdeki etkinliği artırmayı hedefliyoruz. Detayları konuşmak için uygun bir zaman ayarlayabilir miyiz?
+Saygılarımla,
+[Adınız]  
+[Telefon Numaranız]  
+[Email Adresiniz]</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Enes'in HR profesyoneli olarak çalışan gelişimi ve eğitim konusuna odaklanması, aynı zamanda global iletişimde İngilizce konuşma becerisinin önemine vurgu yapması.</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -6515,54 +6700,57 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional (to verify)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee development in English speaking skills and global meeting readiness</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As a HR professional, likely involved in employee training and development, could benefit from English speaking practice solutions</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>58</v>
+          <t>Highlight how online English speaking practice can enhance employee confidence and readiness for global engagements</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Merhaba Sadullah Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sadullah, İngilizce konuşma pratiği ile çalışanlarınızın global toplantılara hazırlığını artırabileceğinizi biliyor muydunuz? Konuşarak Öğren olarak bu konuda destek sunabiliriz. Detaylı bilgi için bağlantı kuralım!</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sadullah Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Sadullah,
+Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek ve global toplantılara daha iyi hazırlanmaları için etkili bir çözüm arıyorsanız, Konuşarak Öğren size yardımcı olabilir. Online platformumuz, çalışanlarınıza özgü gelişim takibi ve raporlama imkanı sunarak, kendilerine olan güvenlerini artırmalarını sağlıyor.
+Daha fazla bilgi almak isterseniz, size uygun bir zaman diliminde görüşmeyi çok isterim.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sadullah Albayrak'ın HR profesyoneli olması ve çalışan gelişimi üzerine odaklanması</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6605,54 +6793,57 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication challenges in English, need for global meeting readiness.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for improving employees' speaking confidence and English communication skills.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>58</v>
+          <t>Enhancing team members' speaking confidence and global meeting readiness through online English practice.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Merhaba Ikbal Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba İkbal Hanım, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, global toplantılara hazır olmalarını sağlamak için online pratik imkanı sunuyoruz. Ekibinizin iletişim becerilerini artırmak için nasıl bir destek sağlayabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ikbal Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Güçlendirin
+Merhaba, 
+Şirketinizdeki çalışanların İngilizce iletişim becerilerinde yaşadığı zorlukları anlıyorum. Konuşarak Öğren olarak, ekip üyelerinizin konuşma özgüvenini artırmak ve global toplantılara daha iyi hazırlanmalarını sağlamak için online İngilizce pratik imkanı sunuyoruz. Gelişim takibi ve raporlama ile desteklediğimiz bu süreç, çalışanlarınızın iletişim becerilerini hızla geliştirmesine yardımcı olabilir. 
+Detayları görüşmek isterseniz, size yardımcı olmaktan memnuniyet duyarım. 
+İyi günler, 
+[Adınız]</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>İkbal Akyol'un HR profesyoneli olarak İngilizce iletişim zorlukları yaşadığı ve global toplantılara hazırlık ihtiyacının olduğu bilgisi.</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6695,54 +6886,58 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Mid-level or Senior (estimate based on title)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Need for effective communication in English during global meetings and enhancing team members' speaking confidence</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training, indicating a need for English language improvement</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>50</v>
+          <t>Offering solutions for enhancing speaking confidence and global meeting readiness for employees, which aligns with HR development goals</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Merhaba Ahmet Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ahmet, global toplantılarda etkili iletişim ve ekip üyelerinin konuşma özgüvenini artırma ihtiyacınızı anlıyorum. Konuşarak Öğren ile İngilizce pratik yaparak bu hedeflere ulaşmanıza yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ahmet Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Ahmet,
+Şirketinizdeki ekiplerin global toplantılarda etkili iletişim kurabilmesi ve bireylerin konuşma özgüvenini artırabilmesi için online İngilizce pratik imkanı sunuyoruz. Konuşarak Öğren ile çalışanlarınızın İngilizce becerilerini geliştirmesine yardımcı olabiliriz. Bu, HR gelişim hedeflerinize katkıda bulunabilir. İlgilenirseniz, detayları konuşmak isterim.
+Saygılarımla,
+[Adınız]
+[Pozisyonunuz]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ahmet'in HR profesyoneli olarak global toplantılarda etkili iletişim ve ekip üyelerinin konuşma özgüvenini artırmaya yönelik ihtiyacı</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6785,54 +6980,57 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Estimate: Mid to Senior Level</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee communication skills for global meetings and collaboration</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Possibly needs support in enhancing English speaking confidence among employees</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>58</v>
+          <t>Highlighting the importance of speaking confidence and global meeting readiness for HR professionals</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Merhaba Gündem Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Gündem, HR profesyoneli olarak global toplantılardaki iletişim becerilerinin artırılması üzerine konuşmak isterim. Konuşarak Öğren, ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazandırmasına yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Gündem Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global Toplantılarda İletişim Becerilerini Geliştirin
+Merhaba Gündem,
+Şirketinizdeki ekiplerin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma pratiği yapmalarının önemini biliyoruz. Konuşarak Öğren, çalışanlarınızın kendine güven kazanmalarına ve iletişim becerilerini geliştirmelerine yardımcı olabilir. Online platformumuz, gelişim takibi ve raporlama ile destekleniyor. Bu konuyu detaylandırmak için bir görüşme ayarlamak ister misiniz?
+İyi günler dilerim,
+[Adınız]  
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Gündem Düvenci'nin HR profesyoneli olarak global toplantılardaki iletişim becerilerini geliştirme ihtiyacı ve çalışanların İngilizce konuşma güvenine odaklanılması</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6875,54 +7073,56 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness eksiklikleri</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Online İngilizce konuşma pratiği ihtiyacı</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>58</v>
+          <t>Ekiplerin İngilizce konuşma pratiği yaparak global ortamlarda daha etkili olmalarını sağlama</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Merhaba Ersoy Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ersoy, Kurumsal ekiplerin global ortamlarda daha etkili olabilmesi için İngilizce konuşma pratiği yapmalarının önemini biliyorum. Konuşarak Öğren olarak, ekiplerinizin speaking confidence kazanmasına yardımcı olabiliriz. Detayları görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ersoy Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Yetkinliğini Artırın
+Merhaba Ersoy Polat,
+Umarım bu mesaj sizi iyi bulur. Şirketinizdeki ekiplerin global toplantılarda daha etkili olabilmesi için İngilizce konuşma pratiği ihtiyaçlarının farkındayım. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunuyor ve gelişimlerini takip ederek raporlama yapıyoruz. Ekiplerinizin speaking confidence kazanarak uluslararası ortamlarda daha başarılı olmalarına yardımcı olabiliriz. Detayları görüşmek ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ersoy Polat'ın HR profesyoneli olarak ekiplerin global toplantılarda etkili olmaları için İngilizce konuşma pratiği ihtiyacını hedefleme.</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6965,54 +7165,58 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında ekiplerin İngilizce konuşma becerilerini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyoneli olarak çalışanların iletişim becerilerini geliştirme sorumluluğu</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerin İngilizce konuşma pratiği yaparak global toplantılara hazırlık ve güven artırma ihtiyaçlarına odaklanmak</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Merhaba Berrin Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Berrin, global iş ortamında ekiplerin İngilizce konuşma becerilerini geliştirmeye yönelik bir çözüm sunuyoruz. Çalışanlarınızın güvenle global toplantılara katılmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Berrin Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Yetkinliğini Artırmak
+Merhaba Berrin,
+Gelişen global iş ortamında ekiplerinizin İngilizce konuşma becerilerini artırmak, başarı için kritik bir adım. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunuyoruz. Bu sayede çalışanlarınızın global toplantılara daha iyi hazırlanmalarını ve kendilerine olan güvenlerini artırmalarını sağlıyoruz. 
+Ekiplerinizin iletişim becerilerini güçlendirmek için bir görüşme ayarlamak ister misiniz?
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Berrin'in HR profesyoneli olarak çalışanların iletişim becerilerini geliştirme sorumluluğu ve global iş ortamındaki ihtiyaçlar.</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7055,54 +7259,56 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Estimate: Mid-level to Senior based on HR/People Professional title</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving speaking confidence and global meeting readiness for employees</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training initiatives, indicating a potential need for English language practice.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>50</v>
+          <t>Highlight how Konuşarak Öğren can enhance employee communication skills, leading to improved performance in global settings.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Merhaba Efe Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Efe, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve global toplantılara daha iyi hazırlanmalarını sağlamak için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz? Detayları paylaşmak için sabırsızlanıyorum!</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Efe Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerelerini Geliştirin
+Merhaba Efe,
+Kurumsal ekibinizin global toplantılarda daha etkili olmasını sağlamak için, Konuşarak Öğren olarak online İngilizce konuşma pratiği, gelişim takibi ve raporlama sunuyoruz. Çalışanlarınızın konuşma özgüvenini artırarak, uluslararası ortamlarda daha başarılı olmalarına yardımcı olabiliriz. Bu konuda daha fazla bilgi almak isterseniz, sizinle görüşmeyi çok isterim.
+İyi çalışmalar,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Efe'nin HR profesyoneli olması ve çalışan gelişimi ile ilgili görevleri bulunması nedeniyle, İngilizce konuşma pratiği ihtiyacı üzerinde duruldu.</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7145,54 +7351,57 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication and language proficiency in global contexts</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for speaking confidence and meeting readiness in a corporate environment</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>58</v>
+          <t>Highlighting the importance of effective communication in HR processes and employee development</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Merhaba Sevda Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sevda, HR süreçlerinde etkili iletişimin önemini biliyorum. Kurumsal ekibinizin İngilizce konuşma pratiği ile gelişim takibi ihtiyacını karşılayabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sevda Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İletişimde Fark Yaratın
+Merhaba Sevda,
+HR alanında etkili iletişimin, çalışan gelişimi ve iş süreçlerinde ne kadar kritik olduğunu biliyoruz. Kurumsal ekibinizin İngilizce konuşma pratiği yaparak, global ortamlarda daha etkili olmasını sağlamak için 'Konuşarak Öğren' olarak yanınızdayız. İhtiyaç duydukları anlarda kendilerini ifade edebilmeleri ve toplantılara daha hazır olmaları için destek sunuyoruz. 
+İlgilenirseniz, detayları paylaşmak isterim.
+İyi çalışmalar,
+[Your Name]</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sevda'nın HR alanındaki rolü ve çalışan iletişimi ile dil yeterliliği konusundaki potansiyel ihtiyacı.</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7235,54 +7444,58 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level to senior level (estimate)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>improving employee communication skills and global meeting readiness</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, likely involved in training and development, which includes language skills</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>58</v>
+          <t>enhancing employee confidence in English speaking through targeted practice solutions</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Merhaba Hilal Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Hilal, İngilizce konuşma pratiği ile çalışanlarınızın iletişim becerilerini geliştirmelerine yardımcı olabileceğimizi düşünüyorum. Kurumsal ekipler için sunduğumuz çözümleri konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Hilal Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce İletişim Becerilerini Geliştirin
+Merhaba Hilal,
+Şirketinizdeki çalışanların iletişim becerilerini güçlendirmek, global toplantılara daha hazır hale gelmelerini sağlamak için online İngilizce konuşma pratiği sunuyoruz. Hedefe yönelik uygulamalarımızla çalışanların kendilerine olan güvenlerini artırabiliriz. Gelişim takibi ve raporlama ile de süreci daha verimli hale getirebiliriz. Detayları konuşmak isterseniz, size uygun bir zamanda görüşmeyi çok isterim.
+İyi çalışmalar dilerim,
+[Adınız] 
+[Şirket Adınız] 
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Hilal Atici'nin HR alanındaki uzmanlığı ve çalışanların iletişim becerilerini geliştirme ihtiyacı.</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7325,54 +7538,59 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication barriers in global meetings</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for improving speaking confidence among employees</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>58</v>
+          <t>Enhancing global meeting readiness and employee development through online English speaking practice</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Merhaba Ahmet Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ahmet, global toplantılardaki iletişim engellerini aşmak adına çalışanlarınızın İngilizce konuşma pratiğine ihtiyaç duyabileceğini düşünüyorum. Konuşarak Öğren ile bu süreci kolaylaştırabiliriz. Biraz sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ahmet Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global Toplantılarda İletişimi Güçlendirin
+Merhaba Ahmet Bey,
+Şirketinizdeki global toplantılarda iletişim engellerinin, çalışanların performansını etkilediğini biliyoruz. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak bu durumu aşmanıza yardımcı olabiliriz. Ekibinizin kendine güvenini artırarak, global iletişimde daha etkili olmalarını sağlamak bizim için önemli.
+İlginizi çekerse, detayları konuşmak için bir görüşme ayarlayabilir miyiz? 
+Saygılarımla,
+[Adınız] 
+[Şirketiniz] 
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Ahmet Bey'in global toplantılardaki iletişim engellerine yönelik bir çözüm arayışında olduğu ve çalışanların İngilizce konuşma pratiği ihtiyacını göz önünde bulundurarak yazılmıştır.</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7415,54 +7633,56 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee communication skills and confidence in English for global collaboration.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, may require tools for enhancing employees' English speaking skills.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>50</v>
+          <t>Offering a solution to boost speaking confidence and readiness for global meetings.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Merhaba Fatih Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Fatih, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmek için nasıl çözümler aradığınızı merak ediyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Fatih Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce İletişim Becerilerini Geliştirin
+Merhaba Fatih,
+HR alanındaki tecrübelerinizle, çalışanlarınızın İngilizce iletişim becerilerini geliştirme ihtiyacını anlıyorum. Konuşarak Öğren olarak, ekibinize online İngilizce konuşma pratiği sunuyoruz. Bu sayede, global toplantılara daha özgüvenli katılmalarını sağlıyor ve gelişimlerini raporluyoruz. Çözümümüz hakkında daha fazla bilgi almak isterseniz, bir görüşme ayarlayalım.
+İyi çalışmalar,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Fatih'in HR profesyoneli olması ve ekiplerin İngilizce iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -7505,54 +7725,58 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen iş dünyasında çalışanların İngilizce konuşma becerilerini geliştirmekte zorluk çekmeleri</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness ihtiyacı</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>58</v>
+          <t>Online İngilizce konuşma pratiği ile çalışanların kendine güvenini artırarak, global toplantılara daha hazırlıklı olmalarını sağlamak</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Merhaba Birgul Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Birgul Hanım, gelişen iş dünyasında çalışanlarınızın İngilizce konuşma becerilerini artırmalarına yardımcı olabileceğimize inanıyorum. Online konuşma pratiği ile ekibinizin global toplantılara daha hazır hale gelmesini sağlayabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Birgul Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Birgul Hanım,
+Gelişen iş dünyasında, ekiplerinizin İngilizce konuşma becerilerini geliştirmekte zorluklar yaşadığını biliyorum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın kendine güvenlerini artırmalarına ve global toplantılara daha iyi hazırlanmalarına yardımcı olabiliriz.
+Görüşmek için uygun bir zaman ayarlamak ister misiniz?
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Birgul Sert'in HR/People Professional olarak çalışanların İngilizce konuşma becerilerindeki zorlukları ile ilgili bilgi</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7595,54 +7819,58 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee engagement and development in English communication skills</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for improving speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>58</v>
+          <t>Offering tailored online English speaking practice to enhance team communication skills and track development</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Merhaba Emine Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Emine, çalışanların İngilizce iletişim becerilerini geliştirmek ve bu süreçteki ilerlemeyi takip etmek adına sizlerle tanışmak istedim. Online konuşma pratiği ile ekiplerinizi daha etkili hale getirebiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Emine Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişimini Güçlendirin
+Merhaba,
+Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek ve çalışan bağlılığını artırmak için özel bir çözüm sunuyoruz. Online konuşma pratiği ile ekip üyelerinizin iletişim becerilerini güçlendirirken, gelişimlerini de takip edebilirsiniz. Global toplantılara daha hazır hale gelmek için birlikte çalışmaya ne dersiniz?
+İlginizi çeker mi? 
+Saygılarımla,
+[Adınız] 
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Emine Önal'ın HR alanındaki deneyimi ve ekip içindeki iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -7685,54 +7913,59 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level or senior (estimate based on title)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>employee communication skills in English, global meeting effectiveness</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR role suggests a need for improved English communication among employees</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>58</v>
+          <t>promote online English speaking practice to enhance team confidence and meeting readiness</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Merhaba Tuğba Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Tuğba, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmelerine yardımcı olmanın önemini biliyorum. Konuşarak Öğren ile online konuşma pratiği sunarak, ekibinizin özgüvenini ve toplantılardaki etkinliğini artırabilirsiniz. Detayları paylaşmak ister misiniz? Sevgiler!</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Tuğba Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Güçlendirin
+Merhaba Tuğba,
+Türkiye'deki HR profesyonelleri olarak, kurumsal ekiplerde etkili iletişimin önemini biliyoruz. Konuşarak Öğren olarak, çalışanlarınıza online İngilizce konuşma pratiği sunarak, iletişim becerilerini geliştirmelerine yardımcı olabiliriz. Bu, global toplantılarda daha etkili olmalarını sağlayacak ve özgüvenlerini artıracaktır.
+Daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
+Sevgiler,
+[Adınız] 
+[Pozisyonunuz] 
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Tuğba'nın HR profesyoneli olarak çalışanların İngilizce iletişim becerilerini geliştirme gereksinimi ve global toplantılardaki etkinliği artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -7775,54 +8008,57 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>estimate, based on typical HR roles</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>estimate, likely mid to senior level based on title</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>need for improving speaking confidence and global meeting readiness among employees</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>potential need for online English speaking practice for team members</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>50</v>
+          <t>emphasize the importance of English communication skills in global HR practices and team collaboration</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Merhaba Latif Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Latif, HR teknolojileri alanındaki çalışmalarınızı takip ediyorum. Ekibinizin İngilizce konuşma becerilerini geliştirmesi, global toplantılarda daha etkili olmalarını sağlayabilir. Konuşarak Öğren, bu konuda destek olabilir. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Latif Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: İngilizce İletişim Becerilerini Geliştirin
+Merhaba,
+Şirketinizin global HR uygulamalarında etkili olabilmesi için çalışanlarınızın İngilizce konuşma becerilerinin artırılması büyük önem taşıyor. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği sunarak, hem gelişim takibi yapıyor hem de raporlama imkanı sağlıyor.
+Bu süreçte size nasıl yardımcı olabileceğimiz hakkında konuşmak isterim.
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Latif Yönder'in HR profesyoneli olarak global toplantılarda etkili iletişim ve konuşma becerileri üzerine odaklanması.</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -7865,54 +8101,57 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication and global collaboration challenges</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, Lara may be focused on enhancing employees' English speaking skills for better global meeting readiness.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>58</v>
+          <t>Offering solutions to improve English speaking confidence and provide structured development tracking for employees.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Merhaba Lara Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Lara, HR alanındaki deneyiminizle, çalışanların İngilizce konuşma becerilerini geliştirmesi için etkili çözümler sunabileceğimize inanıyorum. Konuşarak Öğren ile ekibinizin iletişim yeteneklerini güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Lara Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Lara,
+Kurumsal ekibinizin global toplantılara daha iyi hazırlanabilmesi için İngilizce konuşma becerilerini geliştirmek önemli bir konu. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ile çalışanlarınızın güvenini artırmayı ve gelişimlerini düzenli olarak takip etmeyi sağlıyoruz. Bu konuda sizinle bir görüşme yapmak isterim. 
+İyi çalışmalar dilerim,
+[İsminiz]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Lara'nın HR profesyoneli olarak çalışanların İngilizce konuşma becerilerini geliştirme odaklı olması ve global iletişim zorlukları ile ilgilenmesi.</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -7955,54 +8194,57 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında ekiplerin İngilizce iletişim becerilerini artırmak</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyonellerinin uluslararası toplantılara hazırlık ve kendine güven eksikliği</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N84" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerde iletişim becerilerini geliştirme ve global toplantılara hazırlık için online İngilizce pratik imkanı sunma</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Merhaba Gülşah Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Gülşah, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırma konusundaki çabalarınızı duydum. Kurumsal ekipler için online İngilizce pratik imkanı sunarak bu hedefe ulaşmalarına yardımcı olabiliriz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Gülşah Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerin İngilizce İletişim Becerilerini Geliştirin
+Merhaba Gülşah,
+Global iş ortamında ekiplerinizin İngilizce iletişim becerilerini artırmak için etkili bir yol arıyorsanız, size yardımcı olabiliriz. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Ekiplerinizin uluslararası toplantılara daha iyi hazırlanması ve kendine güven eksikliklerini gidermesi için birlikte çalışabiliriz. 
+Detayları paylaşmak isterim.
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Gülşah Eriş'in HR profesyoneli olarak ekiplerin İngilizce iletişim becerilerini artırma hedefi.</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8045,54 +8287,58 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>HR / People Management</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>employee engagement in English communication and global meeting effectiveness</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>as an HR professional, may require effective English communication skills for global interactions</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>58</v>
+          <t>enhancing team communication and global readiness through online English speaking practice</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Merhaba Yasemin Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Yasemin, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmesine yardımcı olma konusunda katkınızın büyük olduğunu düşünüyorum. Konuşarak Öğren ile ekiplerinizi global toplantılara daha iyi hazırlayabilirsiniz. Daha fazla bilgi için bağlantı kuralım!</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Yasemin Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekip İletişimini Güçlendirin
+Merhaba Yasemin,
+Kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmeleri, global toplantılarda etkinliklerini artırmak için kritik. Konuşarak Öğren, ekiplerinize çevrimiçi İngilizce konuşma pratiği sunarak bu süreci destekliyor. Gelişim takibi ve raporlama ile ilerlemenizi kolayca takip edebilirsiniz. 
+Detayları konuşmak için bir görüşme ayarlamak ister misiniz?
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Yasemin'in HR profesyoneli olması ve ekiplerin İngilizce iletişim becerilerini geliştirmeye yönelik bir ihtiyaç duyması.</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8135,54 +8381,58 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişmiş iletişim becerileri ve global toplantılara hazırlık eksikliği</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Çalışanların İngilizce konuşma pratiği ihtiyaçları</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>50</v>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness geliştirme</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Merhaba Onur Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Onur, şirketinizdeki ekiplerin İngilizce konuşma pratiği ihtiyacını gözlemledim. Konuşarak Öğren ile speaking confidence ve global toplantılara hazırlık süreçlerinizi güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Onur Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce İletişim Becerilerini Geliştirin
+Merhaba Onur,
+Gelişmiş iletişim becerileri, global toplantılarda etkin olmanın anahtarı. Konuşarak Öğren olarak, kurumsal ekiplerinize özel online İngilizce konuşma pratiği sunuyoruz. Ekip üyelerinizin speaking confidence ve global meeting readiness düzeylerini artırarak, uluslararası arenada daha etkili olmalarını sağlamak istiyoruz. 
+Detayları görüşmek için uygun bir zamanınız var mı?
+İyi çalışmalar,
+[Adınız]
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Onur Bayar'ın HR profesyoneli olması ve iletişim becerileri ile global toplantılara hazırlık eksikliğine yönelik ihtiyaçları.</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -8225,54 +8475,58 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employees' speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in training and development, may recognize the need for English communication skills</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>58</v>
+          <t>Highlight how online English speaking practice can enhance team collaboration and confidence in global meetings</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Merhaba Duygu Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Duygu, HR alanındaki tecrübelerinizle ekibinizin global toplantılarda daha özgüvenli olmasına katkı sağlamak için online İngilizce konuşma pratiği sunuyoruz. Bu konuda daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Duygu Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekibinizin İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Duygu,
+Şirketinizin global toplantılarda daha etkin bir şekilde yer alabilmesi için, ekibinize özel online İngilizce konuşma pratiği sunuyoruz. Bu program, çalışanlarınızın kendilerine olan güvenini artırarak, uluslararası işbirliklerinde daha başarılı olmalarına yardımcı olabilir. 
+Detayları konuşmak isterseniz, size yardımcı olmaktan mutluluk duyarım.
+İyi çalışmalar,
+[Adınız]
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Duygu'nun HR profesyoneli olarak ekibinin global toplantılarda özgüvenli olma ihtiyacına yönelik bir çözüm sunulması.</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8315,54 +8569,57 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>HR Technology</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında çalışanların İngilizce konuşma yeteneklerinin yetersizliği.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness'in artırılması ihtiyacı.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N88" t="n">
-        <v>58</v>
+          <t>Online İngilizce konuşma pratiği ile ekiplerin iletişim becerilerini geliştirmeyi ve global toplantılarda daha etkili olmayı sağlamak.</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Merhaba Nejla Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Nejla, global iş ortamında İngilizce konuşma becerilerinin önemini biliyorum. Kurumsal ekipler için sunduğumuz online konuşma pratiği ile iletişim becerilerini geliştirmek konusunda yardımcı olabilirim. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Nejla Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Takımınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Nejla,
+Gelişen global iş ortamında, çalışanların İngilizce konuşma yeteneklerinin yetersizliği büyük bir zorluk oluşturuyor. Konuşarak Öğren olarak, ekiplerinizi online İngilizce konuşma pratiği ile destekleyerek, iletişim becerilerini artırmayı ve global toplantılarda daha etkili olmalarını sağlamayı hedefliyoruz.
+Bu süreçte, gelişim takibi ve raporlama ile sürekli ilerleme kaydetmelerine yardımcı oluyoruz. Şirketinizin bu konuda nasıl bir destek alabileceğini konuşmak ister misiniz?
+İyi çalışmalar,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Nejla'nın HR Technology alanındaki uzmanlığı ve global iş ortamında İngilizce konuşma becerilerinin geliştirilmesine yönelik ilgi alanı.</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -8405,54 +8662,57 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Gelişen global iş ortamında ekiplerin İngilizce iletişim becerilerini artırmak</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyoneli olarak çalışanların iletişim becerileri ve gelişim takibi üzerine odaklanma</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>58</v>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness üzerine değer yaratma</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Merhaba Sebla Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Sebla, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırmak adına nasıl bir yol izlediğinizi merak ediyorum. Konuşarak Öğren ile kurumsal ekiplere yönelik çözümler sunuyoruz. İlgilenirseniz, detayları konuşalım.</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Sebla Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İngilizce İletişim Becerilerini Güçlendirin
+Merhaba Sebla,
+Gelişen global iş ortamında, ekiplerin İngilizce konuşma pratiği yaparak kendilerine güven kazanması ve uluslararası toplantılara hazır hale gelmesi oldukça önemli. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Çalışanlarınızın iletişim becerilerini geliştirmeye yönelik çözümlerimizle, gelişim takibi ve raporlama süreçlerini de destekliyoruz. 
+Detayları konuşmak isterseniz, memnuniyetle yardımcı olurum.
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Sebla'nın HR profesyoneli olması ve ekiplerin İngilizce iletişim becerilerini artırma ihtiyacı</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -8495,54 +8755,57 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>İngilizce konuşma pratiği eksikliği ve global toplantılara hazırlık</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Kurumsal ekiplerde speaking confidence ve global meeting readiness üzerine odaklanma</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N90" t="n">
-        <v>50</v>
+          <t>Online İngilizce konuşma pratiği ile ekiplerin global ortamlarda daha etkili olmasına destek sağlama</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Merhaba Nurdan Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Nurdan, İngilizce konuşma pratiği eksikliğinin ekiplerinizdeki global toplantılara hazırlığı etkilediğini biliyoruz. Konuşarak Öğren ile bu süreci geliştirmek ve ekiplerinizin özgüvenini artırmak hakkında konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Nurdan Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekipleriniz için İngilizce Konuşma Pratiği
+Merhaba Nurdan,
+Umarım iyisinizdir! Şirketinizdeki ekiplerin global toplantılara daha etkili katılım göstermesi için İngilizce konuşma pratiğinin önemini biliyorum. Konuşarak Öğren olarak, online platformumuz ile ekip üyelerinizin speaking confidence ve global meeting readiness becerilerini geliştirmelerine yardımcı olabiliriz. 
+Sizinle bu konuda daha detaylı konuşmak isterim. Uygun olduğunuzda bir görüşme ayarlayabilir miyiz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Nurdan'ın HR profesyoneli olarak ekiplerin global ortamlarda daha etkili olma ihtiyacına odaklanmak.</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -8585,54 +8848,56 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>Potential need for online English speaking practice for employees</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N91" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of improving communication skills and readiness for global interactions</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Merhaba Banu Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Banu, İngilizce konuşma pratiği ile çalışanların global toplantılara daha hazır hale gelmesini sağlıyoruz. Ekibinizin iletişim becerilerini güçlendirmek, uluslararası iletişimdeki özgüvenlerini artırmak için yardımcı olabiliriz. Görüşelim mi?</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Banu Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba,
+Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek, global toplantılara hazır olmalarını sağlamak için size yardımcı olabiliriz. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunuyoruz. Çalışanlarınızın kendine güvenini artırarak, uluslararası iş fırsatlarına daha iyi hazırlanmalarını sağlamak için bir görüşme ayarlamak ister misiniz?
+Sevgi ve saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Banu Toraman'ın HR profesyoneli olarak çalışanların konuşma becerilerini geliştirme konusundaki ilgisi ve global toplantılara hazırlık ihtiyacı</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -8675,54 +8940,57 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee language proficiency and confidence in global communication</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely responsible for employee development and training, indicating a need for English language improvement solutions.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N92" t="n">
-        <v>58</v>
+          <t>Highlight how online English speaking practice can enhance employee communication skills, boost confidence in meetings, and support ongoing development tracking.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Merhaba Meral Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Meral Hanım, İngilizce konuşma pratiği ve gelişim takibi ile çalışanların iletişim becerilerini artırmaya yardımcı olabileceğimizi düşünüyorum. Kurumsal ekibinize değer katacak çözümlerimiz hakkında konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Meral Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Meral Hanım,
+Şirketinizdeki çalışanların küresel iletişimde daha fazla özgüven kazanmasına yardımcı olmak için özel bir çözüm sunuyoruz. Online İngilizce konuşma pratiği ile birlikte gelişim takibi ve raporlama yaparak, ekip üyelerinizin dil yeterliliklerini artırabiliriz. Bu süreç, toplantılardaki özgüvenlerini de yükseltecektir. 
+Detayları görüşmek ister misiniz?
+İyi çalışmalar,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Meral Hanım'ın HR profesyoneli olarak çalışan gelişimi ve eğitimden sorumlu olduğuna dair çıkarım ve çalışanların dil yeterliliği ile küresel iletişim konusundaki ihtiyaçları.</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -8765,54 +9033,57 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employees' speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training initiatives</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N93" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of online English speaking practice for enhancing communication skills in a corporate environment</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Merhaba Leyla Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Leyla, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmanın ve uluslararası toplantılara hazırlanmanın ne kadar önemli olduğunu biliyorum. Konuşarak Öğren olarak bu alanda destek olabileceğimizi düşünüyorum. Bağlantıda kalalım!</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Leyla Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
+Merhaba Leyla Hanım,
+HR alanındaki deneyiminizle, çalışanların İngilizce konuşma becerilerini geliştirmesinin önemini takdir edersiniz. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunarak, hem iletişim becerilerini güçlendirebilir hem de global toplantılara daha iyi hazırlanmalarını sağlayabiliriz.
+Sizinle bu konuda daha detaylı konuşmak isterim. Görüşmek dileğiyle!
+Saygılarımla,
+[İsminiz]</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Leyla'nın HR profesyoneli olarak çalışan gelişimine odaklandığını ve global toplantılara hazırlık ile iletişim becerilerinin önemini vurgulamak.</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -8855,54 +9126,57 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Finance / Fintech - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Employee communication challenges in English, need for effective global collaboration</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, may seek to improve employees' English speaking skills for global meetings</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N94" t="n">
-        <v>50</v>
+          <t>Enhancing speaking confidence and meeting readiness for HR teams to improve communication across diverse teams</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Merhaba Ferda Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Ferda, HR profesyonellerinin İngilizce iletişim becerilerini güçlendirmek için online konuşma pratiği sunuyoruz. Takımınızın global işbirliğinde daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Ferda Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Takımınız için İngilizce Konuşma Pratiği 
+Merhaba Ferda, 
+Şirketinizin HR ekibinin global işbirliğini güçlendirmek için etkili bir çözüm arayışında olduğunu biliyorum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın iletişim becerilerini geliştirmelerine yardımcı olabiliriz. Bu sayede, global toplantılara daha hazır bir şekilde katılabilirler. Gelişim takibi ve raporlama ile süreci daha da verimli hale getiriyoruz. 
+İlgilenirseniz, detayları konuşmak için bir görüşme ayarlayabiliriz.
+İyi çalışmalar, 
+[Adınız]</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli olarak global işbirliği ve iletişim becerileri üzerine odaklanmak</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -8945,54 +9219,56 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Education - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>Estimate: Mid to Senior level based on HR/People Professional title</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving English speaking skills within the corporate team for global communication</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in employee development and training programs</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N95" t="n">
-        <v>58</v>
+          <t>Enhancing speaking confidence and global meeting readiness for employees</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Merhaba Müzeyyen Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Müzeyyen, iletişim becerilerini geliştirmek için harika bir fırsat sunuyoruz! Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim raporlaması ile global iletişimi güçlendirmek istemez misin? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Müzeyyen Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Kurumsal Ekipler İçin İngilizce Konuşma Pratiği
+Merhaba Müzeyyen,
+Çalışanlarınızın İngilizce konuşma becerilerini artırarak global toplantılara daha hazırlıklı olmalarını sağlamak istiyorsanız, 'Konuşarak Öğren' olarak size destek olabiliriz. Online İngilizce konuşma pratiği sunarak, ekibinizin kendine güvenini artırmayı ve gelişimlerini takip etmeyi hedefliyoruz. İlgilenirseniz, detayları paylaşmak isterim.
+Saygılarımla,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Müzeyyen'in HR profesyoneli olarak kurumsal ekiplerin İngilizce konuşma becerilerini geliştirme ihtiyacına odaklanma.</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9035,54 +9311,58 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Logistics - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>İngilizce konuşma pratiği eksikliği ve global toplantılara hazırlık</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>HR profesyonellerinin iletişim becerilerini geliştirme ihtiyacı</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N96" t="n">
-        <v>58</v>
+          <t>Kurumsal ekipler için konuşma pratiği ve gelişim takibi sunarak, global toplantılara daha iyi hazırlanmalarına yardımcı olma</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Merhaba Yağmur Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Yağmur, İngilizce konuşma pratiği ve global toplantılara hazırlık konusunda ekibinize destek olabileceğimizi düşünüyorum. Konuşarak Öğren ile iletişim becerilerinizi geliştirebilir ve daha etkili bir şekilde global platformlarda yer alabilirsiniz. Detaylar için bir sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Yağmur Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Global Toplantılara Daha Hazır Ekipler İçin
+Merhaba Yağmur,
+Kurumsal ekibinizin İngilizce konuşma pratiği eksikliği ile başa çıkmak için size yardımcı olabileceğimize inanıyorum. Konuşarak Öğren, ekiplerinize online İngilizce konuşma pratiği, bireysel gelişim takibi ve raporlama sunarak, global toplantılara daha iyi hazırlanmalarına destek oluyor.
+Bu konuda bir görüşme yapmayı ister misiniz? 
+Saygılarımla,
+[Adınız]
+[İletişim Bilgileriniz]</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Yağmur'un İngilizce konuşma pratiği eksikliği ve global toplantılara hazırlık ihtiyacı</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9125,54 +9405,57 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Professional Services - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>To be verified</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employees' speaking confidence and readiness for global meetings</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, there may be a need for enhancing English communication skills among employees</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>58</v>
+          <t>Offering a solution to boost speaking confidence and facilitate global communication for employees</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Merhaba Betül Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Betül, HR alanında çalışan biri olarak, çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlık süreçlerini kolaylaştırmak adına size yardımcı olabileceğimi düşünüyorum. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Betül Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Güvenini Artırın
+Merhaba Betül Hanım,
+Şirketinizde çalışanların global iletişim becerilerini geliştirmek üzere bir çözüm arayışında olduğunuzu duydum. Konuşarak Öğren, online İngilizce konuşma pratiği sunarak, çalışanlarınızın konuşma güvenini artırmalarına yardımcı olmaktadır. Gelişim takibi ve raporlama ile süreçlerinizi destekliyoruz.
+Detayları görüşmek isterseniz, memnuniyetle yardımcı olurum.
+Sevgiler,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Betül'ün HR alanındaki uzmanlığı ve çalışanların İngilizce konuşma güvenini artırma ihtiyacı.</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -9215,54 +9498,57 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Technology / SaaS - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>51-200 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional (to verify)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Improving employee speaking confidence and global meeting readiness</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>High, as the role likely requires effective communication in English</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N98" t="n">
-        <v>50</v>
+          <t>Highlight the importance of English speaking practice for enhancing team collaboration and performance in global meetings.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Merhaba Yeliz Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Yeliz, İngilizce konuşma pratiği konusundaki deneyimlerinizi merak ediyorum. Takımınızın global toplantılarda daha etkili olabilmesi için pratik yapma fırsatları sunuyoruz. İlgilenir misiniz?</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Yeliz Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Takımınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Yeliz Hanım,
+Şirketinizdeki ekiplerin global toplantılarda daha etkili olabilmesi için İngilizce konuşma pratiği büyük önem taşıyor. Konuşarak Öğren olarak, ekiplerinize online pratik imkanı sunarak, kendilerine güvenen bireyler ve güçlü takım dinamikleri oluşturmalarına yardımcı oluyoruz. Gelişim takibi ve raporlama ile ilerlemelerini ölçümleyebiliyorlar. Bu konuda sizinle daha fazla bilgi paylaşmak isterim.
+Saygılarımla,
+[Adınız]  
+Konuşarak Öğren</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Yeliz Kırcalı'nın HR profesyoneli olarak, çalışanların İngilizce konuşma güvenini artırma ve global toplantılara hazırlık konusundaki ihtiyaçları.</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9305,54 +9591,56 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Retail / E-commerce - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>201-500 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional - to verify</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Developing speaking confidence among employees and ensuring global meeting readiness</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, there may be a need for improved communication skills within the team</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N99" t="n">
-        <v>58</v>
+          <t>Highlight the benefits of enhancing speaking confidence and global communication skills through tailored online English practice</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Merhaba Busra Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Busra, HR profesyoneli olarak ekiplerinizin İngilizce konuşma becerilerini geliştirmesine katkı sağlamak ilginizi çekebilir. Konuşarak Öğren ile online pratik yaparak, çalışanların güvenle iletişim kurmalarını sağlama fırsatını keşfedelim!</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Busra Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Ekiplerinizin İletişim Becerilerini Geliştirin
+Merhaba Busra,
+HR alanındaki deneyiminiz ile çalışanlarınızın İngilizce konuşma pratiği yaparak iletişim becerilerini geliştirmesine katkıda bulunmak isteyebilirsiniz. Konuşarak Öğren, kurumsal ekipler için özel olarak tasarlanmış online pratik programları sunuyor. Bu sayede, çalışanlarınızın konuşma özgüveni artarken, global toplantılara daha iyi hazırlanabilecekler. Daha fazla bilgi almak isterseniz, memnuniyetle görüşürüm.
+İyi günler dilerim,
+[Adınız]</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>HR profesyoneli olarak ekiplerin İngilizce konuşma becerilerini geliştirme ihtiyacı ve global toplantılara hazırlık konusundaki ilgi.</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9395,54 +9683,59 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Manufacturing - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>501-1000 employees - AI estimate, verify</t>
+          <t>To be verified from LinkedIn profile/company page</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>To verify, but likely mid to senior level based on title</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Need for improved English speaking skills among employees for global meetings and collaboration</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in training and development, thus may recognize the need for English communication skills</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N100" t="n">
-        <v>58</v>
+          <t>Highlight how Konuşarak Öğren can enhance speaking confidence and readiness for global meetings, aligning with HR development goals</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Merhaba Mehmet Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Mehmet, HR profesyoneli olarak, çalışanlarınızın global toplantılara daha iyi hazırlanmaları için İngilizce konuşma becerilerini geliştirmeleri gerektiğini biliyorum. Konuşarak Öğren, ekibinize online pratik imkanı sunarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Mehmet Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
+Merhaba Mehmet,
+Şirketinizin global toplantılarda etkili iletişim kurabilmesi için çalışanların İngilizce konuşma becerilerini geliştirmesi kritik. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği, gelişim takibi ve raporlama sunarak bu ihtiyacı karşılıyor.
+Ekibinizin güvenle İngilizce konuşmasını sağlamaya yardımcı olabiliriz. Bir görüşme ayarlayıp detayları konuşmayı çok isterim.
+İyi çalışmalar,
+[Adınız] 
+[Unvanınız] 
+[İletişim Bilgileri]</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Mehmet'in HR alanındaki rolü ve çalışanların global toplantılara hazırlık ihtiyacı.</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -9485,54 +9778,57 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Healthcare - AI estimate, verify</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1001-5000 employees - AI estimate, verify</t>
+          <t>to be verified</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Mid/Senior - inferred from HR search context, verify</t>
+          <t>HR / People Professional</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.</t>
+          <t>Enhancing employees' English speaking skills for global communication and confidence in meetings</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Medium/High - inferred from Turkey-based corporate HR audience and potential global communication needs</t>
+          <t>As an HR professional, likely involved in training and development, indicating a need for English language improvement among employees</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici Ingilizce konusma</t>
-        </is>
-      </c>
-      <c r="N101" t="n">
-        <v>58</v>
+          <t>Offer tailored online English speaking practice solutions to enhance speaking confidence and global meeting readiness within corporate teams</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Merhaba Duygu Hanim/Bey, sirketiniz tarafinda HR/People alanindaki profilinizi gordum. Turkiye'deki ekipler icin global toplantilarda ve sunumlarda daha akici ingilizce konusma konusu HR ekipleri icin pratik bir gelisim alani olabilir. Konusarak Ogren'in kurumsal Ingilizce konusma pratigi modelini kisaca paylasmami ister misiniz?</t>
+          <t>Merhaba Duygu, kurumsal ekiplerin İngilizce konuşma pratiği ve gelişim takibi konusunda sağladığımız çözümlerle ilgili konuşmak isterim. Çalışanlarınızın global iletişim becerilerini artırmalarına nasıl destek olabileceğimize bakalım mı?</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Konu: sirketiniz ekipleri icin Ingilizce konusma pratigi
-Merhaba Duygu Hanim/Bey,
-sirketiniz tarafinda HR/People alanindaki profilinizi gorunce yazmak istedim. Ekiplerde Ingilizce bilen fakat toplanti, sunum ve musteri gorusmelerinde konusma ozguveni eksik kalan calisanlar olabilir.
-Konusarak Ogren olarak sirket ekiplerine online Ingilizce konusma pratigi, gelisim takibi ve raporlama sunuyoruz. Uygunsa size 2-3 kurumsal kullanim senaryosu gonderebilirim.
-Sevgiler,</t>
+          <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirelim
+Merhaba Duygu Hanım,
+Kurumsal ekiplerde İngilizce konuşma pratiği ve gelişim takibi sunan "Konuşarak Öğren" ile tanışmayı çok isterim. Çalışanlarınızın global toplantılarda kendilerini daha rahat ifade edebilmeleri ve güven kazanmaları için özel çözümlerimiz mevcut. Birlikte, ekiplerinizin İngilizce becerilerini nasıl geliştirebileceğimizi keşfetmek ister misiniz? 
+Saygılarımla,
+[Adınız] 
+[İletişim Bilgileri]</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>Used LinkedIn URL-derived name plus HR audience context; company/title still needs verification.</t>
+          <t>Duygu Yalçın Boransü'nün HR alanındaki uzmanlığı ve çalışanların İngilizce becerilerini geliştirme ihtiyacı.</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -9542,7 +9838,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/linkedin_hr_growth_leads_100.xlsx
+++ b/outputs/linkedin_hr_growth_leads_100.xlsx
@@ -516,12 +516,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Üçay Mühendislik</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,7 +532,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -572,18 +572,18 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Merhaba Elif, HR alanındaki deneyiminizle çalışanların İngilizce yeterliliğini artırmanın önemini biliyorsunuz. Konuşarak Öğren ile, ekiplerinizi global işbirliklerine hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Elif Hanım, HR alanındaki deneyiminizle çalışanların İngilizce yeterliliğini artırmanın önemini biliyorsunuz. Konuşarak Öğren ile, ekiplerinizi global işbirliklerine hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizi Global İşbirliğine Hazırlayın
-Merhaba Elif,
+Merhaba Elif Hanım,
 HR profesyoneli olarak, ekip üyelerinizin İngilizce yeterliliklerinin ve global toplantılara katılım becerilerinin arttırılması gerektiğini biliyorum. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği sunarak, kendilerine olan güvenlerini artırmalarına ve uluslararası işbirliklerine daha etkili katılmalarına yardımcı olabilir.
 Detayları görüşmek isterseniz, sevinirim.
 Saygılarımla,
@@ -598,7 +598,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Merhaba Eylül, Antwell Suites İstanbul'da İnsan Kaynakları Müdürü olarak çalışan bir profesyonel olarak, ekiplerinizin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma pratiğine ihtiyaç duyduğunuzu biliyorum. Bu konuda konuşmak ister misiniz?</t>
+          <t>Merhaba Eylül Hanım, Antwell Suites İstanbul'da İnsan Kaynakları Müdürü olarak çalışan bir profesyonel olarak, ekiplerinizin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma pratiğine ihtiyaç duyduğunuzu biliyorum. Bu konuda konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -950,13 +950,13 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Merhaba Berkan, iletişim becerilerinin geliştirilmesi konusundaki çalışmalarınızı görüyorum. Kurumsal ekipler için İngilizce konuşma pratiği sağlıyor ve bu sayede global toplantılara hazırlığı artırıyoruz. Bir sohbet edelim mi?</t>
+          <t>Merhaba Berkan Bey, iletişim becerilerinin geliştirilmesi konusundaki çalışmalarınızı görüyorum. Kurumsal ekipler için İngilizce konuşma pratiği sağlıyor ve bu sayede global toplantılara hazırlığı artırıyoruz. Bir sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Konu: Kurumsal Ekipler İçin İngilizce Konuşma Pratiği
-Merhaba Berkan,
+Merhaba Berkan Bey,
 Gelişen çalışanlarınızın İngilizce konuşma becerilerini artırmak ve global toplantılara hazırlıklarını güçlendirmek adına size yardımcı olabileceğimizi düşünüyorum. Konuşarak Öğren, kurumsal ekiplerin online İngilizce konuşma pratiği yapmasını sağlarken, gelişim takibi ve raporlama sunarak performanslarını artırmayı hedefliyor. İlgilenirseniz, sizinle bir görüşme ayarlamak isterim.
 Saygılarımla,
 [Adınız]
@@ -1044,13 +1044,13 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Merhaba Nihal, kurumunuzun global iş ilişkilerindeki iletişim becerilerini geliştirmeye yönelik çabalarınızı takdir ediyorum. Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yapmalarına yardımcı olabiliriz. Daha fazla bilgi almak ister misiniz?</t>
+          <t>Merhaba Nihal Hanım, kurumunuzun global iş ilişkilerindeki iletişim becerilerini geliştirmeye yönelik çabalarınızı takdir ediyorum. Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yapmalarına yardımcı olabiliriz. Daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
-Merhaba Nihal,
+Merhaba Nihal Hanım,
 Naci Çorap San. ve Tic. A.Ş.'deki iletişim becerilerini güçlendirme çabalarınızı biliyorum. Global iş ortamında etkili iletişim, başarı için kritik öneme sahip. Biz, Konuşarak Öğren olarak, çalışanlarınıza online İngilizce konuşma pratiği sunarak, güvenli bir iletişim ortamı yaratmayı hedefliyoruz. Bu süreçte gelişimlerini takip edip raporlayarak, ihtiyaçlarınıza özel çözümler sunabiliriz. 
 Detayları konuşmak ister misiniz?
 Saygılarımla,
@@ -1137,13 +1137,13 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Merhaba Nursen, çalışanlarınızın İngilizce konuşma becerilerini geliştirmelerine yardımcı olabileceğimizi düşündüm. Kurumsal eğitim programlarımızla, global toplantılara hazırlıkları için pratik imkanı sunuyoruz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Nursen Hanım, çalışanlarınızın İngilizce konuşma becerilerini geliştirmelerine yardımcı olabileceğimizi düşündüm. Kurumsal eğitim programlarımızla, global toplantılara hazırlıkları için pratik imkanı sunuyoruz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Konu: İngilizce Konuşma Becerilerini Geliştirme Fırsatı
-Merhaba Nursen,
+Merhaba Nursen Hanım,
 Sektör Kimya'daki çalışanlarınızın İngilizce konuşma becerilerindeki eksiklikleri gidermeye yardımcı olabileceğimizi düşünüyorum. Kurumsal eğitim programlarımızla, global toplantılara daha iyi hazırlanmalarına ve iletişim becerilerini geliştirmelerine destek sunuyoruz. 
 Daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
 İyi çalışmalar,
@@ -1230,7 +1230,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Merhaba Sevda, global etkileşimlerde iletişim becerilerinin önemi gün geçtikçe artıyor. Konuşarak Öğren ile ekibinizin İngilizce konuşma pratiğini geliştirerek bu süreci destekleyebiliriz. Detayları paylaşmak isterim. Selamlar!</t>
+          <t>Merhaba Sevda Hanım, global etkileşimlerde iletişim becerilerinin önemi gün geçtikçe artıyor. Konuşarak Öğren ile ekibinizin İngilizce konuşma pratiğini geliştirerek bu süreci destekleyebiliriz. Detayları paylaşmak isterim. Selamlar!</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1323,13 +1323,13 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Merhaba Burak, global iş ortamında ekiplerin İngilizce konuşma becerilerini artırmak için neler yapıyorsunuz? Konuşarak Öğren ile kurumsal ekiplerinize online pratik imkanı sunarak özgüven kazandırmayı hedefliyoruz. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Burak Bey, global iş ortamında ekiplerin İngilizce konuşma becerilerini artırmak için neler yapıyorsunuz? Konuşarak Öğren ile kurumsal ekiplerinize online pratik imkanı sunarak özgüven kazandırmayı hedefliyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Burak,
+Merhaba Burak Bey,
 Gelişen global iş ortamında, ekiplerinizin İngilizce konuşma becerilerini artırmak kritik bir öneme sahip. Konuşarak Öğren, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, özgüven kazanmalarına yardımcı oluyor. 
 Hedefimiz, HR profesyonellerinin global toplantılarda etkili iletişim kurma ihtiyaçlarına yanıt vermek. Eğer bu konuda daha fazla bilgi almak isterseniz, sizinle görüşmekten mutluluk duyarım.
 İyi çalışmalar,
@@ -1416,13 +1416,13 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Merhaba Şefaat Bey, Kırar Holding'deki insan kaynakları süreçlerinizi takip ediyorum. Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Global pazarlarda iletişim yetkinliğini artırmanın yollarını keşfetmek ister misiniz?</t>
+          <t>Merhaba Şefaat Hanım, Kırar Holding'deki insan kaynakları süreçlerinizi takip ediyorum. Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Global pazarlarda iletişim yetkinliğini artırmanın yollarını keşfetmek ister misiniz?</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Yetkinliğini Artırın
-Merhaba Şefaat Bey,
+Merhaba Şefaat Hanım,
 Kırar Holding'deki ekiplerinizin global pazarlarda etkili iletişim kurabilmesi için İngilizce konuşma pratiği sunuyoruz. Online platformumuz, çalışanlarınızın konuşma güvenini artırırken, gelişim takibi ve raporlama imkanı da sağlıyor. Global toplantılara daha iyi hazırlanmaları için nasıl destek olabileceğimizi konuşmak ister misiniz?
 İyi çalışmalar,
 [Adınız]
@@ -1509,7 +1509,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Merhaba Esra, Bilek İstanbul'da çalışanların global iletişim becerilerini geliştirmek için bir çözüm arayışında olduğunuzu anlıyorum. Konuşarak Öğren, ekiplerinizi online İngilizce konuşma pratiği ile güçlendirmeye yardımcı olabilir. Görüşmek ister misiniz?</t>
+          <t>Merhaba Esra Hanım, Bilek İstanbul'da çalışanların global iletişim becerilerini geliştirmek için bir çözüm arayışında olduğunuzu anlıyorum. Konuşarak Öğren, ekiplerinizi online İngilizce konuşma pratiği ile güçlendirmeye yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Adil Işık Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Merhaba Pervin, İngilizce iletişimde güven artırma konusunda çalışan bir HR profesyoneli olarak, ekibinizin uluslararası toplantılarda daha hazır olmasına yardımcı olabileceğimi düşünüyorum. Konuşarak Öğren ile detayları paylaşmak isterim. Görüşmek üzere!</t>
+          <t>Merhaba Pervin Hanım, İngilizce iletişimde güven artırma konusunda çalışan bir HR profesyoneli olarak, ekibinizin uluslararası toplantılarda daha hazır olmasına yardımcı olabileceğimi düşünüyorum. Konuşarak Öğren ile detayları paylaşmak isterim. Görüşmek üzere!</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Merhaba Merve, İngilizce konuşma pratiği ve gelişim takibi konusunda destek sunuyoruz. Çalışanlarınızın kendine güvenini artırmalarına ve global toplantılara hazır olmalarına yardımcı olabileceğimizi düşünüyorum. Tanışmak ister misiniz?</t>
+          <t>Merhaba Merve Hanım, İngilizce konuşma pratiği ve gelişim takibi konusunda destek sunuyoruz. Çalışanlarınızın kendine güvenini artırmalarına ve global toplantılara hazır olmalarına yardımcı olabileceğimizi düşünüyorum. Tanışmak ister misiniz?</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Merhaba Ceren, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, iletişim ve küresel işbirliği konularında yaşadıkları zorlukları aşmalarına yardımcı olabileceğimize inanıyorum. Konuşarak Öğren ile bu konuda nasıl destek olabileceğimizi konuşmak ister misiniz?</t>
+          <t>Merhaba Ceren Hanım, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, iletişim ve küresel işbirliği konularında yaşadıkları zorlukları aşmalarına yardımcı olabileceğimize inanıyorum. Konuşarak Öğren ile bu konuda nasıl destek olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2068,13 +2068,13 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Merhaba Tuğçe, global toplantılardaki iletişim zorluklarını aşmak için ekibinize online İngilizce konuşma pratiği sunuyoruz. İletişim becerilerini geliştirmek ve toplantılara daha hazır girmek için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
+          <t>Merhaba Tuğçe Hanım, global toplantılardaki iletişim zorluklarını aşmak için ekibinize online İngilizce konuşma pratiği sunuyoruz. İletişim becerilerini geliştirmek ve toplantılara daha hazır girmek için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Konu: Ekibinizin İletişim Becerilerini Geliştirin
-Merhaba Tuğçe,
+Merhaba Tuğçe Hanım,
 Kurumsal ekiplere yönelik sunduğumuz online İngilizce konuşma pratiği, gelişim takibi ve raporlama hizmeti ile global toplantılardaki iletişim zorluklarını aşmanıza yardımcı olabiliriz. Ekibinizin kendine güvenini artırarak, etkili iletişim kurmalarını sağlamak istiyoruz. Bu konuda nasıl bir yol alabileceğimiz hakkında bir görüşme ayarlamak ister misiniz?
 İlginiz için teşekkürler,
 [Adınız]  
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Uçak Tekstil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2116,7 +2116,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Aydın, Turkey</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2156,18 +2156,18 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Merhaba Latife, HR profesyonellerinin dil becerilerini geliştirmeye yönelik çalışmalarda oldukça etkili olabileceğini düşünüyorum. Konuşarak Öğren ile ekip üyelerinizin İngilizce konuşma güvenini artırarak global iletişimde daha etkili olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Latife Hanım, HR profesyonellerinin dil becerilerini geliştirmeye yönelik çalışmalarda oldukça etkili olabileceğini düşünüyorum. Konuşarak Öğren ile ekip üyelerinizin İngilizce konuşma güvenini artırarak global iletişimde daha etkili olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Latife,
+Merhaba Latife Hanım,
 Kurumsal ekibinizin global toplantılarda daha güçlü bir iletişim kurmasını sağlamak için İngilizce konuşma pratiği sunuyoruz. Konuşarak Öğren ile çalışanlarınızın konuşma güvenini artırarak, çeşitli takımlarda etkili bir iletişim sağlamalarına yardımcı olabiliriz. Bu konuda bir görüşme yapmak ister misiniz?
 Sevgiler,
 [Adınız]
@@ -2181,7 +2181,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -2346,13 +2346,13 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Merhaba Ümmühan, iletişim becerilerinin global iş dünyasında ne kadar önemli olduğunu biliyoruz. Konuşarak Öğren ile ekibinizin İngilizce konuşma becerilerini geliştirmesine yardımcı olabiliriz. Detayları konuşmak ister misiniz?</t>
+          <t>Merhaba Ümmühan Bey, iletişim becerilerinin global iş dünyasında ne kadar önemli olduğunu biliyoruz. Konuşarak Öğren ile ekibinizin İngilizce konuşma becerilerini geliştirmesine yardımcı olabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Konu: Ekibinizin İletişim Becerilerini Geliştirin
-Merhaba Ümmühan,
+Merhaba Ümmühan Bey,
 Global iş dünyasında etkili iletişim, başarıyı belirleyen kritik bir faktördür. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, çalışanlarınızın özgüvenini artırmayı ve global toplantılara hazırlıklarını geliştirmeyi hedefliyoruz. İş birliğimiz sayesinde, ekibinizin performansını önemli ölçüde artırabiliriz. Detayları görüşmek için uygun bir zamanınız var mı?
 İyi çalışmalar dilerim,
 [Adınız]  
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Süvari</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Grup İnsan Kaynakları ve İdari İşler Müdürü</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2435,18 +2435,18 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Merhaba Nazan, kurumsal ekiplerdeki İngilizce konuşma pratiği ile ilgili zorlukları bildiğinizi düşünüyorum. Konuşarak Öğren olarak, ekiplerinizi global toplantılara daha iyi hazırlamak için online çözümler sunuyoruz. Detayları konuşmak ister misiniz?</t>
+          <t>Merhaba Nazan Hanım, kurumsal ekiplerdeki İngilizce konuşma pratiği ile ilgili zorlukları bildiğinizi düşünüyorum. Konuşarak Öğren olarak, ekiplerinizi global toplantılara daha iyi hazırlamak için online çözümler sunuyoruz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Konu: Ekipleriniz İçin İngilizce Konuşma Pratiği
-Merhaba Nazan,
+Merhaba Nazan Hanım,
 Şirketinizin global toplantılarda daha fazla başarı elde etmesi için ekiplerinizin İngilizce konuşma becerilerini geliştirmek önem taşıyor. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Bu sayede, speaking confidence eksikliğini giderip, global toplantılara daha hazırlıklı hale gelmelerine yardımcı olabiliriz. 
 Size uygun bir zamanda detayları paylaşmak isterim.
 Saygılarımla,
@@ -2461,7 +2461,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Merhaba İlker, HR profesyonelleri olarak iletişim becerilerinin önemini biliyoruz. Ekibinizin İngilizce konuşma güvenini artırmak, global toplantılara hazırlıklarını güçlendirmek için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz?</t>
+          <t>Merhaba Ilker Bey, HR profesyonelleri olarak iletişim becerilerinin önemini biliyoruz. Ekibinizin İngilizce konuşma güvenini artırmak, global toplantılara hazırlıklarını güçlendirmek için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz?</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Doku Clinic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2622,18 +2622,18 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Merhaba Merve, gelişen global iş ortamında ekiplerinizin İngilizce konuşma pratiği yapma ihtiyacını göz önünde bulundurarak, Konuşarak Öğren olarak onlara nasıl destek olabileceğimizi paylaşmak isterim. Görüşmeye ne dersiniz?</t>
+          <t>Merhaba Merve Hanım, gelişen global iş ortamında ekiplerinizin İngilizce konuşma pratiği yapma ihtiyacını göz önünde bulundurarak, Konuşarak Öğren olarak onlara nasıl destek olabileceğimizi paylaşmak isterim. Görüşmeye ne dersiniz?</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Merve,
+Merhaba Merve Hanım,
 Umarım iyisinizdir. Gelişen global iş ortamında, çalışanlarınızın İngilizce konuşma pratiği yapma ihtiyacının ne denli önemli olduğunu biliyorum. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunuyoruz. Böylece hem speaking confidence kazanabilirler hem de global toplantılara daha hazır hale gelebilirler.
 Detayları konuşmak için uygun bir zaman ayarlayabilir miyiz?
 Sevgiler,
@@ -2650,7 +2650,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>ERNA MAŞ MAKİNA TİCARET VE SANAYİ A.Ş.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2678,7 +2678,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Çankırı, Turkey</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2718,18 +2718,18 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Merhaba Mesut, insan kaynakları profesyonellerinin ekip iletişimini geliştirmelerine yardımcı olma konusunda uzmanız. Konuşarak Öğren olarak, çalışanlarınızın global toplantılara hazır olmalarını sağlamak için online İngilizce konuşma pratiği sunuyoruz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Mesut Bey, insan kaynakları profesyonellerinin ekip iletişimini geliştirmelerine yardımcı olma konusunda uzmanız. Konuşarak Öğren olarak, çalışanlarınızın global toplantılara hazır olmalarını sağlamak için online İngilizce konuşma pratiği sunuyoruz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
-Merhaba Mesut,
+Merhaba Mesut Bey,
 Şirketinizde ekiplerinizi global toplantalara daha iyi hazırlamak ve İngilizce konuşma becerilerini geliştirmek için bir çözüm arıyorsanız, Konuşarak Öğren tam size göre. Online platformumuz sayesinde çalışanlarınız, güvenle iletişim kurma pratiği yapabilir. Gelin, ekiplerinizi daha etkili hale getirelim.
 Detayları görüşmek ister misiniz?
 İyi çalışmalar,
@@ -2743,7 +2743,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -2816,13 +2816,13 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Merhaba Ali, iletişim becerilerini geliştirmek ve çalışanların uluslararası toplantılara daha hazırlıklı olmalarını sağlamak için çözümler sunuyoruz. Konuşarak Öğren ile online İngilizce pratiği yaparak bu hedeflere ulaşmanızda yardımcı olabiliriz. Detayları görüşmek ister misin?</t>
+          <t>Merhaba Ali Bey, iletişim becerilerini geliştirmek ve çalışanların uluslararası toplantılara daha hazırlıklı olmalarını sağlamak için çözümler sunuyoruz. Konuşarak Öğren ile online İngilizce pratiği yaparak bu hedeflere ulaşmanızda yardımcı olabiliriz. Detayları görüşmek ister misin?</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
-Merhaba Ali,
+Merhaba Ali Bey,
 Kurumsal ekibinizin uluslararası ortamlarda daha etkili iletişim kurabilmesi için destek sunmak istiyoruz. Konuşarak Öğren, online İngilizce konuşma pratiği ile çalışanlarınızın kendine güvenini artırmayı ve global toplantılara hazır olmalarını sağlamayı hedefliyor. İlgilenirseniz, nasıl bir işbirliği yapabileceğimizi konuşmak isterim.
 İyi çalışmalar,
 [Adınız]</t>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Mavi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2863,7 +2863,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2903,18 +2903,18 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Merhaba Ecem, HR profesyonellerinin ekip iletişimini güçlendirmek için arayış içinde olduğunu biliyorum. Konuşarak Öğren ile İngilizce konuşma pratiği yaparak, global toplantılara daha hazır hale gelmeleri konusunda nasıl yardımcı olabileceğimizi keşfetmek ister misin?</t>
+          <t>Merhaba Ecem Bey, HR profesyonellerinin ekip iletişimini güçlendirmek için arayış içinde olduğunu biliyorum. Konuşarak Öğren ile İngilizce konuşma pratiği yaparak, global toplantılara daha hazır hale gelmeleri konusunda nasıl yardımcı olabileceğimizi keşfetmek ister misin?</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Ecem,
+Merhaba Ecem Bey,
 Ekiplerinizin İngilizce konuşma pratiği ile iletişim becerilerini geliştirmeleri, global toplantılarda daha özgüvenli olmalarını sağlayabilir. Konuşarak Öğren, kurumsal ekipler için özel olarak tasarlanmış online İngilizce programları sunuyor. Bu sayede, çalışanlarınızın gelişimini takip edebilir ve raporlarla destekleyebilirsiniz.
 Detayları konuşmak için bir görüşme ayarlayabilir miyiz?
 İyi çalışmalar,
@@ -2930,7 +2930,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Cronton Design Hotel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2998,18 +2998,18 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Merhaba Şeyda, HR profesyonellerinin ekiplerinin konuşma özgüvenini artırmalarına yardımcı olduğumuzu duydum. Global toplantılara hazırlık konusunda nasıl destek olabileceğimizi konuşmak ister misin?</t>
+          <t>Merhaba Şeyda Hanım, HR profesyonellerinin ekiplerinin konuşma özgüvenini artırmalarına yardımcı olduğumuzu duydum. Global toplantılara hazırlık konusunda nasıl destek olabileceğimizi konuşmak ister misin?</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Gücünü Artırın
-Merhaba Şeyda,
+Merhaba Şeyda Hanım,
 Şirketinizdeki çalışanların İngilizce konuşma becerilerini geliştirmeleri, global toplantılarda daha etkili olmaları için kritik öneme sahip. Konuşarak Öğren, online İngilizce konuşma pratiğiyle ekip üyelerinizin güvenini artırarak, global arenada daha etkin olmalarına yardımcı olabilir.
 Gelişim takibi ve raporlama ile desteklenen programlarımız hakkında daha fazla bilgi almak istersen, sizinle görüşmeyi çok isterim.
 İyi çalışmalar,
@@ -3023,7 +3023,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3035,12 +3035,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>İstanbul Beykent Üniversitesi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3051,7 +3051,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3091,18 +3091,18 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Merhaba Mehmet, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve uluslararası toplantılara hazırlıklarını güçlendirmek için nasıl bir yol izlediğinizi merak ediyorum. Bu konuda size yardımcı olabilecek bir çözüm sunabilirim. Görüşmek ister misiniz?</t>
+          <t>Merhaba Mehmet Bey, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve uluslararası toplantılara hazırlıklarını güçlendirmek için nasıl bir yol izlediğinizi merak ediyorum. Bu konuda size yardımcı olabilecek bir çözüm sunabilirim. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Mehmet,
+Merhaba Mehmet Bey,
 Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek, uluslararası iletişimde daha etkili olmalarını sağlamak için önemli bir adım. Konuşarak Öğren olarak, çalışanlarınız için kişiselleştirilmiş online İngilizce konuşma pratiği sunuyoruz. Bu sayede, hem konuşma özgüvenleri artacak hem de global toplantılara hazırlıkları güçlenecek. 
 Detayları konuşmak için zaman ayırabilir miyiz? 
 Saygılarımla,
@@ -3118,7 +3118,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3191,13 +3191,13 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Merhaba Serpil, global toplantılarda konuşma güveni ve farklı takımlarla etkili iletişim, HR profesyonelleri için kritik. Konuşarak Öğren'le, bu alandaki yetkinliğinizi artırabilirsiniz. Detaylar için bağlantıda kalalım!</t>
+          <t>Merhaba Serpil Bey, global toplantılarda konuşma güveni ve farklı takımlarla etkili iletişim, HR profesyonelleri için kritik. Konuşarak Öğren'le, bu alandaki yetkinliğinizi artırabilirsiniz. Detaylar için bağlantıda kalalım!</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Konu: HR Ekibiniz İçin İngilizce Konuşma Desteği
-Merhaba Serpil Hanım,
+Merhaba Serpil Bey,
 Şirketinizin uluslararası iletişimdeki başarıları için İngilizce konuşma pratiğinin önemini biliyoruz. Konuşarak Öğren, kurumsal ekiplere online İngilizce konuşma pratiği sunarak, global toplantılarda daha fazla özgüven ve etkili iletişim sağlamanıza yardımcı olabilir. Takım dinamiklerinizi güçlendirirken, gelişim takibi ve raporlama ile sürecinizi de destekliyoruz.
 Detayları paylaşmak için bir görüşme ayarlamayı çok isterim.
 Sevgiler,
@@ -3226,12 +3226,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>TÜBİTAK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3242,7 +3242,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Gebze, Kocaeli, Turkey</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Merhaba Ayten, Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yaparak global toplantılara daha hazır hale gelmelerine yardımcı olabiliriz. İlgilendiğiniz bir konu mu? Detayları paylaşmak isterim.</t>
+          <t>Merhaba Ayten Hanım, Konuşarak Öğren olarak, çalışanlarınızın İngilizce konuşma pratiği yaparak global toplantılara daha hazır hale gelmelerine yardımcı olabiliriz. İlgilendiğiniz bir konu mu? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Blueforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3337,7 +3337,7 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Başiskele, Kocaeli, Turkey</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3377,18 +3377,18 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Merhaba Sinem, İngilizce iletişim becerilerini geliştirmek ve çalışanların global toplantılara hazırlıklarını artırmak için online pratik sunuyoruz. Bu konuda daha fazla bilgi almak istersen, sevinirim! İyi çalışmalar dilerim.</t>
+          <t>Merhaba Sinem Hanım, İngilizce iletişim becerilerini geliştirmek ve çalışanların global toplantılara hazırlıklarını artırmak için online pratik sunuyoruz. Bu konuda daha fazla bilgi almak istersen, sevinirim! İyi çalışmalar dilerim.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirme
-Merhaba Sinem,
+Merhaba Sinem Hanım,
 Kurumsal ekibinizin İngilizce konuşma pratiği ve global toplantılara hazırlık konusunda zorluklar yaşadığını biliyorum. Konuşarak Öğren olarak, online platformumuzda çalışanlarınıza kişiselleştirilmiş İngilizce pratik imkanı sunuyoruz. Gelişim takibi ve raporlama ile bu süreci daha etkili kılabiliriz. 
 Detayları paylaşmak ve size nasıl yardımcı olabileceğimizi konuşmak için bir görüşme ayarlamak ister misiniz?
 İyi çalışmalar,
@@ -3402,7 +3402,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>COPRECI TR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3430,7 +3430,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Gebze, Kocaeli, Turkey</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3470,18 +3470,18 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Merhaba İnci, HR profesyonellerine yönelik sunduğumuz online İngilizce konuşma pratiği ile ekiplerinizi toplantılarda daha özgüvenli hale getirebiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Inci Hanım, HR profesyonellerine yönelik sunduğumuz online İngilizce konuşma pratiği ile ekiplerinizi toplantılarda daha özgüvenli hale getirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Geliştirin
-Merhaba İnci,
+Merhaba Inci Hanım,
 Şirketinizdeki HR süreçlerini güçlendirmek için, ekip üyelerinizin İngilizce iletişim becerilerini artırmaya yönelik özel online konuşma pratiği sunuyoruz. Bu program, çalışanlarınızın toplantılarda daha özgüvenli olmalarına ve etkin bir şekilde iletişim kurmalarına yardımcı olabilir. 
 Detayları konuşmak isterseniz, size yardımcı olmaktan memnuniyet duyarım.
 Saygılarımla,
@@ -3495,7 +3495,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Cast Merkezi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İK Yöneticisi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Merhaba Sevgi, kurumsal ekiplerin İngilizce konuşma pratiğiyle gelişimlerini destekleyen Konuşarak Öğren'i paylaşmak istedim. Çalışanlarınızın global toplantılarda daha özgüvenli olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Sevgi Hanım, kurumsal ekiplerin İngilizce konuşma pratiğiyle gelişimlerini destekleyen Konuşarak Öğren'i paylaşmak istedim. Çalışanlarınızın global toplantılarda daha özgüvenli olmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3660,13 +3660,13 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Merhaba Özgen, ekiplerin global toplantılara hazırlık sürecinde İngilizce konuşma becerilerini geliştirmek için nasıl bir yol izlediğinizi merak ettim. Konuşarak Öğren ile çalışanlarınızın kendine güvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Özgen Hanım, ekiplerin global toplantılara hazırlık sürecinde İngilizce konuşma becerilerini geliştirmek için nasıl bir yol izlediğinizi merak ettim. Konuşarak Öğren ile çalışanlarınızın kendine güvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin Global Başarıları İçin İngilizce Pratiği
-Merhaba Özgen,
+Merhaba Özgen Hanım,
 Şirketinizdeki ekiplerin global toplantılara daha iyi hazırlanmaları için etkili bir yol arayışında olduğunuzu duydum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın kendine güvenini artırabiliriz. 
 Bu süreç, ekip üyelerinizin iletişim becerilerini geliştirmelerine ve uluslararası iş ortamında daha etkili olmalarına yardımcı olacaktır. Detayları konuşmak için bir zaman ayıralım mı?
 Saygılarımla,
@@ -3754,13 +3754,13 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Merhaba Müzeyyen, HR alanındaki deneyiminizle global iş ortamında etkili iletişimin önemini bildiğinizi düşünüyorum. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için bir çözüm sunuyoruz. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Müzeyyen Hanım, HR alanındaki deneyiminizle global iş ortamında etkili iletişimin önemini bildiğinizi düşünüyorum. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için bir çözüm sunuyoruz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Müzeyyen,
+Merhaba Müzeyyen Hanım,
 Kurumsal ekiplerde çalışanların İngilizce konuşma becerilerini geliştirmek, global işbirliğini artırabilir. Konuşarak Öğren olarak, çevrimiçi platformda personelinizin konuşma pratiği yapmasını sağlıyoruz. Bu süreç, gelişim takibi ve raporlama ile destekleniyor. Ekibinizin güvenle global toplantılara katılmasına yardımcı olmak için bir görüşme ayarlamak ister misiniz?
 Saygılarımla,
 [İsminiz]</t>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>İMED</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3801,7 +3801,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3841,18 +3841,18 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Merhaba Şule, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirme üzerine çalıştığınızı biliyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha iyi hazırlanmasını sağlamak için bir çözüm sunuyoruz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Şule Hanım, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirme üzerine çalıştığınızı biliyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha iyi hazırlanmasını sağlamak için bir çözüm sunuyoruz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Konu: İngilizce İletişim Becerilerini Geliştirin
-Merhaba Şule,
+Merhaba Şule Hanım,
 Gelişen global iş ortamında, çalışanlarınızın İngilizce iletişim becerilerini artırmak adına etkili bir çözüm arayışında olduğunuzu biliyorum. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği, gelişim takibi ve raporlama hizmeti sunuyor. Ekibinizin global toplantılara daha iyi hazırlanmalarına destek olmak ve konuşma güvenlerini artırmak için birlikte çalışabiliriz. Detayları görüşmek ister misiniz?
 Sevgiler,
 [Adınız]</t>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3877,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>ELSAN Elektrik Sanayi ve Ticaret A.Ş.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3893,7 +3893,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Ankara, Turkey</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3933,18 +3933,18 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Merhaba Zeynep, çalışanların global toplantılarda daha etkili iletişim kurabilmesi için online İngilizce konuşma pratiği sunuyoruz. Ekibinizin kendine güvenini artırmak ve iletişim becerilerini geliştirmek için birlikte çalışabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Zeynep Hanım, çalışanların global toplantılarda daha etkili iletişim kurabilmesi için online İngilizce konuşma pratiği sunuyoruz. Ekibinizin kendine güvenini artırmak ve iletişim becerilerini geliştirmek için birlikte çalışabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Konu: Global İletişim Becerilerini Geliştirin
-Merhaba Zeynep,
+Merhaba Zeynep Hanım,
 Kurumsal ekibinizin global toplantılarda daha etkili olabilmesi için iletişim becerilerini geliştirmek önemlidir. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Çalışanlarınızın kendine güvenini artırarak, global iş dünyasında daha hazır hale gelmelerine yardımcı olabiliriz. İlgilenirseniz, detayları paylaşmak isterim.
 İyi çalışmalar,
 [Adınız]</t>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -3969,12 +3969,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Parex</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3985,7 +3985,7 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4025,18 +4025,18 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Merhaba Bahar, ekibinizin İngilizce iletişim becerilerini geliştirmek için online konuşma pratiği sunuyoruz. Küresel etkileşimlerde daha özgüvenli bir iletişim için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
+          <t>Merhaba Bahar Hanım, ekibinizin İngilizce iletişim becerilerini geliştirmek için online konuşma pratiği sunuyoruz. Küresel etkileşimlerde daha özgüvenli bir iletişim için nasıl yardımcı olabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Konu: İngilizce İletişim Becerilerinizi Geliştirin
-Merhaba Bahar,
+Merhaba Bahar Hanım,
 Şirketinizdeki ekip üyelerinin İngilizce iletişim becerilerini geliştirmek ve global etkileşimlerde daha etkili olmalarına yardımcı olmak için online İngilizce konuşma pratiği sunuyoruz. Gelişim takibi ve raporlama ile süreçlerinizi kolaylaştırıyoruz. Ekiplerinizin daha özgüvenli olmasını sağlayacak çözümlerimiz hakkında daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
 İyi çalışmalar,
 [Adınız]
@@ -4051,7 +4051,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4063,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Kalyon PV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Ankara, Turkey</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4219,13 +4219,13 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Merhaba İlker, HR alanında çalışan biri olarak, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmeleri konusunda önemli bir rol oynadığınızı biliyorum. Konuşarak Öğren ile bu becerileri güçlendirmek ve global toplantılara hazırlık sağlamak üzerine bir görüşme yapmayı ister misiniz?</t>
+          <t>Merhaba Ilker Bey, HR alanında çalışan biri olarak, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmeleri konusunda önemli bir rol oynadığınızı biliyorum. Konuşarak Öğren ile bu becerileri güçlendirmek ve global toplantılara hazırlık sağlamak üzerine bir görüşme yapmayı ister misiniz?</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Konu: Kurumsal Ekipler İçin İngilizce Pratiği
-Merhaba İlker,
+Merhaba Ilker Bey,
 Umarım iyisinizdir. Şirketinizdeki ekiplerin global toplantılara daha iyi hazırlanmaları ve İngilizce konuşma konusundaki güvenlerini artırmaları için online pratik fırsatları sunuyoruz. Konuşarak Öğren ile, ekip üyelerinizin iletişim becerilerini geliştirmek ve gelişimlerini raporlamak mümkün. Sizinle bu konuda bir görüşme yapmayı çok isterim.
 İyi günler dilerim,
 [Adınız]  
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Kopuz Şirketler Grubu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Grup İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4269,7 +4269,7 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4309,18 +4309,18 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Merhaba Gökçe, HR alanında çalışan bir profesyonel olarak, çalışanların İngilizce konuşma becerilerini geliştirmelerine nasıl katkıda bulunduğunuzu merak ediyorum. Konuşarak Öğren ile bu konuda destek olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Gökçe Hanım, HR alanında çalışan bir profesyonel olarak, çalışanların İngilizce konuşma becerilerini geliştirmelerine nasıl katkıda bulunduğunuzu merak ediyorum. Konuşarak Öğren ile bu konuda destek olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
-Merhaba Gökçe,
+Merhaba Gökçe Hanım,
 Kurumsal ekibinizin İngilizce konuşma pratiği yaparak global toplantılara daha hazır hale gelmesine nasıl katkıda bulunabileceğimizi konuşmak isterim. Konuşarak Öğren, çalışanlarınızın iletişim becerilerini geliştirmelerine ve güvenle konuşmalarına yardımcı oluyor. Eğitim süreçlerinize entegre edebileceğimiz çözümler sunuyoruz. İlgilenirseniz, detayları görüşmek için bir zaman ayarlayalım.
 İyi çalışmalar,
 [Adınız]</t>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4406,13 +4406,13 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Merhaba İlker Bey, iletişim becerileri geliştirmek, çalışanlarınızın global toplantılara hazırlığını artırmak için Konuşarak Öğren olarak destek olabileceğimizi düşünüyorum. Daha fazla bilgi almak ister misiniz?</t>
+          <t>Merhaba Ilker Bey, iletişim becerileri geliştirmek, çalışanlarınızın global toplantılara hazırlığını artırmak için Konuşarak Öğren olarak destek olabileceğimizi düşünüyorum. Daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerilerini Geliştirin
-Merhaba İlker Bey,
+Merhaba Ilker Bey,
 Şirketinizdeki çalışanların İngilizce konuşma becerilerini geliştirmek ve global toplantılara hazırlıklarını artırmak adına Konuşarak Öğren olarak size yardımcı olabiliriz. Online platformumuzla, çalışanlarınızın iletişim yeteneklerini güçlendirirken gelişim takibi ve raporlama sunuyoruz. Daha fazla bilgi almak isterseniz, sizinle görüşmekten memnuniyet duyarım.
 İyi çalışmalar,
 [Adınız]</t>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Kibar Holding</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>HRBP Müdürü</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Merhaba Lale, İngilizce iletişim becerilerini güçlendirmek ve ekiplerinizi uluslararası toplantalara hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim. Görüşmek üzere!</t>
+          <t>Merhaba Lale Hanım, İngilizce iletişim becerilerini güçlendirmek ve ekiplerinizi uluslararası toplantalara hazırlamak için online konuşma pratiği sunuyoruz. Detayları paylaşmak isterim. Görüşmek üzere!</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Optimum İnsan Kaynakları</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Senior Human Resources Specialist</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4546,7 +4546,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4586,18 +4586,18 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Merhaba Gizem, global toplantılarda etkili iletişimin ne kadar önemli olduğunu biliyoruz. Ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazanmasına yardımcı olabiliriz. Daha fazla bilgi almak isterseniz, memnuniyetle konuşalım!</t>
+          <t>Merhaba Gizem Hanım, global toplantılarda etkili iletişimin ne kadar önemli olduğunu biliyoruz. Ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazanmasına yardımcı olabiliriz. Daha fazla bilgi almak isterseniz, memnuniyetle konuşalım!</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Konu: İletişim Becerilerinizi Geliştirin
-Merhaba Gizem,
+Merhaba Gizem Hanım,
 Global toplantılarda etkili iletişim, ekiplerin başarısını doğrudan etkiler. Konuşarak Öğren olarak, şirketinizin İngilizce konuşma pratiği yaparak çalışanlarınızın kendine güven kazanmasına yardımcı olabiliriz. Ekip üyelerinin gelişimini takip edebilir ve raporlayabiliriz. Bu konuyu daha detaylı konuşmak için bir görüşme ayarlamayı ister misiniz?
 Saygılarımla,
 [Adınız]
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Yardımcı Beton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4734,7 +4734,7 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Konya, Turkey</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4774,18 +4774,18 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Merhaba Şahika, global HR rollerinde iletişim becerilerinin önemini biliyorum. Konuşarak Öğren ile online İngilizce pratiği yaparak ekibinizin global toplantılara daha hazır olmasını sağlayabilirsiniz. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Şahika Hanım, global HR rollerinde iletişim becerilerinin önemini biliyorum. Konuşarak Öğren ile online İngilizce pratiği yaparak ekibinizin global toplantılara daha hazır olmasını sağlayabilirsiniz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Konu: Global HR İletişim Becerilerinizi Geliştirin
-Merhaba Şahika,
+Merhaba Şahika Hanım,
 Şirketinizdeki HR profesyonellerinin İngilizce iletişim becerilerini geliştirmek, uluslararası işbirliklerinde başarıyı artırabilir. Konuşarak Öğren, kurumsal ekiplerinize online konuşma pratiği sunarak, global toplantılara daha hazır olmalarını sağlıyor. Ekibinizin bu fırsattan nasıl faydalanabileceğini konuşmak ister misiniz?
 Saygılarımla,
 [Adınız]</t>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>ANL FOOD INC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4826,7 +4826,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4866,18 +4866,18 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Merhaba Ezgi, Konuşarak Öğren ile ekiplerinizi küresel toplantılara daha hazır hale getirebilirsiniz. İngilizce konuşma pratiği ile iletişim becerilerini geliştirmek ve güven artırmak için bir görüşme ayarlamak ister misiniz?</t>
+          <t>Merhaba Ezgi Hanım, Konuşarak Öğren ile ekiplerinizi küresel toplantılara daha hazır hale getirebilirsiniz. İngilizce konuşma pratiği ile iletişim becerilerini geliştirmek ve güven artırmak için bir görüşme ayarlamak ister misiniz?</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Ezgi,
+Merhaba Ezgi Hanım,
 Kurumsal ekibinizin global toplantılardaki iletişimini geliştirmek için etkili bir çözüm arıyorsanız, Konuşarak Öğren tam size göre. Online İngilizce konuşma pratiği ile ekip üyelerinizin konuşma güvenini artırabilir ve toplantılara daha iyi hazırlanmış olmalarını sağlayabilirsiniz. 
 Eğitim programlarımız hakkında daha fazla bilgi almak isterseniz, size yardımcı olmaktan memnuniyet duyarım.
 Saygılarımla,
@@ -4894,7 +4894,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4906,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>BÜROTIME</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4922,7 +4922,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4962,18 +4962,18 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Merhaba Onur, İngilizce konuşma becerileri global iş dünyasında büyük önem taşıyor. Konuşarak Öğren, ekiplerinize çevrimiçi pratik yapma imkanı sunarak güvenlerini artırmalarına yardımcı olabilir. Görüşmek ister misiniz?</t>
+          <t>Merhaba Onur Bey, İngilizce konuşma becerileri global iş dünyasında büyük önem taşıyor. Konuşarak Öğren, ekiplerinize çevrimiçi pratik yapma imkanı sunarak güvenlerini artırmalarına yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Onur,
+Merhaba Onur Bey,
 Kurumsal ekipler için İngilizce konuşma pratiği sağlamak, global iş ortamlarında iletişim becerilerini güçlendirmenin anahtarı. Konuşarak Öğren olarak, çalışanlarınızın konuşma güvenini artırmalarına ve uluslararası toplantılara hazırlanmalarına yardımcı oluyoruz. Ekiplerinize özel programlarımızla gelişim takibi ve raporlama sunuyoruz. Detayları paylaşmak için bir görüşme ayarlayabilir miyiz?
 Saygılarımla,
 [Adınız]</t>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4998,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Aran Tekstil San. Tic. A.Ş.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5014,7 +5014,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Denizli, Turkey</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5054,18 +5054,18 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Merhaba Serdal, HR ekiplerinin iletişim becerilerini geliştirmesine yardımcı olan etkili bir çözüm sunuyoruz. Küresel toplantılarda daha fazla özgüven ve etkili iletişim için konuşma pratiği yapmayı düşünür müsünüz? Detayları paylaşmak isterim.</t>
+          <t>Merhaba Serdal Bey, HR ekiplerinin iletişim becerilerini geliştirmesine yardımcı olan etkili bir çözüm sunuyoruz. Küresel toplantılarda daha fazla özgüven ve etkili iletişim için konuşma pratiği yapmayı düşünür müsünüz? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Konu: Küresel Toplantılarda Başarı İçin Konuşma Pratiği
-Merhaba Serdal,
+Merhaba Serdal Bey,
 Kurumsal ekibinizin global toplantılarda daha etkili iletişim kurabilmesi için bir çözüm sunmak istiyorum. Konuşarak Öğren, çalışanlarınıza online İngilizce konuşma pratiği ve gelişim takibi sunarak, kendilerine olan güvenlerini artırmalarını sağlıyor. Bu sayede, ekibinizin uluslararası platformlarda daha başarılı olmasını hedefliyoruz.
 Detayları görüşmek isterseniz, sevinirim.
 İyi çalışmalar,
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Dicle FZA Otomotiv San. Ve Tic. A.Ş.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Satın Alma ve Personel Müdürü</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5107,7 +5107,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5147,18 +5147,18 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Merhaba Türkan, HR profesyonelleri için global toplantılarda etkili iletişim önemli. Konuşarak Öğren ile ekiplerinizin İngilizce konuşma pratiğini destekleyerek bu alanda güven kazanmalarına yardımcı olabiliriz. Detayları paylaşmayı çok isterim.</t>
+          <t>Merhaba Türkan Bey, HR profesyonelleri için global toplantılarda etkili iletişim önemli. Konuşarak Öğren ile ekiplerinizin İngilizce konuşma pratiğini destekleyerek bu alanda güven kazanmalarına yardımcı olabiliriz. Detayları paylaşmayı çok isterim.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Türkan, 
+Merhaba Türkan Bey, 
 Ekiplerinizin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma becerilerini geliştirmek önemli. Konuşarak Öğren, çalışanlarınızın konuşma pratiği yapmasını ve gelişimlerini takip etmesini sağlıyor. Eğlenceli ve etkileşimli bir ortamda, ekibinizin kendine güvenini artırmak için nasıl bir yol izleyebileceğimizi konuşmak isterim.
 İlgilenirseniz, bir görüşme ayarlayalım. 
 İyi çalışmalar,
@@ -5172,7 +5172,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Remed Assistance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5200,7 +5200,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Merhaba Ezgi, İngilizce konuşma pratiği ile ekiplerinizi global toplantılara daha hazır hale getirmek için birlikte çalışabileceğimizi düşünüyorum. Konuşarak Öğren ile çalışanlarımızın özgüvenini artırabiliriz. Detayları konuşmak ister misiniz?</t>
+          <t>Merhaba Ezgi Hanım, İngilizce konuşma pratiği ile ekiplerinizi global toplantılara daha hazır hale getirmek için birlikte çalışabileceğimizi düşünüyorum. Konuşarak Öğren ile çalışanlarımızın özgüvenini artırabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>İstanbul Silah ve Savunma Sanayi A.Ş.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5292,7 +5292,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Merhaba Duygu, LinkedIn profilinizdeki HR deneyiminizi inceledim. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için sizinle bağlantı kurmak istedim. Global toplantılara hazırlık sağlamak, çalışanlarınızın güvenini artırabilir. Görüşmek ister misiniz?</t>
+          <t>Merhaba Duygu Hanım, LinkedIn profilinizdeki HR deneyiminizi inceledim. Kurumsal ekiplerdeki İngilizce konuşma becerilerini geliştirmek için sizinle bağlantı kurmak istedim. Global toplantılara hazırlık sağlamak, çalışanlarınızın güvenini artırabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5431,13 +5431,13 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Merhaba Izel, HR alanındaki deneyiminizle, ekipler arası iletişimi güçlendirmenin önemini biliyorsunuz. Konuşarak Öğren ile online İngilizce pratiği yaparak, ekiplerinizin küresel toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Izel Bey, HR alanındaki deneyiminizle, ekipler arası iletişimi güçlendirmenin önemini biliyorsunuz. Konuşarak Öğren ile online İngilizce pratiği yaparak, ekiplerinizin küresel toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Konu: Takım İletişimini Güçlendirin
-Merhaba Izel,
+Merhaba Izel Bey,
 HR alanındaki deneyiminizle, çalışanların iletişim becerilerinin artmasının ekip dinamiklerine katkısını biliyorsunuzdur. Konuşarak Öğren, kurumsal ekiplerinize online İngilizce konuşma pratiği sunarak, global toplantılara hazırlık ve gelişim takibi yapmanızı sağlıyor. Ekibinizin kendine güvenle iletişim kurabilmesi için nasıl bir destek sunabileceğimizi konuşmak ister misiniz?
 Saygılarımla,
 [Adınız]</t>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>İmza</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5478,7 +5478,7 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5518,18 +5518,18 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Merhaba Yasemin, gelişen global iş ortamında çalışanların İngilizce konuşma becerilerini artırmanın öneminin farkındayım. Konuşarak Öğren olarak, kurumsal ekiplerin speaking confidence ve global meeting readiness alanlarında gelişim sağlamalarına yardımcı olabiliyoruz. Görüşmek ister misin?</t>
+          <t>Merhaba Yasemin Hanım, gelişen global iş ortamında çalışanların İngilizce konuşma becerilerini artırmanın öneminin farkındayım. Konuşarak Öğren olarak, kurumsal ekiplerin speaking confidence ve global meeting readiness alanlarında gelişim sağlamalarına yardımcı olabiliyoruz. Görüşmek ister misin?</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Konu: İngilizce Konuşma Pratiği ile Ekibinizi Güçlendirin
-Merhaba Yasemin,
+Merhaba Yasemin Hanım,
 Kurumsal ekipler için İngilizce konuşma pratiği sağlamak, gelişen global iş ortamında önemli bir ihtiyaç haline geldi. Konuşarak Öğren olarak, ekiplerinizin speaking confidence ve global meeting readiness alanlarında gelişim göstermelerine yardımcı oluyoruz.
 Eğer şirketinizin bu alanda destek alabileceği bir çözüm arayışı varsa, sizinle bu konuyu daha detaylı konuşmak isterim. Uygun olduğunuz bir zaman diliminde görüşebilir miyiz?
 İyi çalışmalar,
@@ -5543,7 +5543,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5647,12 +5647,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Bursa Çimento Fabrikası A.Ş.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5663,7 +5663,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Bursa, Turkey</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5703,18 +5703,18 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Merhaba Orhan, İngilizce iletişimde güven eksikliği, global toplantılara hazırlık açısından büyük bir engel olabilir. Kurumsal ekipler için online konuşma pratiği sunuyoruz. Bu konuda bir konuşma ayarlamak ister misiniz?</t>
+          <t>Merhaba Orhan Bey, İngilizce iletişimde güven eksikliği, global toplantılara hazırlık açısından büyük bir engel olabilir. Kurumsal ekipler için online konuşma pratiği sunuyoruz. Bu konuda bir konuşma ayarlamak ister misiniz?</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Konu: Global Toplantılara Hazırlık İçin İngilizce Pratiği
-Merhaba Orhan Çelebi,
+Merhaba Orhan Bey Çelebi,
 Umarım bu mesajım sizi iyi bulur. Şirketinizdeki ekiplerin İngilizce iletişiminde yaşadığı güven eksikliği, global toplantılarda zorlanmalara neden olabilir. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunarak bu sorunu aşmalarına yardımcı olabiliriz. Gelişim takibi ve raporlama ile desteklenen programlarımız, ekiplerinizin kendine güvenini artırmalarını sağlayacaktır. 
 Daha fazla bilgi almak veya bir toplantı ayarlamak isterseniz, lütfen benimle iletişime geçin.
 Saygılarımla,
@@ -5728,7 +5728,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Merhaba H Özdemir, global toplantılarda çalışanlarınızın İngilizce konuşma güvenini artırmak için neler yaptığınızı merak ediyorum. Konuşarak Öğren, online pratik ve gelişim takibi ile bu konuda destek olabilir. Görüşmek ister misiniz?</t>
+          <t>Merhaba H Bey Özdemir, global toplantılarda çalışanlarınızın İngilizce konuşma güvenini artırmak için neler yaptığınızı merak ediyorum. Konuşarak Öğren, online pratik ve gelişim takibi ile bu konuda destek olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Karaca Gümrük Müşavirliği</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5849,7 +5849,7 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -5926,12 +5926,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Oxigen Laboratuvarları</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Yöneticisi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5942,7 +5942,7 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5982,18 +5982,18 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Merhaba Derya, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmak ve global toplantılara hazırlık konusunda destek olabileceğimizi düşünmüştüm. Konuşarak Öğren'i keşfetmek isterseniz, memnuniyetle paylaşırım. İyi çalışmalar dilerim!</t>
+          <t>Merhaba Derya Hanım, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmak ve global toplantılara hazırlık konusunda destek olabileceğimizi düşünmüştüm. Konuşarak Öğren'i keşfetmek isterseniz, memnuniyetle paylaşırım. İyi çalışmalar dilerim!</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Derya,
+Merhaba Derya Hanım,
 Şirketinizdeki çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlık süreçlerini desteklemek için online pratik imkanı sunuyoruz. Konuşarak Öğren, gelişim takibi ve raporlama ile süreci daha etkili hale getiriyor. 
 İlgilenirseniz, detayları paylaşmaktan memnuniyet duyarım.
 İyi çalışmalar,
@@ -6009,7 +6009,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>GDZ Elektrik Dağıtım</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6037,7 +6037,7 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>İzmir, Turkey</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6077,18 +6077,18 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Merhaba Özge, kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliğini gidermeye yönelik çözümler sunuyoruz. Çalışanlarınızın global toplantılara daha hazır hale gelmesi için birlikte çalışmayı çok isterim. Detayları konuşalım mı?</t>
+          <t>Merhaba Özge Hanım, kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliğini gidermeye yönelik çözümler sunuyoruz. Çalışanlarınızın global toplantılara daha hazır hale gelmesi için birlikte çalışmayı çok isterim. Detayları konuşalım mı?</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Özge,
+Merhaba Özge Hanım,
 Umarım iyisinizdir! Kurumsal ekiplerde İngilizce konuşma pratiği ve güven eksikliği, global toplantılarda etkili iletişim için önemli bir engel oluşturabiliyor. Konuşarak Öğren olarak, ekiplerinize online İngilizce konuşma pratiği sunarak, bu konuda gelişimlerini takip etmenize yardımcı olabiliriz. Çalışanlarınızın speaking confidence’ını artırarak, global toplantılara daha hazır olmalarını sağlamak için bir araya gelmeyi çok isterim.
 Görüşmek dileğiyle,
 [Adınız]</t>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Gökçelik A.Ş.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6129,7 +6129,7 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Bursa, Turkey</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6169,18 +6169,18 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Merhaba Melike, HR alanında çalışan bir profesyonel olarak, kurumsal ekiplerin İngilizce konuşma pratiğini geliştirmesi konusunda nasıl destek sağlayabileceğimizi konuşmak isterim. Konuşarak Öğren ile çalışanlarınızın güvenle konuşmasını sağlamak mümkün. Görüşmek dileğiyle!</t>
+          <t>Merhaba Melike Hanım, HR alanında çalışan bir profesyonel olarak, kurumsal ekiplerin İngilizce konuşma pratiğini geliştirmesi konusunda nasıl destek sağlayabileceğimizi konuşmak isterim. Konuşarak Öğren ile çalışanlarınızın güvenle konuşmasını sağlamak mümkün. Görüşmek dileğiyle!</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Konu: İngilizce Konuşma Pratiği ile Güçlü Ekipler Yaratın
-Merhaba Melike,
+Merhaba Melike Hanım,
 Kurumsal ekibinizin global iletişimde daha etkili olabilmesi için İngilizce konuşma pratiği sunan Konuşarak Öğren’i tanıtmak istiyorum. Çalışanlarınızın konuşma güvenini artırarak toplantılara daha hazır hale gelmelerini sağlayabiliriz. Detayları görüşmek ister misiniz?
 Saygılarımla,
 [Adınız]</t>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6266,13 +6266,13 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Merhaba Deniz, İngilizce konuşma pratiği ile çalışanların global toplantılardaki özgüvenini artırmanıza yardımcı olabiliriz. Kurumsal ekibinizin performansını artırmak için birlikte çalışmayı çok isteriz. Detayları konuşalım! Sevgiler, Konuşarak Öğren.</t>
+          <t>Merhaba Deniz Hanım, İngilizce konuşma pratiği ile çalışanların global toplantılardaki özgüvenini artırmanıza yardımcı olabiliriz. Kurumsal ekibinizin performansını artırmak için birlikte çalışmayı çok isteriz. Detayları konuşalım! Sevgiler, Konuşarak Öğren.</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Yetkinliğini Artırın
-Merhaba Deniz,
+Merhaba Deniz Hanım,
 HR alanındaki tecrübenizle, global toplantılarda çalışanların özgüvenini artırmanın önemini biliyorsunuzdur. Konuşarak Öğren olarak, kurumsal ekiplere yönelik online İngilizce konuşma pratiği sunuyoruz. Çalışanlarınızın iletişim becerilerini geliştirerek, hem katılımlarını hem de performanslarını artırabiliriz. Sizinle bu konuda detaylı bir görüşme yapmak isterim.
 Sevgiler,
 [Adınız]  
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>EMSA Generator</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Yöneticisi</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6314,7 +6314,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6354,18 +6354,18 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Merhaba Murat, HR alanındaki deneyiminizle ekibinizin global toplantılardaki iletişimini güçlendirmek için bir çözüm sunmak istiyorum. Online İngilizce konuşma pratiği ile ekip üyelerinizin özgüvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Murat Bey, HR alanındaki deneyiminizle ekibinizin global toplantılardaki iletişimini güçlendirmek için bir çözüm sunmak istiyorum. Online İngilizce konuşma pratiği ile ekip üyelerinizin özgüvenini artırabiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Konu: Global Toplantılarda İletişim Gücünüzü Artırın
-Merhaba Murat,
+Merhaba Murat Bey,
 HR profesyoneli olarak, ekibinizin global toplantılarda etkili iletişim kurma yetkinliğini artırmak istediğinizi biliyorum. Konuşarak Öğren olarak, kurumsal ekipler için kişiselleştirilmiş online İngilizce konuşma pratiği sunuyoruz. Bu sayede çalışanlarınızın kendilerine olan güvenlerini artırarak, uluslararası ortamlarda daha etkili olmalarını sağlıyoruz.
 İlgilenirseniz, detayları konuşmak için bir görüşme ayarlayabiliriz.
 Saygılarımla,
@@ -6381,7 +6381,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6393,12 +6393,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Miracle Cash&amp;More</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6409,7 +6409,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6449,18 +6449,18 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Merhaba Zeynep, İngilizce konuşma pratiği ve gelişim takibi konusunda Konuşarak Öğren ile çalışan ekiplerin, global toplantılarda kendilerini daha güvende hissettiğini görüyoruz. İlgini çekerse, detayları paylaşmak isterim.</t>
+          <t>Merhaba Zeynep Hanım, İngilizce konuşma pratiği ve gelişim takibi konusunda Konuşarak Öğren ile çalışan ekiplerin, global toplantılarda kendilerini daha güvende hissettiğini görüyoruz. İlgini çekerse, detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Yetkinliğini Artırın
-Merhaba Zeynep,
+Merhaba Zeynep Hanım,
 Şirketinizdeki çalışanların global toplantılarda daha fazla özgüvenle konuşmalarını sağlamak için Konuşarak Öğren olarak online İngilizce konuşma pratiği ve gelişim takibi sunuyoruz. Ekibinizin iletişim becerilerini geliştirmesi, uluslararası etkileşimlerde daha etkili olmalarına katkı sağlayacaktır. 
 Detayları paylaşmak için bir görüşme ayarlamak ister misin?
 İyi çalışmalar,
@@ -6474,7 +6474,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6547,13 +6547,13 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Merhaba Emre, global toplantılarda İngilizce iletişim zorluklarının farkındayım. Konuşarak Öğren, ekip üyelerinizin konuşma özgüvenini artırarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim!</t>
+          <t>Merhaba Emre Bey, global toplantılarda İngilizce iletişim zorluklarının farkındayım. Konuşarak Öğren, ekip üyelerinizin konuşma özgüvenini artırarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim!</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Konu: İngilizce İletişimde Güçlenin
-Merhaba Emre,
+Merhaba Emre Bey,
 Ekiplerinizin global toplantılarda etkili iletişim kurabilmesi için İngilizce konuşma pratiğine ihtiyaç duyduğunu düşünüyorum. Konuşarak Öğren, çalışanlarınızın konuşma özgüvenini artırarak bu zorlukları aşmalarına yardımcı olabilir. Online platformumuz sayesinde gelişim takibi ve raporlama da sağlıyoruz. 
 Detayları görüşmek ister misiniz?
 İyi çalışmalar,
@@ -6640,7 +6640,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Merhaba Enes, İngilizce konuşma pratiği üzerine sunduğumuz çözümlerle çalışanların kendine güvenini artırarak global iletişimini güçlendirmeyi hedefliyoruz. Bu konuda daha fazla bilgi almak isterseniz, görüşmek isterim.</t>
+          <t>Merhaba Enes Bey, İngilizce konuşma pratiği üzerine sunduğumuz çözümlerle çalışanların kendine güvenini artırarak global iletişimini güçlendirmeyi hedefliyoruz. Bu konuda daha fazla bilgi almak isterseniz, görüşmek isterim.</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Nevita</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6690,7 +6690,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6730,18 +6730,18 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Merhaba Sadullah, İngilizce konuşma pratiği ile çalışanlarınızın global toplantılara hazırlığını artırabileceğinizi biliyor muydunuz? Konuşarak Öğren olarak bu konuda destek sunabiliriz. Detaylı bilgi için bağlantı kuralım!</t>
+          <t>Merhaba Sadullah Bey, İngilizce konuşma pratiği ile çalışanlarınızın global toplantılara hazırlığını artırabileceğinizi biliyor muydunuz? Konuşarak Öğren olarak bu konuda destek sunabiliriz. Detaylı bilgi için bağlantı kuralım!</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Sadullah,
+Merhaba Sadullah Bey,
 Kurumsal ekibinizin İngilizce konuşma becerilerini geliştirmek ve global toplantılara daha iyi hazırlanmaları için etkili bir çözüm arıyorsanız, Konuşarak Öğren size yardımcı olabilir. Online platformumuz, çalışanlarınıza özgü gelişim takibi ve raporlama imkanı sunarak, kendilerine olan güvenlerini artırmalarını sağlıyor.
 Daha fazla bilgi almak isterseniz, size uygun bir zaman diliminde görüşmeyi çok isterim.
 İyi çalışmalar,
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6767,12 +6767,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Eyüpsultan Belediyesi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>Genel Müdür Yardımcısı (İnsan Kaynakları)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6783,7 +6783,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Merhaba İkbal Hanım, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, global toplantılara hazır olmalarını sağlamak için online pratik imkanı sunuyoruz. Ekibinizin iletişim becerilerini artırmak için nasıl bir destek sağlayabileceğimizi konuşmak ister misiniz?</t>
+          <t>Merhaba Ikbal Bey, çalışanlarınızın İngilizce konuşma becerilerini geliştirmek, global toplantılara hazır olmalarını sağlamak için online pratik imkanı sunuyoruz. Ekibinizin iletişim becerilerini artırmak için nasıl bir destek sağlayabileceğimizi konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -6921,13 +6921,13 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Merhaba Ahmet, global toplantılarda etkili iletişim ve ekip üyelerinin konuşma özgüvenini artırma ihtiyacınızı anlıyorum. Konuşarak Öğren ile İngilizce pratik yaparak bu hedeflere ulaşmanıza yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Ahmet Bey, global toplantılarda etkili iletişim ve ekip üyelerinin konuşma özgüvenini artırma ihtiyacınızı anlıyorum. Konuşarak Öğren ile İngilizce pratik yaparak bu hedeflere ulaşmanıza yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Ahmet,
+Merhaba Ahmet Bey,
 Şirketinizdeki ekiplerin global toplantılarda etkili iletişim kurabilmesi ve bireylerin konuşma özgüvenini artırabilmesi için online İngilizce pratik imkanı sunuyoruz. Konuşarak Öğren ile çalışanlarınızın İngilizce becerilerini geliştirmesine yardımcı olabiliriz. Bu, HR gelişim hedeflerinize katkıda bulunabilir. İlgilenirseniz, detayları konuşmak isterim.
 Saygılarımla,
 [Adınız]
@@ -7015,13 +7015,13 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Merhaba Gündem, HR profesyoneli olarak global toplantılardaki iletişim becerilerinin artırılması üzerine konuşmak isterim. Konuşarak Öğren, ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazandırmasına yardımcı olabilir. Görüşmek ister misiniz?</t>
+          <t>Merhaba Gündem Bey, HR profesyoneli olarak global toplantılardaki iletişim becerilerinin artırılması üzerine konuşmak isterim. Konuşarak Öğren, ekibinizin İngilizce konuşma pratiği yaparak kendine güven kazandırmasına yardımcı olabilir. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Konu: Global Toplantılarda İletişim Becerilerini Geliştirin
-Merhaba Gündem,
+Merhaba Gündem Bey,
 Şirketinizdeki ekiplerin global toplantılarda daha etkili iletişim kurabilmesi için İngilizce konuşma pratiği yapmalarının önemini biliyoruz. Konuşarak Öğren, çalışanlarınızın kendine güven kazanmalarına ve iletişim becerilerini geliştirmelerine yardımcı olabilir. Online platformumuz, gelişim takibi ve raporlama ile destekleniyor. Bu konuyu detaylandırmak için bir görüşme ayarlamak ister misiniz?
 İyi günler dilerim,
 [Adınız]  
@@ -7047,12 +7047,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Tibet / Sultanlar Holding</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Direktörü</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7063,7 +7063,7 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7103,18 +7103,18 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Merhaba Ersoy, Kurumsal ekiplerin global ortamlarda daha etkili olabilmesi için İngilizce konuşma pratiği yapmalarının önemini biliyorum. Konuşarak Öğren olarak, ekiplerinizin speaking confidence kazanmasına yardımcı olabiliriz. Detayları görüşmek ister misiniz?</t>
+          <t>Merhaba Ersoy Bey, Kurumsal ekiplerin global ortamlarda daha etkili olabilmesi için İngilizce konuşma pratiği yapmalarının önemini biliyorum. Konuşarak Öğren olarak, ekiplerinizin speaking confidence kazanmasına yardımcı olabiliriz. Detayları görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Yetkinliğini Artırın
-Merhaba Ersoy Polat,
+Merhaba Ersoy Bey Polat,
 Umarım bu mesaj sizi iyi bulur. Şirketinizdeki ekiplerin global toplantılarda daha etkili olabilmesi için İngilizce konuşma pratiği ihtiyaçlarının farkındayım. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunuyor ve gelişimlerini takip ederek raporlama yapıyoruz. Ekiplerinizin speaking confidence kazanarak uluslararası ortamlarda daha başarılı olmalarına yardımcı olabiliriz. Detayları görüşmek ister misiniz?
 İyi çalışmalar,
 [Adınız]</t>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Platform Gayrimenkul Değerleme ve Danışmanlık A.Ş.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7155,7 +7155,7 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7195,18 +7195,18 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Merhaba Berrin, global iş ortamında ekiplerin İngilizce konuşma becerilerini geliştirmeye yönelik bir çözüm sunuyoruz. Çalışanlarınızın güvenle global toplantılara katılmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Berrin Bey, global iş ortamında ekiplerin İngilizce konuşma becerilerini geliştirmeye yönelik bir çözüm sunuyoruz. Çalışanlarınızın güvenle global toplantılara katılmalarına yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Yetkinliğini Artırmak
-Merhaba Berrin,
+Merhaba Berrin Bey,
 Gelişen global iş ortamında ekiplerinizin İngilizce konuşma becerilerini artırmak, başarı için kritik bir adım. Konuşarak Öğren olarak, kurumsal ekiplerinize online İngilizce konuşma pratiği sunuyoruz. Bu sayede çalışanlarınızın global toplantılara daha iyi hazırlanmalarını ve kendilerine olan güvenlerini artırmalarını sağlıyoruz. 
 Ekiplerinizin iletişim becerilerini güçlendirmek için bir görüşme ayarlamak ister misiniz?
 Saygılarımla,
@@ -7221,7 +7221,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -7294,13 +7294,13 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Merhaba Efe, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve global toplantılara daha iyi hazırlanmalarını sağlamak için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz? Detayları paylaşmak için sabırsızlanıyorum!</t>
+          <t>Merhaba Efe Bey, İngilizce konuşma pratiğiyle çalışanlarınızın özgüvenini artırmak ve global toplantılara daha iyi hazırlanmalarını sağlamak için Konuşarak Öğren'in sunduğu çözümleri keşfetmek ister misiniz? Detayları paylaşmak için sabırsızlanıyorum!</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İletişim Becerelerini Geliştirin
-Merhaba Efe,
+Merhaba Efe Bey,
 Kurumsal ekibinizin global toplantılarda daha etkili olmasını sağlamak için, Konuşarak Öğren olarak online İngilizce konuşma pratiği, gelişim takibi ve raporlama sunuyoruz. Çalışanlarınızın konuşma özgüvenini artırarak, uluslararası ortamlarda daha başarılı olmalarına yardımcı olabiliriz. Bu konuda daha fazla bilgi almak isterseniz, sizinle görüşmeyi çok isterim.
 İyi çalışmalar,
 [İsminiz]</t>
@@ -7386,13 +7386,13 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Merhaba Sevda, HR süreçlerinde etkili iletişimin önemini biliyorum. Kurumsal ekibinizin İngilizce konuşma pratiği ile gelişim takibi ihtiyacını karşılayabiliriz. Detayları konuşmak ister misiniz?</t>
+          <t>Merhaba Sevda Hanım, HR süreçlerinde etkili iletişimin önemini biliyorum. Kurumsal ekibinizin İngilizce konuşma pratiği ile gelişim takibi ihtiyacını karşılayabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Konu: İletişimde Fark Yaratın
-Merhaba Sevda,
+Merhaba Sevda Hanım,
 HR alanında etkili iletişimin, çalışan gelişimi ve iş süreçlerinde ne kadar kritik olduğunu biliyoruz. Kurumsal ekibinizin İngilizce konuşma pratiği yaparak, global ortamlarda daha etkili olmasını sağlamak için 'Konuşarak Öğren' olarak yanınızdayız. İhtiyaç duydukları anlarda kendilerini ifade edebilmeleri ve toplantılara daha hazır olmaları için destek sunuyoruz. 
 İlgilenirseniz, detayları paylaşmak isterim.
 İyi çalışmalar,
@@ -7479,13 +7479,13 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Merhaba Hilal, İngilizce konuşma pratiği ile çalışanlarınızın iletişim becerilerini geliştirmelerine yardımcı olabileceğimizi düşünüyorum. Kurumsal ekipler için sunduğumuz çözümleri konuşmak ister misiniz?</t>
+          <t>Merhaba Hilal Hanım, İngilizce konuşma pratiği ile çalışanlarınızın iletişim becerilerini geliştirmelerine yardımcı olabileceğimizi düşünüyorum. Kurumsal ekipler için sunduğumuz çözümleri konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce İletişim Becerilerini Geliştirin
-Merhaba Hilal,
+Merhaba Hilal Hanım,
 Şirketinizdeki çalışanların iletişim becerilerini güçlendirmek, global toplantılara daha hazır hale gelmelerini sağlamak için online İngilizce konuşma pratiği sunuyoruz. Hedefe yönelik uygulamalarımızla çalışanların kendilerine olan güvenlerini artırabiliriz. Gelişim takibi ve raporlama ile de süreci daha verimli hale getirebiliriz. Detayları konuşmak isterseniz, size uygun bir zamanda görüşmeyi çok isterim.
 İyi çalışmalar dilerim,
 [Adınız] 
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>GEMAK GENEL SOGUTMA A.Ş.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7528,7 +7528,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Tuzla, Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>85</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Merhaba Ahmet, global toplantılardaki iletişim engellerini aşmak adına çalışanlarınızın İngilizce konuşma pratiğine ihtiyaç duyabileceğini düşünüyorum. Konuşarak Öğren ile bu süreci kolaylaştırabiliriz. Biraz sohbet edelim mi?</t>
+          <t>Merhaba Ahmet Bey, global toplantılardaki iletişim engellerini aşmak adına çalışanlarınızın İngilizce konuşma pratiğine ihtiyaç duyabileceğini düşünüyorum. Konuşarak Öğren ile bu süreci kolaylaştırabiliriz. Biraz sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -7607,12 +7607,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>EKO TEKSTİL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -7623,7 +7623,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -7663,18 +7663,18 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Merhaba Fatih, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmek için nasıl çözümler aradığınızı merak ediyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Fatih Bey, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmek için nasıl çözümler aradığınızı merak ediyorum. Konuşarak Öğren ile, çalışanlarınızın global toplantılara daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce İletişim Becerilerini Geliştirin
-Merhaba Fatih,
+Merhaba Fatih Bey,
 HR alanındaki tecrübelerinizle, çalışanlarınızın İngilizce iletişim becerilerini geliştirme ihtiyacını anlıyorum. Konuşarak Öğren olarak, ekibinize online İngilizce konuşma pratiği sunuyoruz. Bu sayede, global toplantılara daha özgüvenli katılmalarını sağlıyor ve gelişimlerini raporluyoruz. Çözümümüz hakkında daha fazla bilgi almak isterseniz, bir görüşme ayarlayalım.
 İyi çalışmalar,
 [İsminiz]</t>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -7760,13 +7760,13 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Merhaba Birgul Hanım, gelişen iş dünyasında çalışanlarınızın İngilizce konuşma becerilerini artırmalarına yardımcı olabileceğimize inanıyorum. Online konuşma pratiği ile ekibinizin global toplantılara daha hazır hale gelmesini sağlayabiliriz. Detayları konuşmak ister misiniz?</t>
+          <t>Merhaba Birgul Bey, gelişen iş dünyasında çalışanlarınızın İngilizce konuşma becerilerini artırmalarına yardımcı olabileceğimize inanıyorum. Online konuşma pratiği ile ekibinizin global toplantılara daha hazır hale gelmesini sağlayabiliriz. Detayları konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Birgul Hanım,
+Merhaba Birgul Bey,
 Gelişen iş dünyasında, ekiplerinizin İngilizce konuşma becerilerini geliştirmekte zorluklar yaşadığını biliyorum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın kendine güvenlerini artırmalarına ve global toplantılara daha iyi hazırlanmalarına yardımcı olabiliriz.
 Görüşmek için uygun bir zaman ayarlamak ister misiniz?
 Saygılarımla,
@@ -7793,12 +7793,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>QTerminals Antalya</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7809,7 +7809,7 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Antalya, Turkey</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Merhaba Emine, çalışanların İngilizce iletişim becerilerini geliştirmek ve bu süreçteki ilerlemeyi takip etmek adına sizlerle tanışmak istedim. Online konuşma pratiği ile ekiplerinizi daha etkili hale getirebiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Emine Hanım, çalışanların İngilizce iletişim becerilerini geliştirmek ve bu süreçteki ilerlemeyi takip etmek adına sizlerle tanışmak istedim. Online konuşma pratiği ile ekiplerinizi daha etkili hale getirebiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7887,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Sirena Marine</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları ve İSG Müdürü</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7903,7 +7903,7 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Bursa, Turkey</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7943,18 +7943,18 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Merhaba Tuğba, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmelerine yardımcı olmanın önemini biliyorum. Konuşarak Öğren ile online konuşma pratiği sunarak, ekibinizin özgüvenini ve toplantılardaki etkinliğini artırabilirsiniz. Detayları paylaşmak ister misiniz? Sevgiler!</t>
+          <t>Merhaba Tuğba Hanım, kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmelerine yardımcı olmanın önemini biliyorum. Konuşarak Öğren ile online konuşma pratiği sunarak, ekibinizin özgüvenini ve toplantılardaki etkinliğini artırabilirsiniz. Detayları paylaşmak ister misiniz? Sevgiler!</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Konu: Ekibinizin İngilizce İletişim Becerilerini Güçlendirin
-Merhaba Tuğba,
+Merhaba Tuğba Hanım,
 Türkiye'deki HR profesyonelleri olarak, kurumsal ekiplerde etkili iletişimin önemini biliyoruz. Konuşarak Öğren olarak, çalışanlarınıza online İngilizce konuşma pratiği sunarak, iletişim becerilerini geliştirmelerine yardımcı olabiliriz. Bu, global toplantılarda daha etkili olmalarını sağlayacak ve özgüvenlerini artıracaktır.
 Daha fazla bilgi almak isterseniz, sizinle görüşmek isterim.
 Sevgiler,
@@ -7970,7 +7970,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Merhaba Latif, HR teknolojileri alanındaki çalışmalarınızı takip ediyorum. Ekibinizin İngilizce konuşma becerilerini geliştirmesi, global toplantılarda daha etkili olmalarını sağlayabilir. Konuşarak Öğren, bu konuda destek olabilir. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Latif Bey, HR teknolojileri alanındaki çalışmalarınızı takip ediyorum. Ekibinizin İngilizce konuşma becerilerini geliştirmesi, global toplantılarda daha etkili olmalarını sağlayabilir. Konuşarak Öğren, bu konuda destek olabilir. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8136,13 +8136,13 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Merhaba Lara, HR alanındaki deneyiminizle, çalışanların İngilizce konuşma becerilerini geliştirmesi için etkili çözümler sunabileceğimize inanıyorum. Konuşarak Öğren ile ekibinizin iletişim yeteneklerini güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Lara Hanım, HR alanındaki deneyiminizle, çalışanların İngilizce konuşma becerilerini geliştirmesi için etkili çözümler sunabileceğimize inanıyorum. Konuşarak Öğren ile ekibinizin iletişim yeteneklerini güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Lara,
+Merhaba Lara Hanım,
 Kurumsal ekibinizin global toplantılara daha iyi hazırlanabilmesi için İngilizce konuşma becerilerini geliştirmek önemli bir konu. Konuşarak Öğren olarak, online İngilizce konuşma pratiği ile çalışanlarınızın güvenini artırmayı ve gelişimlerini düzenli olarak takip etmeyi sağlıyoruz. Bu konuda sizinle bir görüşme yapmak isterim. 
 İyi çalışmalar dilerim,
 [İsminiz]  
@@ -8229,13 +8229,13 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Merhaba Gülşah, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırma konusundaki çabalarınızı duydum. Kurumsal ekipler için online İngilizce pratik imkanı sunarak bu hedefe ulaşmalarına yardımcı olabiliriz. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Gülşah Hanım, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırma konusundaki çabalarınızı duydum. Kurumsal ekipler için online İngilizce pratik imkanı sunarak bu hedefe ulaşmalarına yardımcı olabiliriz. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Konu: Ekiplerin İngilizce İletişim Becerilerini Geliştirin
-Merhaba Gülşah,
+Merhaba Gülşah Hanım,
 Global iş ortamında ekiplerinizin İngilizce iletişim becerilerini artırmak için etkili bir yol arıyorsanız, size yardımcı olabiliriz. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Ekiplerinizin uluslararası toplantılara daha iyi hazırlanması ve kendine güven eksikliklerini gidermesi için birlikte çalışabiliriz. 
 Detayları paylaşmak isterim.
 Saygılarımla,
@@ -8322,13 +8322,13 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Merhaba Yasemin, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmesine yardımcı olma konusunda katkınızın büyük olduğunu düşünüyorum. Konuşarak Öğren ile ekiplerinizi global toplantılara daha iyi hazırlayabilirsiniz. Daha fazla bilgi için bağlantı kuralım!</t>
+          <t>Merhaba Yasemin Hanım, HR alanındaki deneyiminizle, ekiplerin İngilizce iletişim becerilerini geliştirmesine yardımcı olma konusunda katkınızın büyük olduğunu düşünüyorum. Konuşarak Öğren ile ekiplerinizi global toplantılara daha iyi hazırlayabilirsiniz. Daha fazla bilgi için bağlantı kuralım!</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Konu: Ekip İletişimini Güçlendirin
-Merhaba Yasemin,
+Merhaba Yasemin Hanım,
 Kurumsal ekiplerin İngilizce iletişim becerilerini geliştirmeleri, global toplantılarda etkinliklerini artırmak için kritik. Konuşarak Öğren, ekiplerinize çevrimiçi İngilizce konuşma pratiği sunarak bu süreci destekliyor. Gelişim takibi ve raporlama ile ilerlemenizi kolayca takip edebilirsiniz. 
 Detayları konuşmak için bir görüşme ayarlamak ister misiniz?
 Saygılarımla,
@@ -8416,13 +8416,13 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Merhaba Onur, şirketinizdeki ekiplerin İngilizce konuşma pratiği ihtiyacını gözlemledim. Konuşarak Öğren ile speaking confidence ve global toplantılara hazırlık süreçlerinizi güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Onur Bey, şirketinizdeki ekiplerin İngilizce konuşma pratiği ihtiyacını gözlemledim. Konuşarak Öğren ile speaking confidence ve global toplantılara hazırlık süreçlerinizi güçlendirebiliriz. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce İletişim Becerilerini Geliştirin
-Merhaba Onur,
+Merhaba Onur Bey,
 Gelişmiş iletişim becerileri, global toplantılarda etkin olmanın anahtarı. Konuşarak Öğren olarak, kurumsal ekiplerinize özel online İngilizce konuşma pratiği sunuyoruz. Ekip üyelerinizin speaking confidence ve global meeting readiness düzeylerini artırarak, uluslararası arenada daha etkili olmalarını sağlamak istiyoruz. 
 Detayları görüşmek için uygun bir zamanınız var mı?
 İyi çalışmalar,
@@ -8449,12 +8449,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Auto Life Center</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -8465,7 +8465,7 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8505,18 +8505,18 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>90</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Merhaba Duygu, HR alanındaki tecrübelerinizle ekibinizin global toplantılarda daha özgüvenli olmasına katkı sağlamak için online İngilizce konuşma pratiği sunuyoruz. Bu konuda daha fazla bilgi almak ister misiniz?</t>
+          <t>Merhaba Duygu Hanım, HR alanındaki tecrübelerinizle ekibinizin global toplantılarda daha özgüvenli olmasına katkı sağlamak için online İngilizce konuşma pratiği sunuyoruz. Bu konuda daha fazla bilgi almak ister misiniz?</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Konu: Ekibinizin İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Duygu,
+Merhaba Duygu Hanım,
 Şirketinizin global toplantılarda daha etkin bir şekilde yer alabilmesi için, ekibinize özel online İngilizce konuşma pratiği sunuyoruz. Bu program, çalışanlarınızın kendilerine olan güvenini artırarak, uluslararası işbirliklerinde daha başarılı olmalarına yardımcı olabilir. 
 Detayları konuşmak isterseniz, size yardımcı olmaktan mutluluk duyarım.
 İyi çalışmalar,
@@ -8531,7 +8531,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -8543,12 +8543,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>PozitifTech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8559,7 +8559,7 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8599,18 +8599,18 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Merhaba Nejla, global iş ortamında İngilizce konuşma becerilerinin önemini biliyorum. Kurumsal ekipler için sunduğumuz online konuşma pratiği ile iletişim becerilerini geliştirmek konusunda yardımcı olabilirim. Görüşmek ister misiniz?</t>
+          <t>Merhaba Nejla Hanım, global iş ortamında İngilizce konuşma becerilerinin önemini biliyorum. Kurumsal ekipler için sunduğumuz online konuşma pratiği ile iletişim becerilerini geliştirmek konusunda yardımcı olabilirim. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Konu: Takımınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Nejla,
+Merhaba Nejla Hanım,
 Gelişen global iş ortamında, çalışanların İngilizce konuşma yeteneklerinin yetersizliği büyük bir zorluk oluşturuyor. Konuşarak Öğren olarak, ekiplerinizi online İngilizce konuşma pratiği ile destekleyerek, iletişim becerilerini artırmayı ve global toplantılarda daha etkili olmalarını sağlamayı hedefliyoruz.
 Bu süreçte, gelişim takibi ve raporlama ile sürekli ilerleme kaydetmelerine yardımcı oluyoruz. Şirketinizin bu konuda nasıl bir destek alabileceğini konuşmak ister misiniz?
 İyi çalışmalar,
@@ -8624,7 +8624,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -8636,12 +8636,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>MAY Tohum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8652,7 +8652,7 @@
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Bursa, Turkey</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -8692,18 +8692,18 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Merhaba Sebla, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırmak adına nasıl bir yol izlediğinizi merak ediyorum. Konuşarak Öğren ile kurumsal ekiplere yönelik çözümler sunuyoruz. İlgilenirseniz, detayları konuşalım.</t>
+          <t>Merhaba Sebla Hanım, global iş ortamında ekiplerin İngilizce iletişim becerilerini artırmak adına nasıl bir yol izlediğinizi merak ediyorum. Konuşarak Öğren ile kurumsal ekiplere yönelik çözümler sunuyoruz. İlgilenirseniz, detayları konuşalım.</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İngilizce İletişim Becerilerini Güçlendirin
-Merhaba Sebla,
+Merhaba Sebla Hanım,
 Gelişen global iş ortamında, ekiplerin İngilizce konuşma pratiği yaparak kendilerine güven kazanması ve uluslararası toplantılara hazır hale gelmesi oldukça önemli. Konuşarak Öğren olarak, kurumsal ekipler için online İngilizce konuşma pratiği sunuyoruz. Çalışanlarınızın iletişim becerilerini geliştirmeye yönelik çözümlerimizle, gelişim takibi ve raporlama süreçlerini de destekliyoruz. 
 Detayları konuşmak isterseniz, memnuniyetle yardımcı olurum.
 İyi çalışmalar,
@@ -8717,7 +8717,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -8790,13 +8790,13 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Merhaba Nurdan, İngilizce konuşma pratiği eksikliğinin ekiplerinizdeki global toplantılara hazırlığı etkilediğini biliyoruz. Konuşarak Öğren ile bu süreci geliştirmek ve ekiplerinizin özgüvenini artırmak hakkında konuşmak ister misiniz?</t>
+          <t>Merhaba Nurdan Bey, İngilizce konuşma pratiği eksikliğinin ekiplerinizdeki global toplantılara hazırlığı etkilediğini biliyoruz. Konuşarak Öğren ile bu süreci geliştirmek ve ekiplerinizin özgüvenini artırmak hakkında konuşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Konu: Ekipleriniz için İngilizce Konuşma Pratiği
-Merhaba Nurdan,
+Merhaba Nurdan Bey,
 Umarım iyisinizdir! Şirketinizdeki ekiplerin global toplantılara daha etkili katılım göstermesi için İngilizce konuşma pratiğinin önemini biliyorum. Konuşarak Öğren olarak, online platformumuz ile ekip üyelerinizin speaking confidence ve global meeting readiness becerilerini geliştirmelerine yardımcı olabiliriz. 
 Sizinle bu konuda daha detaylı konuşmak isterim. Uygun olduğunuzda bir görüşme ayarlayabilir miyiz?
 İyi çalışmalar,
@@ -8822,12 +8822,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>Healmedy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8838,7 +8838,7 @@
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Merhaba Banu, İngilizce konuşma pratiği ile çalışanların global toplantılara daha hazır hale gelmesini sağlıyoruz. Ekibinizin iletişim becerilerini güçlendirmek, uluslararası iletişimdeki özgüvenlerini artırmak için yardımcı olabiliriz. Görüşelim mi?</t>
+          <t>Merhaba Banu Hanım, İngilizce konuşma pratiği ile çalışanların global toplantılara daha hazır hale gelmesini sağlıyoruz. Ekibinizin iletişim becerilerini güçlendirmek, uluslararası iletişimdeki özgüvenlerini artırmak için yardımcı olabiliriz. Görüşelim mi?</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>FUPS BANK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Müdürü</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8930,7 +8930,7 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>Istanbul, Turkey</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Merhaba Leyla, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmanın ve uluslararası toplantılara hazırlanmanın ne kadar önemli olduğunu biliyorum. Konuşarak Öğren olarak bu alanda destek olabileceğimizi düşünüyorum. Bağlantıda kalalım!</t>
+          <t>Merhaba Leyla Hanım, İngilizce konuşma pratiği ile çalışanların kendine güvenini artırmanın ve uluslararası toplantılara hazırlanmanın ne kadar önemli olduğunu biliyorum. Konuşarak Öğren olarak bu alanda destek olabileceğimizi düşünüyorum. Bağlantıda kalalım!</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9161,13 +9161,13 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Merhaba Ferda, HR profesyonellerinin İngilizce iletişim becerilerini güçlendirmek için online konuşma pratiği sunuyoruz. Takımınızın global işbirliğinde daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
+          <t>Merhaba Ferda Hanım, HR profesyonellerinin İngilizce iletişim becerilerini güçlendirmek için online konuşma pratiği sunuyoruz. Takımınızın global işbirliğinde daha hazır hale gelmesine yardımcı olabiliriz. Görüşmek ister misiniz?</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Konu: Takımınız için İngilizce Konuşma Pratiği 
-Merhaba Ferda, 
+Merhaba Ferda Hanım, 
 Şirketinizin HR ekibinin global işbirliğini güçlendirmek için etkili bir çözüm arayışında olduğunu biliyorum. Konuşarak Öğren olarak, online İngilizce konuşma pratiği sunarak çalışanlarınızın iletişim becerilerini geliştirmelerine yardımcı olabiliriz. Bu sayede, global toplantılara daha hazır bir şekilde katılabilirler. Gelişim takibi ve raporlama ile süreci daha da verimli hale getiriyoruz. 
 İlgilenirseniz, detayları konuşmak için bir görüşme ayarlayabiliriz.
 İyi çalışmalar, 
@@ -9254,13 +9254,13 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Merhaba Müzeyyen, iletişim becerilerini geliştirmek için harika bir fırsat sunuyoruz! Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim raporlaması ile global iletişimi güçlendirmek istemez misin? Detayları paylaşmak isterim.</t>
+          <t>Merhaba Müzeyyen Hanım, iletişim becerilerini geliştirmek için harika bir fırsat sunuyoruz! Kurumsal ekipler için İngilizce konuşma pratiği ve gelişim raporlaması ile global iletişimi güçlendirmek istemez misin? Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Konu: Kurumsal Ekipler İçin İngilizce Konuşma Pratiği
-Merhaba Müzeyyen,
+Merhaba Müzeyyen Hanım,
 Çalışanlarınızın İngilizce konuşma becerilerini artırarak global toplantılara daha hazırlıklı olmalarını sağlamak istiyorsanız, 'Konuşarak Öğren' olarak size destek olabiliriz. Online İngilizce konuşma pratiği sunarak, ekibinizin kendine güvenini artırmayı ve gelişimlerini takip etmeyi hedefliyoruz. İlgilenirseniz, detayları paylaşmak isterim.
 Saygılarımla,
 [Adınız]</t>
@@ -9346,13 +9346,13 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Merhaba Yağmur, İngilizce konuşma pratiği ve global toplantılara hazırlık konusunda ekibinize destek olabileceğimizi düşünüyorum. Konuşarak Öğren ile iletişim becerilerinizi geliştirebilir ve daha etkili bir şekilde global platformlarda yer alabilirsiniz. Detaylar için bir sohbet edelim mi?</t>
+          <t>Merhaba Yağmur Hanım, İngilizce konuşma pratiği ve global toplantılara hazırlık konusunda ekibinize destek olabileceğimizi düşünüyorum. Konuşarak Öğren ile iletişim becerilerinizi geliştirebilir ve daha etkili bir şekilde global platformlarda yer alabilirsiniz. Detaylar için bir sohbet edelim mi?</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Konu: Global Toplantılara Daha Hazır Ekipler İçin
-Merhaba Yağmur,
+Merhaba Yağmur Hanım,
 Kurumsal ekibinizin İngilizce konuşma pratiği eksikliği ile başa çıkmak için size yardımcı olabileceğimize inanıyorum. Konuşarak Öğren, ekiplerinize online İngilizce konuşma pratiği, bireysel gelişim takibi ve raporlama sunarak, global toplantılara daha iyi hazırlanmalarına destek oluyor.
 Bu konuda bir görüşme yapmayı ister misiniz? 
 Saygılarımla,
@@ -9440,7 +9440,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Merhaba Betül, HR alanında çalışan biri olarak, çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlık süreçlerini kolaylaştırmak adına size yardımcı olabileceğimi düşünüyorum. Detayları paylaşmak ister misiniz?</t>
+          <t>Merhaba Betül Hanım, HR alanında çalışan biri olarak, çalışanların İngilizce konuşma güvenini artırmak ve global toplantılara hazırlık süreçlerini kolaylaştırmak adına size yardımcı olabileceğimi düşünüyorum. Detayları paylaşmak ister misiniz?</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>To be verified from LinkedIn profile/company page</t>
+          <t>CR Canreis Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HR / People Professional - to verify</t>
+          <t>İnsan Kaynakları Direktörü</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9488,7 +9488,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Turkey - to verify</t>
+          <t>İzmir, Turkey</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>100</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Merhaba Yeliz, İngilizce konuşma pratiği konusundaki deneyimlerinizi merak ediyorum. Takımınızın global toplantılarda daha etkili olabilmesi için pratik yapma fırsatları sunuyoruz. İlgilenir misiniz?</t>
+          <t>Merhaba Yeliz Hanım, İngilizce konuşma pratiği konusundaki deneyimlerinizi merak ediyorum. Takımınızın global toplantılarda daha etkili olabilmesi için pratik yapma fırsatları sunuyoruz. İlgilenir misiniz?</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>new_enriched_needs_manual_verification</t>
+          <t>verified_message_ready</t>
         </is>
       </c>
     </row>
@@ -9626,13 +9626,13 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Merhaba Busra, HR profesyoneli olarak ekiplerinizin İngilizce konuşma becerilerini geliştirmesine katkı sağlamak ilginizi çekebilir. Konuşarak Öğren ile online pratik yaparak, çalışanların güvenle iletişim kurmalarını sağlama fırsatını keşfedelim!</t>
+          <t>Merhaba Busra Hanım, HR profesyoneli olarak ekiplerinizin İngilizce konuşma becerilerini geliştirmesine katkı sağlamak ilginizi çekebilir. Konuşarak Öğren ile online pratik yaparak, çalışanların güvenle iletişim kurmalarını sağlama fırsatını keşfedelim!</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Konu: Ekiplerinizin İletişim Becerilerini Geliştirin
-Merhaba Busra,
+Merhaba Busra Hanım,
 HR alanındaki deneyiminiz ile çalışanlarınızın İngilizce konuşma pratiği yaparak iletişim becerilerini geliştirmesine katkıda bulunmak isteyebilirsiniz. Konuşarak Öğren, kurumsal ekipler için özel olarak tasarlanmış online pratik programları sunuyor. Bu sayede, çalışanlarınızın konuşma özgüveni artarken, global toplantılara daha iyi hazırlanabilecekler. Daha fazla bilgi almak isterseniz, memnuniyetle görüşürüm.
 İyi günler dilerim,
 [Adınız]</t>
@@ -9718,13 +9718,13 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Merhaba Mehmet, HR profesyoneli olarak, çalışanlarınızın global toplantılara daha iyi hazırlanmaları için İngilizce konuşma becerilerini geliştirmeleri gerektiğini biliyorum. Konuşarak Öğren, ekibinize online pratik imkanı sunarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim.</t>
+          <t>Merhaba Mehmet Bey, HR profesyoneli olarak, çalışanlarınızın global toplantılara daha iyi hazırlanmaları için İngilizce konuşma becerilerini geliştirmeleri gerektiğini biliyorum. Konuşarak Öğren, ekibinize online pratik imkanı sunarak bu süreci kolaylaştırabilir. Detayları paylaşmak isterim.</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Konu: Çalışanlarınızın İngilizce Konuşma Becerilerini Geliştirin
-Merhaba Mehmet,
+Merhaba Mehmet Bey,
 Şirketinizin global toplantılarda etkili iletişim kurabilmesi için çalışanların İngilizce konuşma becerilerini geliştirmesi kritik. Konuşarak Öğren, kurumsal ekipler için online İngilizce konuşma pratiği, gelişim takibi ve raporlama sunarak bu ihtiyacı karşılıyor.
 Ekibinizin güvenle İngilizce konuşmasını sağlamaya yardımcı olabiliriz. Bir görüşme ayarlayıp detayları konuşmayı çok isterim.
 İyi çalışmalar,
@@ -9813,7 +9813,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Merhaba Duygu, kurumsal ekiplerin İngilizce konuşma pratiği ve gelişim takibi konusunda sağladığımız çözümlerle ilgili konuşmak isterim. Çalışanlarınızın global iletişim becerilerini artırmalarına nasıl destek olabileceğimize bakalım mı?</t>
+          <t>Merhaba Duygu Hanım, kurumsal ekiplerin İngilizce konuşma pratiği ve gelişim takibi konusunda sağladığımız çözümlerle ilgili konuşmak isterim. Çalışanlarınızın global iletişim becerilerini artırmalarına nasıl destek olabileceğimize bakalım mı?</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
